--- a/briefings/sezon-kadro-20260902/verimlilik-2026.xlsx
+++ b/briefings/sezon-kadro-20260902/verimlilik-2026.xlsx
@@ -7,11 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ozet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Magaza" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yillar" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Oca-Agu" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yontem" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sunum" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ozet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Magaza" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kadro" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bolum" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yillar" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Oca-Agu" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yontem" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +23,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="+0.0%;-0.0%"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0"/>
-    <numFmt numFmtId="166" formatCode="0.0&quot;x&quot;"/>
-    <numFmt numFmtId="167" formatCode="+0;-0;0"/>
+  <numFmts count="9">
+    <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
+    <numFmt numFmtId="165" formatCode="+0.0%;-0.0%"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+    <numFmt numFmtId="167" formatCode="0.0&quot;x&quot;"/>
+    <numFmt numFmtId="168" formatCode="+0;-0;0"/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
+    <numFmt numFmtId="170" formatCode="+0 kişi;-0 kişi"/>
+    <numFmt numFmtId="171" formatCode="+0,0%"/>
+    <numFmt numFmtId="172" formatCode="0,0&quot;x&quot;"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,7 +53,6 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -58,12 +65,41 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="10"/>
     </font>
     <font>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F5B57"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11.5"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F7A4D"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <color rgb="00444444"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F5B57"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,6 +109,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E30622"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F5B57"/>
       </patternFill>
     </fill>
     <fill>
@@ -112,43 +153,79 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="1" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -795,10 +872,261 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A2:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="82" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Sezon 2026 — kadro mu büyüdü, iş mi büyüdü?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Beş mağaza kadrosu · üç POS mağazası iş hacmi · 2025 ile aynı takvim dönemi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Kadro farkı sezon başlamadan ÖNCE oluştu.</t>
+        </is>
+      </c>
+      <c r="C5" s="5">
+        <f>'Ozet'!D20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>30 Haziran'da kadrolu personel 139'dan 153'e çıkmıştı.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Sezon boyunca kadro büyümedi, KÜÇÜLDÜ.</t>
+        </is>
+      </c>
+      <c r="C7" s="5">
+        <f>'Ozet'!C22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>1 Temmuz – 31 Ağustos: kadrolu 153 → 149. Geçen yıl da aynı yönde (−4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Sezonluk personel geçen yıldan AZ.</t>
+        </is>
+      </c>
+      <c r="C9" s="5">
+        <f>'Ozet'!D23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>31 Ağustos'ta çalışan sezonluk: 65 → 62 kişi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Aynı dönemde elleçlenen ürün adedi %35 arttı.</t>
+        </is>
+      </c>
+      <c r="C11" s="7">
+        <f>'Ozet'!E8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>574.718 → 775.192 adet. Adet enflasyondan etkilenmez — fiilen kasadan geçen, rafa dizilen mal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Ciro %71 arttı.</t>
+        </is>
+      </c>
+      <c r="C13" s="7">
+        <f>'Ozet'!E10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>71,8 milyon → 122,6 milyon ₺ (KDV dahil, iadeler düşülmüş).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>KİŞİ BAŞINA düşen iş de arttı.</t>
+        </is>
+      </c>
+      <c r="C15" s="7">
+        <f>'Ozet'!E13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Kişi başı ürün 4.019 → 4.845 adet; günlük 71,8 → 86,5 adet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>İş hacmi, kadronun yaklaşık 3 KATI hızla büyüdü.</t>
+        </is>
+      </c>
+      <c r="C17" s="8">
+        <f>'Ozet'!B17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Ürün adedi +%34,9 · kadro +%11,9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Artış yönetimde değil, RAFIN ÖNÜNDE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Yönetim +0 · Mal Kabul +0 · İdari İşler +0. Artış: Yardımcı Kitap +6 · Kırtasiye +3 · Kasa +2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Büyüme kurumsaldan gelmedi, mağazadan geldi.</t>
+        </is>
+      </c>
+      <c r="C21" s="7">
+        <f>'Oca-Agu'!G4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Sınav Okulları Ocak–Ağustos cirosu −%22,4 küçüldü; mağaza tarafı +%54,9 büyüdü.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="9" t="n"/>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>TEK CÜMLE: Kadro farkı 1 Temmuz'dan önce kurulmuştu; sezon içinde kadro küçülürken iş hacmi %35 büyüdü, kişi başına düşen iş %21 arttı.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>Rakamların kaynağı ve kontrolü: Ozet · Magaza · Kadro · Bolum · Yillar · Oca-Agu · Yontem sayfaları. Kadro = Zirve İK (İK'nın kendi karşılaştırma raporuyla birebir), iş hacmi = DerinSIS mağaza satışı (Sınav hariç).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -806,337 +1134,511 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Ayni kadro, daha cok is — uc POS magazasi (okul-hizali pencere, 56 gun)</t>
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Ayni kadro, daha cok is — kapsamlar AYRI etiketli, altta kopru kontrolu</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Olcu</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Fark</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Degisim</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Kadro — 31.08 (kisi)</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>143</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>160</v>
-      </c>
-      <c r="D4" s="4">
-        <f>C4-B4</f>
-        <v/>
-      </c>
-      <c r="E4" s="5">
-        <f>IF(B4=0,"",C4/B4-1)</f>
-        <v/>
-      </c>
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>KAPSAM A — UC POS MAGAZASI (FSM · Ozluce · Ist. Yolu) · is hacmi YALNIZ burada olculebilir</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Urun adedi (elleclenen)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Kadrolu — 31.08</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n">
+        <v>96</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>111</v>
+      </c>
+      <c r="D5" s="18">
+        <f>C5-B5</f>
+        <v/>
+      </c>
+      <c r="E5" s="19">
+        <f>IF(B5=0,"",C5/B5-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Sezonluk — 31.08</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>49</v>
+      </c>
+      <c r="D6" s="18">
+        <f>C6-B6</f>
+        <v/>
+      </c>
+      <c r="E6" s="19">
+        <f>IF(B6=0,"",C6/B6-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20">
+        <f> TOPLAM KADRO — 31.08 (kisi)</f>
+        <v/>
+      </c>
+      <c r="B7" s="21">
+        <f>B5+B6</f>
+        <v/>
+      </c>
+      <c r="C7" s="21">
+        <f>C5+C6</f>
+        <v/>
+      </c>
+      <c r="D7" s="22">
+        <f>C7-B7</f>
+        <v/>
+      </c>
+      <c r="E7" s="23">
+        <f>C7/B7-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Urun adedi (elleclenen) — 56 gun</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n">
         <v>574717.7</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C8" s="17" t="n">
         <v>775191.55</v>
       </c>
-      <c r="D5" s="4">
-        <f>C5-B5</f>
-        <v/>
-      </c>
-      <c r="E5" s="5">
-        <f>IF(B5=0,"",C5/B5-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Ciro — KDV haric (TL)</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>66929723.56999837</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>114687785.5800005</v>
-      </c>
-      <c r="D6" s="4">
-        <f>C6-B6</f>
-        <v/>
-      </c>
-      <c r="E6" s="5">
-        <f>IF(B6=0,"",C6/B6-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Ciro — KDV dahil (TL)</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>71837429.11999327</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>122601380.8499953</v>
-      </c>
-      <c r="D7" s="4">
-        <f>C7-B7</f>
-        <v/>
-      </c>
-      <c r="E7" s="5">
-        <f>IF(B7=0,"",C7/B7-1)</f>
+      <c r="D8" s="18">
+        <f>C8-B8</f>
+        <v/>
+      </c>
+      <c r="E8" s="19">
+        <f>IF(B8=0,"",C8/B8-1)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>KISI BASI — asil olcu</t>
-        </is>
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Ciro — KDV haric (TL)</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n">
+        <v>66929723.56999852</v>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>114687785.58</v>
+      </c>
+      <c r="D9" s="18">
+        <f>C9-B9</f>
+        <v/>
+      </c>
+      <c r="E9" s="19">
+        <f>IF(B9=0,"",C9/B9-1)</f>
+        <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Urun adedi / kisi</t>
-        </is>
-      </c>
-      <c r="B10" s="7">
-        <f>B5/B4</f>
-        <v/>
-      </c>
-      <c r="C10" s="7">
-        <f>C5/C4</f>
-        <v/>
-      </c>
-      <c r="D10" s="7">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Ciro — KDV dahil (TL)</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="n">
+        <v>71837429.11999343</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>122601380.8499947</v>
+      </c>
+      <c r="D10" s="18">
         <f>C10-B10</f>
         <v/>
       </c>
-      <c r="E10" s="8">
-        <f>C10/B10-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Urun adedi / kisi / gun</t>
-        </is>
-      </c>
-      <c r="B11" s="9">
-        <f>B5/B4/56</f>
-        <v/>
-      </c>
-      <c r="C11" s="9">
-        <f>C5/C4/56</f>
-        <v/>
-      </c>
-      <c r="D11" s="9">
-        <f>C11-B11</f>
-        <v/>
-      </c>
-      <c r="E11" s="8">
-        <f>C11/B11-1</f>
+      <c r="E10" s="19">
+        <f>IF(B10=0,"",C10/B10-1)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Ciro (KDV haric) / kisi (TL)</t>
-        </is>
-      </c>
-      <c r="B12" s="7">
-        <f>B6/B4</f>
-        <v/>
-      </c>
-      <c r="C12" s="7">
-        <f>C6/C4</f>
-        <v/>
-      </c>
-      <c r="D12" s="7">
-        <f>C12-B12</f>
-        <v/>
-      </c>
-      <c r="E12" s="8">
-        <f>C12/B12-1</f>
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>KISI BASI — asil olcu · kapsam A toplam kadrosuna bolunur (satir 7)</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Urun adedi / kisi</t>
+        </is>
+      </c>
+      <c r="B13" s="24">
+        <f>B8/B7</f>
+        <v/>
+      </c>
+      <c r="C13" s="24">
+        <f>C8/C7</f>
+        <v/>
+      </c>
+      <c r="D13" s="24">
+        <f>C13-B13</f>
+        <v/>
+      </c>
+      <c r="E13" s="25">
+        <f>C13/B13-1</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>Is buyumesi kadro buyumesinin kac kati</t>
-        </is>
-      </c>
-      <c r="B14" s="11">
-        <f>E5/E4</f>
-        <v/>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>urun adedi / kadro</t>
-        </is>
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Urun adedi / kisi / gun</t>
+        </is>
+      </c>
+      <c r="B14" s="26">
+        <f>B8/B7/56</f>
+        <v/>
+      </c>
+      <c r="C14" s="26">
+        <f>C8/C7/56</f>
+        <v/>
+      </c>
+      <c r="D14" s="26">
+        <f>C14-B14</f>
+        <v/>
+      </c>
+      <c r="E14" s="25">
+        <f>C14/B14-1</f>
+        <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ayni oran ciro ile</t>
-        </is>
-      </c>
-      <c r="B15" s="13">
-        <f>E6/E4</f>
-        <v/>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>ciro (KDV haric) / kadro</t>
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Ciro (KDV haric) / kisi (TL)</t>
+        </is>
+      </c>
+      <c r="B15" s="24">
+        <f>B9/B7</f>
+        <v/>
+      </c>
+      <c r="C15" s="24">
+        <f>C9/C7</f>
+        <v/>
+      </c>
+      <c r="D15" s="24">
+        <f>C15-B15</f>
+        <v/>
+      </c>
+      <c r="E15" s="25">
+        <f>C15/B15-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Is buyumesi kadro buyumesinin kac kati (adet ÷ kadro)</t>
+        </is>
+      </c>
+      <c r="B16" s="27">
+        <f>E8/E7</f>
+        <v/>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>adet degisimi ÷ kadro degisimi</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>BES MAGAZA KADRO HAREKETI (POS'ta olmayan Heykel + Sura dahil)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Kadrolu — taban 30.06</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ayni oran ciro ile (ciro ÷ kadro)</t>
+        </is>
+      </c>
+      <c r="B17" s="28">
+        <f>E9/E7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>KAPSAM B — BES MAGAZA (+ Heykel, Sura: POS raporlamasinda YOK -&gt; is hacmi olculemez)</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Kadrolu — TABAN 30.06 (sezon oncesi kurulu kadro)</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="n">
         <v>139</v>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C20" s="21" t="n">
         <v>153</v>
       </c>
-      <c r="D18" s="14">
-        <f>C18-B18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Kadrolu — kesim 31.08</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
+      <c r="D20" s="29">
+        <f>C20-B20</f>
+        <v/>
+      </c>
+      <c r="E20" s="19">
+        <f>IF(B20=0,"",C20/B20-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Kadrolu — KESIM 31.08</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n">
         <v>135</v>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C21" s="17" t="n">
         <v>149</v>
       </c>
-      <c r="D19" s="14">
-        <f>C19-B19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Sezonluk — kesim 31.08</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
+      <c r="D21" s="18">
+        <f>C21-B21</f>
+        <v/>
+      </c>
+      <c r="E21" s="19">
+        <f>IF(B21=0,"",C21/B21-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Sezon ici kadrolu degisim (kesim - taban)</t>
+        </is>
+      </c>
+      <c r="B22" s="30">
+        <f>B21-B20</f>
+        <v/>
+      </c>
+      <c r="C22" s="30">
+        <f>C21-C20</f>
+        <v/>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>iki yilda da -4: sezon icinde kadro BUYUMEDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Sezonluk — 31.08</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="n">
         <v>65</v>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C23" s="17" t="n">
         <v>62</v>
       </c>
-      <c r="D20" s="14">
-        <f>C20-B20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Toplam — kesim 31.08</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>211</v>
-      </c>
-      <c r="D21" s="14">
-        <f>C21-B21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Sezon ici kadrolu degisim (taban -&gt; kesim)</t>
-        </is>
-      </c>
-      <c r="B22" s="14">
-        <f>B19-B18</f>
-        <v/>
-      </c>
-      <c r="C22" s="15">
-        <f>C19-C18</f>
-        <v/>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>sezon icinde kadro BUYUMEDI</t>
-        </is>
+      <c r="D23" s="18">
+        <f>C23-B23</f>
+        <v/>
+      </c>
+      <c r="E23" s="19">
+        <f>IF(B23=0,"",C23/B23-1)</f>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>Kadro farki 1 Temmuz'dan ONCE olustu: kadrolu taban 30.06'da 139 -&gt; 153. Sezon icinde (1 Tem - 31 Agu) kadro kucumustu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>Kisi basi satirlar ve tum yuzdeler Excel FORMULUDUR — ham rakami degistirin, oran kendini gunceller.</t>
+          <t xml:space="preserve">   = Toplam kadro — 31.08</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n">
+        <v>200</v>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>211</v>
+      </c>
+      <c r="D24" s="18">
+        <f>C24-B24</f>
+        <v/>
+      </c>
+      <c r="E24" s="19">
+        <f>IF(B24=0,"",C24/B24-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>KOPRU — A ile B nasil bagli (KONTROL satiri 0 olmali)</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="15" t="n"/>
+      <c r="E26" s="15" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Kapsam A toplam kadro (31.08)</t>
+        </is>
+      </c>
+      <c r="B27" s="17">
+        <f>B7</f>
+        <v/>
+      </c>
+      <c r="C27" s="17">
+        <f>C7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   + Heykel + Sura (kadrolu + sezonluk)</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="C28" s="17" t="n">
+        <v>51</v>
+      </c>
+      <c r="D28" s="18">
+        <f>C28-B28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   = Kapsam B toplam kadro (hesap)</t>
+        </is>
+      </c>
+      <c r="B29" s="21">
+        <f>B27+B28</f>
+        <v/>
+      </c>
+      <c r="C29" s="21">
+        <f>C27+C28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   KONTROL: hesap - B blogundaki toplam (0 OLMALI)</t>
+        </is>
+      </c>
+      <c r="B30" s="31">
+        <f>B29-B24</f>
+        <v/>
+      </c>
+      <c r="C30" s="31">
+        <f>C29-C24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="32" t="inlineStr">
+        <is>
+          <t>NEDEN IKI KAPSAM: is hacmi (adet/ciro) yalniz POS raporlamasi olan UC magazada olculebilir;</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   kadro hareketi ise bes magazanin tamaminda anlamli. Karismasin diye bloklar ayri + kopru var.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="32" t="inlineStr">
+        <is>
+          <t>NEDEN IKI TARIH: 30.06 = sezon baslamadan onceki kurulu kadro (+14 farki BURADA olustu),</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   31.08 = sezon zirvesindeki fiili kadro. Ayni yilin iki farkli gunu; birbirinin yerine gecmez.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="32" t="inlineStr">
+        <is>
+          <t>Kadrolu = Kadro &lt;&gt; 'SEZONLUK' · Sezonluk = Kadro = 'SEZONLUK' · Toplam = ikisinin toplami.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="32" t="inlineStr">
+        <is>
+          <t>Tum yuzde / oran / kopru satirlari Excel FORMULU — ham rakami degistir, hepsi kendini gunceller.</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1647,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1176,330 +1678,330 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Magaza bazinda kisi basi is — okul-hizali pencere (56 gun, Sinav haric)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Magaza</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Kadro 2025</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Kadro 2026</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Kadro Δ%</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Urun adedi 2025</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>Urun adedi 2026</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>Adet Δ%</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t>Adet/kisi 2025</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>Adet/kisi 2026</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t>Adet/kisi Δ%</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="13" t="inlineStr">
         <is>
           <t>Adet/kisi/gun 2025</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="13" t="inlineStr">
         <is>
           <t>Adet/kisi/gun 2026</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="13" t="inlineStr">
         <is>
           <t>Ciro 2025 (KDV haric)</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="13" t="inlineStr">
         <is>
           <t>Ciro 2026 (KDV haric)</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="13" t="inlineStr">
         <is>
           <t>Ciro Δ%</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="13" t="inlineStr">
         <is>
           <t>Ciro/kisi 2025</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q3" s="13" t="inlineStr">
         <is>
           <t>Ciro/kisi 2026</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="R3" s="13" t="inlineStr">
         <is>
           <t>Ciro/kisi Δ%</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="S3" s="13" t="inlineStr">
         <is>
           <t>Is / kadro (kac kat)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>İst. Yolu</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="17" t="n">
         <v>61</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="19">
         <f>C4/B4-1</f>
         <v/>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="17" t="n">
         <v>173398</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="17" t="n">
         <v>258168.5</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="19">
         <f>F4/E4-1</f>
         <v/>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="17">
         <f>E4/B4</f>
         <v/>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="17">
         <f>F4/C4</f>
         <v/>
       </c>
-      <c r="J4" s="17">
+      <c r="J4" s="33">
         <f>I4/H4-1</f>
         <v/>
       </c>
-      <c r="K4" s="18">
+      <c r="K4" s="34">
         <f>E4/B4/56</f>
         <v/>
       </c>
-      <c r="L4" s="18">
+      <c r="L4" s="34">
         <f>F4/C4/56</f>
         <v/>
       </c>
-      <c r="M4" s="4" t="n">
-        <v>20455158.42999977</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>40444611.76999984</v>
-      </c>
-      <c r="O4" s="5">
+      <c r="M4" s="17" t="n">
+        <v>20455158.42999981</v>
+      </c>
+      <c r="N4" s="17" t="n">
+        <v>40444611.76999976</v>
+      </c>
+      <c r="O4" s="19">
         <f>N4/M4-1</f>
         <v/>
       </c>
-      <c r="P4" s="4">
+      <c r="P4" s="17">
         <f>M4/B4</f>
         <v/>
       </c>
-      <c r="Q4" s="4">
+      <c r="Q4" s="17">
         <f>N4/C4</f>
         <v/>
       </c>
-      <c r="R4" s="17">
+      <c r="R4" s="33">
         <f>Q4/P4-1</f>
         <v/>
       </c>
-      <c r="S4" s="19">
+      <c r="S4" s="35">
         <f>G4/D4</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Özlüce</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="17" t="n">
         <v>51</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="17" t="n">
         <v>54</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="19">
         <f>C5/B5-1</f>
         <v/>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="17" t="n">
         <v>230764.7</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="17" t="n">
         <v>301250.05</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="19">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="17">
         <f>E5/B5</f>
         <v/>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="17">
         <f>F5/C5</f>
         <v/>
       </c>
-      <c r="J5" s="17">
+      <c r="J5" s="33">
         <f>I5/H5-1</f>
         <v/>
       </c>
-      <c r="K5" s="18">
+      <c r="K5" s="34">
         <f>E5/B5/56</f>
         <v/>
       </c>
-      <c r="L5" s="18">
+      <c r="L5" s="34">
         <f>F5/C5/56</f>
         <v/>
       </c>
-      <c r="M5" s="4" t="n">
-        <v>28347121.58999873</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>44784483.14999981</v>
-      </c>
-      <c r="O5" s="5">
+      <c r="M5" s="17" t="n">
+        <v>28347121.58999882</v>
+      </c>
+      <c r="N5" s="17" t="n">
+        <v>44784483.14999945</v>
+      </c>
+      <c r="O5" s="19">
         <f>N5/M5-1</f>
         <v/>
       </c>
-      <c r="P5" s="4">
+      <c r="P5" s="17">
         <f>M5/B5</f>
         <v/>
       </c>
-      <c r="Q5" s="4">
+      <c r="Q5" s="17">
         <f>N5/C5</f>
         <v/>
       </c>
-      <c r="R5" s="17">
+      <c r="R5" s="33">
         <f>Q5/P5-1</f>
         <v/>
       </c>
-      <c r="S5" s="19">
+      <c r="S5" s="35">
         <f>G5/D5</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>FSM</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="17" t="n">
         <v>42</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="17" t="n">
         <v>45</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="19">
         <f>C6/B6-1</f>
         <v/>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="17" t="n">
         <v>170555</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="17" t="n">
         <v>215773</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="19">
         <f>F6/E6-1</f>
         <v/>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="17">
         <f>E6/B6</f>
         <v/>
       </c>
-      <c r="I6" s="4">
+      <c r="I6" s="17">
         <f>F6/C6</f>
         <v/>
       </c>
-      <c r="J6" s="17">
+      <c r="J6" s="33">
         <f>I6/H6-1</f>
         <v/>
       </c>
-      <c r="K6" s="18">
+      <c r="K6" s="34">
         <f>E6/B6/56</f>
         <v/>
       </c>
-      <c r="L6" s="18">
+      <c r="L6" s="34">
         <f>F6/C6/56</f>
         <v/>
       </c>
-      <c r="M6" s="4" t="n">
-        <v>18127443.54999987</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>29458690.66000083</v>
-      </c>
-      <c r="O6" s="5">
+      <c r="M6" s="17" t="n">
+        <v>18127443.54999989</v>
+      </c>
+      <c r="N6" s="17" t="n">
+        <v>29458690.66000078</v>
+      </c>
+      <c r="O6" s="19">
         <f>N6/M6-1</f>
         <v/>
       </c>
-      <c r="P6" s="4">
+      <c r="P6" s="17">
         <f>M6/B6</f>
         <v/>
       </c>
-      <c r="Q6" s="4">
+      <c r="Q6" s="17">
         <f>N6/C6</f>
         <v/>
       </c>
-      <c r="R6" s="17">
+      <c r="R6" s="33">
         <f>Q6/P6-1</f>
         <v/>
       </c>
-      <c r="S6" s="19">
+      <c r="S6" s="35">
         <f>G6/D6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
@@ -1512,7 +2014,7 @@
         <f>SUM(C4:C6)</f>
         <v/>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="37">
         <f>C7/B7-1</f>
         <v/>
       </c>
@@ -1524,7 +2026,7 @@
         <f>SUM(F4:F6)</f>
         <v/>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="37">
         <f>F7/E7-1</f>
         <v/>
       </c>
@@ -1536,15 +2038,15 @@
         <f>F7/C7</f>
         <v/>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="25">
         <f>I7/H7-1</f>
         <v/>
       </c>
-      <c r="K7" s="23">
+      <c r="K7" s="38">
         <f>E7/B7/56</f>
         <v/>
       </c>
-      <c r="L7" s="23">
+      <c r="L7" s="38">
         <f>F7/C7/56</f>
         <v/>
       </c>
@@ -1556,7 +2058,7 @@
         <f>SUM(N4:N6)</f>
         <v/>
       </c>
-      <c r="O7" s="22">
+      <c r="O7" s="37">
         <f>N7/M7-1</f>
         <v/>
       </c>
@@ -1568,31 +2070,31 @@
         <f>N7/C7</f>
         <v/>
       </c>
-      <c r="R7" s="8">
+      <c r="R7" s="25">
         <f>Q7/P7-1</f>
         <v/>
       </c>
-      <c r="S7" s="24">
+      <c r="S7" s="39">
         <f>G7/D7</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="32" t="inlineStr">
         <is>
           <t>Kadro = 31.08 itibariyla o magazada fiilen calisan TUM personel (sezonluk + kadrolu).</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="32" t="inlineStr">
         <is>
           <t>'Is / kadro' = urun adedi buyumesi / kadro buyumesi. 1,0x'in uzeri: is kadrodan hizli buyudu.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="32" t="inlineStr">
         <is>
           <t>Ist. Yolu kadrosu en cok buyuyen magaza (50 -&gt; 61) ama ise ragmen kisi basi adedi de artti.</t>
         </is>
@@ -1604,7 +2106,1355 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Bes magaza kadro tablosu — as-of Igt &lt;= T AND (Ict IS NULL OR Ict &gt;= T)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Magaza</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Kadrolu taban 30.06 · 2025</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Kadrolu taban 30.06 · 2026</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>Taban Δ</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>Kadrolu 31.08 · 2025</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>Kadrolu 31.08 · 2026</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Sezon ici hareket 2025</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Sezon ici hareket 2026</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>Sezonluk 31.08 · 2025</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t>Sezonluk 31.08 · 2026</t>
+        </is>
+      </c>
+      <c r="K3" s="13" t="inlineStr">
+        <is>
+          <t>Toplam 31.08 · 2025</t>
+        </is>
+      </c>
+      <c r="L3" s="13" t="inlineStr">
+        <is>
+          <t>Toplam 31.08 · 2026</t>
+        </is>
+      </c>
+      <c r="M3" s="13" t="inlineStr">
+        <is>
+          <t>Toplam Δ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>İST. YOLU</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="D4" s="40">
+        <f>C4-B4</f>
+        <v/>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G4" s="40">
+        <f>E4-B4</f>
+        <v/>
+      </c>
+      <c r="H4" s="40">
+        <f>F4-C4</f>
+        <v/>
+      </c>
+      <c r="I4" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="J4" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="K4" s="17">
+        <f>E4+I4</f>
+        <v/>
+      </c>
+      <c r="L4" s="17">
+        <f>F4+J4</f>
+        <v/>
+      </c>
+      <c r="M4" s="40">
+        <f>L4-K4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>ÖZLÜCE</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="D5" s="40">
+        <f>C5-B5</f>
+        <v/>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="G5" s="40">
+        <f>E5-B5</f>
+        <v/>
+      </c>
+      <c r="H5" s="40">
+        <f>F5-C5</f>
+        <v/>
+      </c>
+      <c r="I5" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="J5" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="K5" s="17">
+        <f>E5+I5</f>
+        <v/>
+      </c>
+      <c r="L5" s="17">
+        <f>F5+J5</f>
+        <v/>
+      </c>
+      <c r="M5" s="40">
+        <f>L5-K5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>FSM</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="D6" s="40">
+        <f>C6-B6</f>
+        <v/>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="G6" s="40">
+        <f>E6-B6</f>
+        <v/>
+      </c>
+      <c r="H6" s="40">
+        <f>F6-C6</f>
+        <v/>
+      </c>
+      <c r="I6" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="J6" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="K6" s="17">
+        <f>E6+I6</f>
+        <v/>
+      </c>
+      <c r="L6" s="17">
+        <f>F6+J6</f>
+        <v/>
+      </c>
+      <c r="M6" s="40">
+        <f>L6-K6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>HEYKEL</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="D7" s="40">
+        <f>C7-B7</f>
+        <v/>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G7" s="40">
+        <f>E7-B7</f>
+        <v/>
+      </c>
+      <c r="H7" s="40">
+        <f>F7-C7</f>
+        <v/>
+      </c>
+      <c r="I7" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="J7" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="K7" s="17">
+        <f>E7+I7</f>
+        <v/>
+      </c>
+      <c r="L7" s="17">
+        <f>F7+J7</f>
+        <v/>
+      </c>
+      <c r="M7" s="40">
+        <f>L7-K7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>ŞURA</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" s="40">
+        <f>C8-B8</f>
+        <v/>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="G8" s="40">
+        <f>E8-B8</f>
+        <v/>
+      </c>
+      <c r="H8" s="40">
+        <f>F8-C8</f>
+        <v/>
+      </c>
+      <c r="I8" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" s="17">
+        <f>E8+I8</f>
+        <v/>
+      </c>
+      <c r="L8" s="17">
+        <f>F8+J8</f>
+        <v/>
+      </c>
+      <c r="M8" s="40">
+        <f>L8-K8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="36" t="inlineStr">
+        <is>
+          <t>TOPLAM</t>
+        </is>
+      </c>
+      <c r="B9" s="21">
+        <f>SUM(B4:B8)</f>
+        <v/>
+      </c>
+      <c r="C9" s="21">
+        <f>SUM(C4:C8)</f>
+        <v/>
+      </c>
+      <c r="D9" s="30">
+        <f>C9-B9</f>
+        <v/>
+      </c>
+      <c r="E9" s="21">
+        <f>SUM(E4:E8)</f>
+        <v/>
+      </c>
+      <c r="F9" s="21">
+        <f>SUM(F4:F8)</f>
+        <v/>
+      </c>
+      <c r="G9" s="41">
+        <f>E9-B9</f>
+        <v/>
+      </c>
+      <c r="H9" s="30">
+        <f>F9-C9</f>
+        <v/>
+      </c>
+      <c r="I9" s="21">
+        <f>SUM(I4:I8)</f>
+        <v/>
+      </c>
+      <c r="J9" s="21">
+        <f>SUM(J4:J8)</f>
+        <v/>
+      </c>
+      <c r="K9" s="21">
+        <f>E9+I9</f>
+        <v/>
+      </c>
+      <c r="L9" s="21">
+        <f>F9+J9</f>
+        <v/>
+      </c>
+      <c r="M9" s="41">
+        <f>L9-K9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>TABAN FARKI (D kolonu, TOPLAM satiri) = patrona soylenen +14: kadrolu 139 -&gt; 153, 1 TEMMUZ'DAN ONCE olustu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>SEZON ICI HAREKET = kesim - taban. 2026'da -4; 2025'te de -4 -&gt; sezon icinde kadro buyutulmedi, iki yilin deseni ayni.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="32" t="inlineStr">
+        <is>
+          <t>Sayim TEK TABLO uzerinden (vw_PersonelDepartman). Onceki surumde perbilgi LEFT JOIN'i bir kisiyi iki kez saymis:</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Ozluce 31.08.2026 kadrolu 42 gorunuyordu, DOGRUSU 41 (teyit: KADRO 41 + SEZONLUK 13 = 54 kisi).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Bu yuzden magaza toplami 150 degil 149; sezon ici hareket -3 degil -4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="32" t="inlineStr">
+        <is>
+          <t>Heykel ve Sura POS raporlamasinda yok -&gt; is hacmi sayfalarinda yer almaz, kadro tablosunda VARDIR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="32" t="inlineStr">
+        <is>
+          <t>KAPSAM: Lokasyon = MAGAZALAR. Cift gorevli 1 kisi (GM satinalma 'KITAP DISI S.A' + Heykel) bu</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   kapsamda GORUNMEZ. O kisi Heykel'e eklenirse taban 140 -&gt; 154, kesim 136 -&gt; 150 olur;</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   TABAN FARKI yine +14, SEZON ICI HAREKET yine -4. Yani cift gorev savunmayi DEGISTIRMIYOR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="32" t="inlineStr">
+        <is>
+          <t>Kaynak view anlik durumu tutar (kadro gecmisi yok): kisinin BUGUNKU lokasyon etiketi her iki yila</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   da uygulanir. Bu yuzden kapsam iki yilda tutarli, ama gecmis unvan/lokasyon degisimi izlenemez.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Bölüm bazında kadro — 31.08 kesimi, beş mağaza</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Bolum</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Kadrolu 2025</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Kadrolu 2026</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>Kadrolu Δ</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>Sezonluk 2025</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>Sezonluk 2026</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Sezonluk Δ</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Toplam 2025</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>Toplam 2026</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t>Toplam Δ</t>
+        </is>
+      </c>
+      <c r="K3" s="13" t="inlineStr">
+        <is>
+          <t>Sezonluk payi 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>YARDIMCI KİTAP</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="D4" s="40">
+        <f>C4-B4</f>
+        <v/>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="G4" s="40">
+        <f>F4-E4</f>
+        <v/>
+      </c>
+      <c r="H4" s="17">
+        <f>B4+E4</f>
+        <v/>
+      </c>
+      <c r="I4" s="17">
+        <f>C4+F4</f>
+        <v/>
+      </c>
+      <c r="J4" s="40">
+        <f>I4-H4</f>
+        <v/>
+      </c>
+      <c r="K4" s="42">
+        <f>IF(I4=0,"",F4/I4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>KIRTASİYE</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="D5" s="40">
+        <f>C5-B5</f>
+        <v/>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="G5" s="40">
+        <f>F5-E5</f>
+        <v/>
+      </c>
+      <c r="H5" s="17">
+        <f>B5+E5</f>
+        <v/>
+      </c>
+      <c r="I5" s="17">
+        <f>C5+F5</f>
+        <v/>
+      </c>
+      <c r="J5" s="40">
+        <f>I5-H5</f>
+        <v/>
+      </c>
+      <c r="K5" s="42">
+        <f>IF(I5=0,"",F5/I5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>KÜLTÜR</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D6" s="40">
+        <f>C6-B6</f>
+        <v/>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="40">
+        <f>F6-E6</f>
+        <v/>
+      </c>
+      <c r="H6" s="17">
+        <f>B6+E6</f>
+        <v/>
+      </c>
+      <c r="I6" s="17">
+        <f>C6+F6</f>
+        <v/>
+      </c>
+      <c r="J6" s="40">
+        <f>I6-H6</f>
+        <v/>
+      </c>
+      <c r="K6" s="42">
+        <f>IF(I6=0,"",F6/I6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>KASA</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="D7" s="40">
+        <f>C7-B7</f>
+        <v/>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="G7" s="40">
+        <f>F7-E7</f>
+        <v/>
+      </c>
+      <c r="H7" s="17">
+        <f>B7+E7</f>
+        <v/>
+      </c>
+      <c r="I7" s="17">
+        <f>C7+F7</f>
+        <v/>
+      </c>
+      <c r="J7" s="40">
+        <f>I7-H7</f>
+        <v/>
+      </c>
+      <c r="K7" s="42">
+        <f>IF(I7=0,"",F7/I7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>ÇOCUK</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="D8" s="40">
+        <f>C8-B8</f>
+        <v/>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" s="40">
+        <f>F8-E8</f>
+        <v/>
+      </c>
+      <c r="H8" s="17">
+        <f>B8+E8</f>
+        <v/>
+      </c>
+      <c r="I8" s="17">
+        <f>C8+F8</f>
+        <v/>
+      </c>
+      <c r="J8" s="40">
+        <f>I8-H8</f>
+        <v/>
+      </c>
+      <c r="K8" s="42">
+        <f>IF(I8=0,"",F8/I8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>OYUNCAK</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D9" s="40">
+        <f>C9-B9</f>
+        <v/>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="40">
+        <f>F9-E9</f>
+        <v/>
+      </c>
+      <c r="H9" s="17">
+        <f>B9+E9</f>
+        <v/>
+      </c>
+      <c r="I9" s="17">
+        <f>C9+F9</f>
+        <v/>
+      </c>
+      <c r="J9" s="40">
+        <f>I9-H9</f>
+        <v/>
+      </c>
+      <c r="K9" s="42">
+        <f>IF(I9=0,"",F9/I9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>AKADEMİ</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" s="40">
+        <f>C10-B10</f>
+        <v/>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="40">
+        <f>F10-E10</f>
+        <v/>
+      </c>
+      <c r="H10" s="17">
+        <f>B10+E10</f>
+        <v/>
+      </c>
+      <c r="I10" s="17">
+        <f>C10+F10</f>
+        <v/>
+      </c>
+      <c r="J10" s="40">
+        <f>I10-H10</f>
+        <v/>
+      </c>
+      <c r="K10" s="42">
+        <f>IF(I10=0,"",F10/I10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>MAĞAZA</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" s="40">
+        <f>C11-B11</f>
+        <v/>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="40">
+        <f>F11-E11</f>
+        <v/>
+      </c>
+      <c r="H11" s="17">
+        <f>B11+E11</f>
+        <v/>
+      </c>
+      <c r="I11" s="17">
+        <f>C11+F11</f>
+        <v/>
+      </c>
+      <c r="J11" s="40">
+        <f>I11-H11</f>
+        <v/>
+      </c>
+      <c r="K11" s="42">
+        <f>IF(I11=0,"",F11/I11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>MAL KABUL</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" s="40">
+        <f>C12-B12</f>
+        <v/>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="40">
+        <f>F12-E12</f>
+        <v/>
+      </c>
+      <c r="H12" s="17">
+        <f>B12+E12</f>
+        <v/>
+      </c>
+      <c r="I12" s="17">
+        <f>C12+F12</f>
+        <v/>
+      </c>
+      <c r="J12" s="40">
+        <f>I12-H12</f>
+        <v/>
+      </c>
+      <c r="K12" s="42">
+        <f>IF(I12=0,"",F12/I12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>İDARİ İŞLER</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" s="40">
+        <f>C13-B13</f>
+        <v/>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="40">
+        <f>F13-E13</f>
+        <v/>
+      </c>
+      <c r="H13" s="17">
+        <f>B13+E13</f>
+        <v/>
+      </c>
+      <c r="I13" s="17">
+        <f>C13+F13</f>
+        <v/>
+      </c>
+      <c r="J13" s="40">
+        <f>I13-H13</f>
+        <v/>
+      </c>
+      <c r="K13" s="42">
+        <f>IF(I13=0,"",F13/I13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>ETKİNLİK</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="40">
+        <f>C14-B14</f>
+        <v/>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="40">
+        <f>F14-E14</f>
+        <v/>
+      </c>
+      <c r="H14" s="17">
+        <f>B14+E14</f>
+        <v/>
+      </c>
+      <c r="I14" s="17">
+        <f>C14+F14</f>
+        <v/>
+      </c>
+      <c r="J14" s="40">
+        <f>I14-H14</f>
+        <v/>
+      </c>
+      <c r="K14" s="42">
+        <f>IF(I14=0,"",F14/I14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>ŞURA</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="40">
+        <f>C15-B15</f>
+        <v/>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="40">
+        <f>F15-E15</f>
+        <v/>
+      </c>
+      <c r="H15" s="17">
+        <f>B15+E15</f>
+        <v/>
+      </c>
+      <c r="I15" s="17">
+        <f>C15+F15</f>
+        <v/>
+      </c>
+      <c r="J15" s="40">
+        <f>I15-H15</f>
+        <v/>
+      </c>
+      <c r="K15" s="42">
+        <f>IF(I15=0,"",F15/I15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>ÖN MUHASEBE</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="40">
+        <f>C16-B16</f>
+        <v/>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="40">
+        <f>F16-E16</f>
+        <v/>
+      </c>
+      <c r="H16" s="17">
+        <f>B16+E16</f>
+        <v/>
+      </c>
+      <c r="I16" s="17">
+        <f>C16+F16</f>
+        <v/>
+      </c>
+      <c r="J16" s="40">
+        <f>I16-H16</f>
+        <v/>
+      </c>
+      <c r="K16" s="42">
+        <f>IF(I16=0,"",F16/I16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>MUHASEBE</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="40">
+        <f>C17-B17</f>
+        <v/>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="40">
+        <f>F17-E17</f>
+        <v/>
+      </c>
+      <c r="H17" s="17">
+        <f>B17+E17</f>
+        <v/>
+      </c>
+      <c r="I17" s="17">
+        <f>C17+F17</f>
+        <v/>
+      </c>
+      <c r="J17" s="40">
+        <f>I17-H17</f>
+        <v/>
+      </c>
+      <c r="K17" s="42">
+        <f>IF(I17=0,"",F17/I17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>BİLGİ İŞLEM</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="40">
+        <f>C18-B18</f>
+        <v/>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="40">
+        <f>F18-E18</f>
+        <v/>
+      </c>
+      <c r="H18" s="17">
+        <f>B18+E18</f>
+        <v/>
+      </c>
+      <c r="I18" s="17">
+        <f>C18+F18</f>
+        <v/>
+      </c>
+      <c r="J18" s="40">
+        <f>I18-H18</f>
+        <v/>
+      </c>
+      <c r="K18" s="42">
+        <f>IF(I18=0,"",F18/I18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>KIYAFET</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="40">
+        <f>C19-B19</f>
+        <v/>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" s="40">
+        <f>F19-E19</f>
+        <v/>
+      </c>
+      <c r="H19" s="17">
+        <f>B19+E19</f>
+        <v/>
+      </c>
+      <c r="I19" s="17">
+        <f>C19+F19</f>
+        <v/>
+      </c>
+      <c r="J19" s="40">
+        <f>I19-H19</f>
+        <v/>
+      </c>
+      <c r="K19" s="42">
+        <f>IF(I19=0,"",F19/I19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="36" t="inlineStr">
+        <is>
+          <t>TOPLAM</t>
+        </is>
+      </c>
+      <c r="B20" s="21">
+        <f>SUM(B4:B19)</f>
+        <v/>
+      </c>
+      <c r="C20" s="21">
+        <f>SUM(C4:C19)</f>
+        <v/>
+      </c>
+      <c r="D20" s="30">
+        <f>C20-B20</f>
+        <v/>
+      </c>
+      <c r="E20" s="21">
+        <f>SUM(E4:E19)</f>
+        <v/>
+      </c>
+      <c r="F20" s="21">
+        <f>SUM(F4:F19)</f>
+        <v/>
+      </c>
+      <c r="G20" s="41">
+        <f>F20-E20</f>
+        <v/>
+      </c>
+      <c r="H20" s="21">
+        <f>B20+E20</f>
+        <v/>
+      </c>
+      <c r="I20" s="21">
+        <f>C20+F20</f>
+        <v/>
+      </c>
+      <c r="J20" s="41">
+        <f>I20-H20</f>
+        <v/>
+      </c>
+      <c r="K20" s="43">
+        <f>IF(I20=0,"",F20/I20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="32" t="inlineStr">
+        <is>
+          <t>OKUNACAK NOKTA: yonetim (MAGAZA departmani) ve MAL KABUL BUYUMEDI — artis satis/kasa tarafinda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="32" t="inlineStr">
+        <is>
+          <t>Sezonluk payi yuksek bolumler (KIRTASIYE, YARDIMCI KITAP, KIYAFET) sezon yuku tasiyan reyonlar;</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   oradaki kisi artisi kalici kadro degil, Eylul sonunda tahliye edilir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="32" t="inlineStr">
+        <is>
+          <t>Bolum = Zirve 'Departman' alani (reyon). Bir kisi tek bolumde sayilir; toplam kapsam sayimiyla mutabik.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="32" t="inlineStr">
+        <is>
+          <t>Devir (turnover) bolum bazinda AYRI olculdu: en bozuk COCUK %179 · IDARI ISLER %183 · KASA %160;</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   MAGAZA (yonetim) %25 ve ayrilanin ortalama kidemi 4,7 yil -&gt; yonetim katmani stabil.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1621,139 +3471,139 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Kisi basi is — 4 yillik trend (uc POS magazasi, Ocak-Agustos kumulatif, Sinav haric)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Yil</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Kadrolu (31.08)</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Urun adedi (Oca-Agu)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Adet / kisi</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Onceki yila gore</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="16" t="n">
         <v>2023</v>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="17" t="n">
         <v>60</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="17" t="n">
         <v>2064284.43</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="44">
         <f>C4/B4</f>
         <v/>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="16" t="n">
         <v>2024</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="17" t="n">
         <v>91</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="17" t="n">
         <v>2296833.43</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="44">
         <f>C5/B5</f>
         <v/>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="19">
         <f>D5/D4-1</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="16" t="n">
         <v>2025</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="17" t="n">
         <v>96</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="17" t="n">
         <v>2752385.04</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="44">
         <f>C6/B6</f>
         <v/>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="19">
         <f>D6/D5-1</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="16" t="n">
         <v>2026</v>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="17" t="n">
         <v>111</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="17" t="n">
         <v>3607308.91</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="44">
         <f>C7/B7</f>
         <v/>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="19">
         <f>D7/D6-1</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>2024 ATLAMASI: kadrolu 60 -&gt; 91, adet yalniz +%11 -&gt; kisi basi is -%27. Kadro sismesi 2024'te oldu.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>AMA 2023 verimliligi 'norm' DEGIL: 2023'te FSM kasada 0 kisi, Ozluce kasada 1 kisi vardi (eksik kadroyla calisma).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>2024 -&gt; 2026: kisi basi is +%28,8 toparlanma. Bu yil kadro +15 kisi buyurken kisi basi is de artti.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="32" t="inlineStr">
         <is>
           <t>Bu sayfada kadro yalniz KADROLU (sezonluk haric) — yillar arasi sezonluk tahliye zamanlamasi kiyasi bozuyor.</t>
         </is>
@@ -1765,7 +3615,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1784,105 +3634,105 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>"Buyume kurumsaldan geldi" itirazinin cevabi — Ocak-Agustos, uc POS magazasi</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Kanal</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Adet 2025</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Adet 2026</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Adet Δ%</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Ciro 2025 (KDV dahil)</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>Ciro 2026 (KDV dahil)</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>Ciro Δ%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Magaza (perakende raf)</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="17" t="n">
         <v>2752385.04</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="17" t="n">
         <v>3607308.91</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="19">
         <f>C4/B4-1</f>
         <v/>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>316059798.2201176</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>489433287.7801854</v>
-      </c>
-      <c r="G4" s="5">
+      <c r="E4" s="17" t="n">
+        <v>316059798.2202811</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>489433287.7802867</v>
+      </c>
+      <c r="G4" s="19">
         <f>F4/E4-1</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Sinav Okullari (kurumsal)</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="17" t="n">
         <v>33584</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="17" t="n">
         <v>21693</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="19">
         <f>C5/B5-1</f>
         <v/>
       </c>
-      <c r="E5" s="4" t="n">
-        <v>136108071.4499996</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>105575646.11</v>
-      </c>
-      <c r="G5" s="5">
+      <c r="E5" s="17" t="n">
+        <v>136108071.4499999</v>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>105575646.1100004</v>
+      </c>
+      <c r="G5" s="19">
         <f>F5/E5-1</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
@@ -1895,7 +3745,7 @@
         <f>SUM(C4:C5)</f>
         <v/>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="37">
         <f>C6/B6-1</f>
         <v/>
       </c>
@@ -1907,27 +3757,27 @@
         <f>SUM(F4:F5)</f>
         <v/>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="37">
         <f>F6/E6-1</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>Sinav Okullari KUCULDU (adet -%35, ciro -%22). Buyumenin tamami magaza rafindan geldi.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Magaza tarafi kurumsal dususu de kapatti: toplam yine buyudu.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>Sinav = Kategori3 'Sinav Okullari' + 'Sinav Kiyafet'; ayni POS belgesi icinde geldigi icin AYIKLANMASI zorunlu.</t>
         </is>
@@ -1938,7 +3788,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1952,135 +3802,135 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Yontem ve kaynaklar</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="45" t="inlineStr">
         <is>
           <t>Baslik</t>
         </is>
       </c>
-      <c r="B3" s="27" t="inlineStr">
+      <c r="B3" s="46" t="inlineStr">
         <is>
           <t>Kişi başı iş hacmi — sezon 2026 vs 2025</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="45" t="inlineStr">
         <is>
           <t>Kesim tarihi</t>
         </is>
       </c>
-      <c r="B4" s="27" t="inlineStr">
+      <c r="B4" s="46" t="inlineStr">
         <is>
           <t>otomatik (veri sonu, okul-hizalı pencerede)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="45" t="inlineStr">
         <is>
           <t>Pencere</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="46" t="inlineStr">
         <is>
           <t>Okul açılışına hizalı: 2025 açılış 20250908, 2026 açılış 20260914; gün ofseti -69..-14 = her iki yıl 56 gün</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="45" t="inlineStr">
         <is>
           <t>Kadro kaynagi</t>
         </is>
       </c>
-      <c r="B6" s="27" t="inlineStr">
+      <c r="B6" s="46" t="inlineStr">
         <is>
           <t>Zirve BKM_GENEL.dbo.vw_PersonelDepartman — as-of Igt &lt;= T AND (Ict IS NULL OR Ict &gt;= T), sp_PersonelKarsilastirma_Ozet ile birebir</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="45" t="inlineStr">
         <is>
           <t>Is hacmi kaynagi</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="46" t="inlineStr">
         <is>
           <t>DerinSIS irs/irsAyr eTip=100 (POS satışı), Sınav Okulları/Kıyafet hariç, iade netlenmiş</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="45" t="inlineStr">
         <is>
           <t>Cekirdek SQL</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B8" s="46" t="inlineStr">
         <is>
           <t>sorgular/2026-09-02-kadro-vs-is-hacmi-savunma.sql (blok 11)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="47" t="inlineStr">
         <is>
           <t>Dikkat edilecekler</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="B11" s="28" t="inlineStr">
+      <c r="B11" s="48" t="inlineStr">
         <is>
           <t>• Ürün adedi enflasyondan bağımsız — kadro kıyasında birincil ölçüt. Ciro ikincil (fiyat endeksi +%19,8, Fisher, eşleşen ürün).</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="48" t="inlineStr">
         <is>
           <t>• Kıyas okul açılışına hizalı yapılır. Takvim tarihine göre kıyas 2026'da yapay düşüş gösterir: açılış 8 Eylül 2025'ten 14 Eylül 2026'ya, 6 gün kaydı.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="B13" s="28" t="inlineStr">
+      <c r="B13" s="48" t="inlineStr">
         <is>
           <t>• İş hacmi EncoreMerkez POS'tan DEĞİL DerinSIS'ten alınır: POS Temmuz 2025'te değişti (ENPOS → EncoreMerkez), EncoreMerkez'in 2025 tabanı eksik.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="B14" s="28" t="inlineStr">
+      <c r="B14" s="48" t="inlineStr">
         <is>
           <t>• Heykel ve Şura POS raporlamasında yok — mağaza sayfası üç POS mağazası (FSM · Özlüce · İst. Yolu). Beş mağaza kadro hareketi Özet'te ayrı.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="B15" s="28" t="inlineStr">
+      <c r="B15" s="48" t="inlineStr">
         <is>
           <t>• Kadro = o tarihte fiilen çalışan kişi (sezonluk + kadrolu). Kişi başı oranlar kasiyer değil TÜM mağaza kadrosu üzerinden.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="B16" s="28" t="inlineStr">
+      <c r="B16" s="48" t="inlineStr">
         <is>
           <t>• Fiş sayısı bu kaynakta yok: eTip 100 günlük özet belgedir (bir gün = bir belge).</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
-      <c r="B17" s="28" t="inlineStr">
+      <c r="B17" s="48" t="inlineStr">
         <is>
           <t>• Kıdem → verimlilik testi NEGATİF çıktı: aynı kasiyerin öğrenme eğrisi düz (220 → 256 → 242 fiş/gün), mağaza kıdem sıralaması verimlilikle uyuşmuyor. 'Tecrübeli 1 kişi = acemi 3 kişi' iddiası bu veriyle savunulamaz.</t>
         </is>

--- a/briefings/sezon-kadro-20260902/verimlilik-2026.xlsx
+++ b/briefings/sezon-kadro-20260902/verimlilik-2026.xlsx
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>66929723.56999852</v>
+        <v>66929723.56999952</v>
       </c>
       <c r="C9" s="17" t="n">
-        <v>114687785.58</v>
+        <v>114687785.5800005</v>
       </c>
       <c r="D9" s="18">
         <f>C9-B9</f>
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>71837429.11999343</v>
+        <v>71837429.11999629</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>122601380.8499947</v>
+        <v>122601380.8499953</v>
       </c>
       <c r="D10" s="18">
         <f>C10-B10</f>
@@ -2038,10 +2038,10 @@
         <v/>
       </c>
       <c r="M4" s="17" t="n">
-        <v>20455158.42999981</v>
+        <v>20455158.43000022</v>
       </c>
       <c r="N4" s="17" t="n">
-        <v>40444611.76999976</v>
+        <v>40444611.76999984</v>
       </c>
       <c r="O4" s="19">
         <f>N4/M4-1</f>
@@ -2111,10 +2111,10 @@
         <v/>
       </c>
       <c r="M5" s="17" t="n">
-        <v>28347121.58999882</v>
+        <v>28347121.58999878</v>
       </c>
       <c r="N5" s="17" t="n">
-        <v>44784483.14999945</v>
+        <v>44784483.14999981</v>
       </c>
       <c r="O5" s="19">
         <f>N5/M5-1</f>
@@ -2184,10 +2184,10 @@
         <v/>
       </c>
       <c r="M6" s="17" t="n">
-        <v>18127443.54999989</v>
+        <v>18127443.55000052</v>
       </c>
       <c r="N6" s="17" t="n">
-        <v>29458690.66000078</v>
+        <v>29458690.66000083</v>
       </c>
       <c r="O6" s="19">
         <f>N6/M6-1</f>
@@ -3670,24 +3670,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>Kategori büyümesi ve o kategoriye bakan bölümün kadro değişimi</t>
+          <t>Kategori büyümesi (okul-hizalı pencere VE Ocak-Ağustos) + o kategoriye bakan bölümün kadro değişimi</t>
         </is>
       </c>
     </row>
@@ -3734,6 +3738,26 @@
       </c>
       <c r="I3" s="13" t="inlineStr">
         <is>
+          <t>Oca-Ağu adet 2025</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t>Oca-Ağu adet 2026</t>
+        </is>
+      </c>
+      <c r="K3" s="13" t="inlineStr">
+        <is>
+          <t>Oca-Ağu adet Δ</t>
+        </is>
+      </c>
+      <c r="L3" s="13" t="inlineStr">
+        <is>
+          <t>Oca-Ağu ciro Δ</t>
+        </is>
+      </c>
+      <c r="M3" s="13" t="inlineStr">
+        <is>
           <t>Bölüm kadro Δ</t>
         </is>
       </c>
@@ -3760,16 +3784,29 @@
         <v/>
       </c>
       <c r="F4" s="34" t="n">
-        <v>18.50432497000309</v>
+        <v>18.50432497000304</v>
       </c>
       <c r="G4" s="34" t="n">
-        <v>32.38086690000132</v>
+        <v>32.38086690000116</v>
       </c>
       <c r="H4" s="44">
         <f>G4/F4-1</f>
         <v/>
       </c>
-      <c r="I4" s="45" t="n">
+      <c r="I4" s="17" t="n">
+        <v>1069622.3</v>
+      </c>
+      <c r="J4" s="17" t="n">
+        <v>1312972</v>
+      </c>
+      <c r="K4" s="19">
+        <f>IF(OR(I4="—",J4="—"),"",J4/I4-1)</f>
+        <v/>
+      </c>
+      <c r="L4" s="19" t="n">
+        <v>0.3747245332288727</v>
+      </c>
+      <c r="M4" s="45" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3795,16 +3832,29 @@
         <v/>
       </c>
       <c r="F5" s="34" t="n">
-        <v>10.02370844000002</v>
+        <v>10.02370844000004</v>
       </c>
       <c r="G5" s="34" t="n">
-        <v>15.50422909000003</v>
+        <v>15.50422909000002</v>
       </c>
       <c r="H5" s="44">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="I5" s="45" t="n">
+      <c r="I5" s="17" t="n">
+        <v>358316</v>
+      </c>
+      <c r="J5" s="17" t="n">
+        <v>440372</v>
+      </c>
+      <c r="K5" s="19">
+        <f>IF(OR(I5="—",J5="—"),"",J5/I5-1)</f>
+        <v/>
+      </c>
+      <c r="L5" s="19" t="n">
+        <v>0.5770282964719355</v>
+      </c>
+      <c r="M5" s="45" t="n">
         <v>-1</v>
       </c>
     </row>
@@ -3830,16 +3880,29 @@
         <v/>
       </c>
       <c r="F6" s="34" t="n">
-        <v>14.49106598999976</v>
+        <v>14.49106598999973</v>
       </c>
       <c r="G6" s="34" t="n">
-        <v>23.14058788999983</v>
+        <v>23.14058788999988</v>
       </c>
       <c r="H6" s="44">
         <f>G6/F6-1</f>
         <v/>
       </c>
-      <c r="I6" s="45" t="n">
+      <c r="I6" s="17" t="n">
+        <v>298822</v>
+      </c>
+      <c r="J6" s="17" t="n">
+        <v>348758</v>
+      </c>
+      <c r="K6" s="19">
+        <f>IF(OR(I6="—",J6="—"),"",J6/I6-1)</f>
+        <v/>
+      </c>
+      <c r="L6" s="19" t="n">
+        <v>0.4921459875658387</v>
+      </c>
+      <c r="M6" s="45" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3874,7 +3937,20 @@
         <f>G7/F7-1</f>
         <v/>
       </c>
-      <c r="I7" s="40" t="inlineStr">
+      <c r="I7" s="17" t="n">
+        <v>239529.74</v>
+      </c>
+      <c r="J7" s="17" t="n">
+        <v>320282.91</v>
+      </c>
+      <c r="K7" s="19">
+        <f>IF(OR(I7="—",J7="—"),"",J7/I7-1)</f>
+        <v/>
+      </c>
+      <c r="L7" s="19" t="n">
+        <v>1.797673394233622</v>
+      </c>
+      <c r="M7" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3902,7 +3978,7 @@
         <v/>
       </c>
       <c r="F8" s="34" t="n">
-        <v>11.13631268</v>
+        <v>11.13631267999999</v>
       </c>
       <c r="G8" s="34" t="n">
         <v>16.74884972000005</v>
@@ -3911,7 +3987,20 @@
         <f>G8/F8-1</f>
         <v/>
       </c>
-      <c r="I8" s="45" t="n">
+      <c r="I8" s="17" t="n">
+        <v>208095</v>
+      </c>
+      <c r="J8" s="17" t="n">
+        <v>302422</v>
+      </c>
+      <c r="K8" s="19">
+        <f>IF(OR(I8="—",J8="—"),"",J8/I8-1)</f>
+        <v/>
+      </c>
+      <c r="L8" s="19" t="n">
+        <v>0.6655996445022936</v>
+      </c>
+      <c r="M8" s="45" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3937,16 +4026,29 @@
         <v/>
       </c>
       <c r="F9" s="34" t="n">
-        <v>1.475290260000007</v>
+        <v>1.475290260000008</v>
       </c>
       <c r="G9" s="34" t="n">
-        <v>2.616103030000003</v>
+        <v>2.616103030000005</v>
       </c>
       <c r="H9" s="44">
         <f>G9/F9-1</f>
         <v/>
       </c>
-      <c r="I9" s="40" t="inlineStr">
+      <c r="I9" s="17" t="n">
+        <v>147554</v>
+      </c>
+      <c r="J9" s="17" t="n">
+        <v>295058</v>
+      </c>
+      <c r="K9" s="19">
+        <f>IF(OR(I9="—",J9="—"),"",J9/I9-1)</f>
+        <v/>
+      </c>
+      <c r="L9" s="19" t="n">
+        <v>1.258006023303505</v>
+      </c>
+      <c r="M9" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3974,16 +4076,29 @@
         <v/>
       </c>
       <c r="F10" s="34" t="n">
-        <v>11.66512253999997</v>
+        <v>11.66512254</v>
       </c>
       <c r="G10" s="34" t="n">
-        <v>22.35794457999995</v>
+        <v>22.35794457999996</v>
       </c>
       <c r="H10" s="44">
         <f>G10/F10-1</f>
         <v/>
       </c>
-      <c r="I10" s="45" t="n">
+      <c r="I10" s="17" t="n">
+        <v>218946</v>
+      </c>
+      <c r="J10" s="17" t="n">
+        <v>266564</v>
+      </c>
+      <c r="K10" s="19">
+        <f>IF(OR(I10="—",J10="—"),"",J10/I10-1)</f>
+        <v/>
+      </c>
+      <c r="L10" s="19" t="n">
+        <v>0.4621370345582259</v>
+      </c>
+      <c r="M10" s="45" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4009,16 +4124,29 @@
         <v/>
       </c>
       <c r="F11" s="34" t="n">
-        <v>0.69211733</v>
+        <v>0.6921173300000001</v>
       </c>
       <c r="G11" s="34" t="n">
-        <v>1.187673780000001</v>
+        <v>1.18767378</v>
       </c>
       <c r="H11" s="44">
         <f>G11/F11-1</f>
         <v/>
       </c>
-      <c r="I11" s="40" t="inlineStr">
+      <c r="I11" s="17" t="n">
+        <v>115494</v>
+      </c>
+      <c r="J11" s="17" t="n">
+        <v>138337</v>
+      </c>
+      <c r="K11" s="19">
+        <f>IF(OR(I11="—",J11="—"),"",J11/I11-1)</f>
+        <v/>
+      </c>
+      <c r="L11" s="19" t="n">
+        <v>0.4636366398909457</v>
+      </c>
+      <c r="M11" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4046,16 +4174,29 @@
         <v/>
       </c>
       <c r="F12" s="34" t="n">
-        <v>1.942142249999997</v>
+        <v>1.942142249999998</v>
       </c>
       <c r="G12" s="34" t="n">
-        <v>6.643827519999998</v>
+        <v>6.643827519999996</v>
       </c>
       <c r="H12" s="44">
         <f>G12/F12-1</f>
         <v/>
       </c>
-      <c r="I12" s="45" t="n">
+      <c r="I12" s="17" t="n">
+        <v>31118</v>
+      </c>
+      <c r="J12" s="17" t="n">
+        <v>78701</v>
+      </c>
+      <c r="K12" s="19">
+        <f>IF(OR(I12="—",J12="—"),"",J12/I12-1)</f>
+        <v/>
+      </c>
+      <c r="L12" s="19" t="n">
+        <v>1.769093453522586</v>
+      </c>
+      <c r="M12" s="45" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4084,13 +4225,26 @@
         <v>0.2846255699999998</v>
       </c>
       <c r="G13" s="34" t="n">
-        <v>0.4203621899999996</v>
+        <v>0.4203621899999997</v>
       </c>
       <c r="H13" s="44">
         <f>G13/F13-1</f>
         <v/>
       </c>
-      <c r="I13" s="40" t="inlineStr">
+      <c r="I13" s="17" t="n">
+        <v>19711</v>
+      </c>
+      <c r="J13" s="17" t="n">
+        <v>46133</v>
+      </c>
+      <c r="K13" s="19">
+        <f>IF(OR(I13="—",J13="—"),"",J13/I13-1)</f>
+        <v/>
+      </c>
+      <c r="L13" s="19" t="n">
+        <v>0.5224217348514231</v>
+      </c>
+      <c r="M13" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4121,13 +4275,26 @@
         <v>1.257655950000001</v>
       </c>
       <c r="G14" s="34" t="n">
-        <v>0.9961937399999999</v>
+        <v>0.9961937400000003</v>
       </c>
       <c r="H14" s="44">
         <f>G14/F14-1</f>
         <v/>
       </c>
-      <c r="I14" s="40" t="inlineStr">
+      <c r="I14" s="17" t="n">
+        <v>21609</v>
+      </c>
+      <c r="J14" s="17" t="n">
+        <v>24495</v>
+      </c>
+      <c r="K14" s="19">
+        <f>IF(OR(I14="—",J14="—"),"",J14/I14-1)</f>
+        <v/>
+      </c>
+      <c r="L14" s="19" t="n">
+        <v>0.4008427609025746</v>
+      </c>
+      <c r="M14" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4155,16 +4322,29 @@
         <v/>
       </c>
       <c r="F15" s="34" t="n">
-        <v>0.2656298399999998</v>
+        <v>0.2656298399999997</v>
       </c>
       <c r="G15" s="34" t="n">
-        <v>0.3784858199999995</v>
+        <v>0.3784858199999996</v>
       </c>
       <c r="H15" s="44">
         <f>G15/F15-1</f>
         <v/>
       </c>
-      <c r="I15" s="40" t="inlineStr">
+      <c r="I15" s="17" t="n">
+        <v>12790</v>
+      </c>
+      <c r="J15" s="17" t="n">
+        <v>13387</v>
+      </c>
+      <c r="K15" s="19">
+        <f>IF(OR(I15="—",J15="—"),"",J15/I15-1)</f>
+        <v/>
+      </c>
+      <c r="L15" s="19" t="n">
+        <v>0.4999858989104842</v>
+      </c>
+      <c r="M15" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4201,37 +4381,56 @@
         <f>G16/F16-1</f>
         <v/>
       </c>
+      <c r="I16" s="21">
+        <f>SUM(I4:I15)</f>
+        <v/>
+      </c>
+      <c r="J16" s="21">
+        <f>SUM(J4:J15)</f>
+        <v/>
+      </c>
+      <c r="K16" s="37">
+        <f>J16/I16-1</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="32" t="inlineStr">
         <is>
-          <t>ESLESME: kategori (urun) -&gt; o urune bakan reyon (bolum). Kadro Δ o BOLUMUN kadrolu degisimidir.</t>
+          <t>IKI PENCERE: sol blok OKUL-HIZALI pencere (sezon kiyasi), sag blok OCAK-AGUSTOS kumulatif (yil geneli).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="32" t="inlineStr">
         <is>
-          <t>OKUNACAK: kadro artisi en hizli buyuyen kategorilere gitti (Hazirlik Kitaplari, Kirtasiye, Akademi);</t>
+          <t>ESLESME: kategori (urun) -&gt; o urune bakan reyon (bolum). Kadro Δ o BOLUMUN kadrolu degisimidir.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">   en yavas buyuyen kategoride (Cocuk Kitabi) kadro AZALTILDI. Yani alim rastgele degil.</t>
+          <t>OKUNACAK: kadro artisi en hizli buyuyen kategorilere gitti (Hazirlik Kitaplari, Kirtasiye, Akademi);</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="32" t="inlineStr">
         <is>
-          <t>Kapsam: uc POS magazasi, okul-hizali pencere, Sinav haric, KDV dahil, iadeler dusulmus.</t>
+          <t xml:space="preserve">   en yavas buyuyen kategoride (Cocuk Kitabi) kadro AZALTILDI. Yani alim rastgele degil.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="32" t="inlineStr">
+        <is>
+          <t>Kapsam: uc POS magazasi, okul-hizali pencere, Sinav haric, KDV dahil, iadeler dusulmus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="32" t="inlineStr">
         <is>
           <t>Toplam satiri yalniz bu tablodaki kategorilerin toplami (adet&gt;=2000 esigi altindaki kuyruk haric).</t>
         </is>
@@ -4857,10 +5056,10 @@
         <v/>
       </c>
       <c r="E4" s="17" t="n">
-        <v>316059798.2202022</v>
+        <v>316059798.2202603</v>
       </c>
       <c r="F4" s="17" t="n">
-        <v>489433287.7802206</v>
+        <v>489433287.7801732</v>
       </c>
       <c r="G4" s="19">
         <f>F4/E4-1</f>
@@ -4884,10 +5083,10 @@
         <v/>
       </c>
       <c r="E5" s="17" t="n">
-        <v>136108071.4499999</v>
+        <v>136108071.4500001</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>105575646.1100001</v>
+        <v>105575646.1100003</v>
       </c>
       <c r="G5" s="19">
         <f>F5/E5-1</f>

--- a/briefings/sezon-kadro-20260902/verimlilik-2026.xlsx
+++ b/briefings/sezon-kadro-20260902/verimlilik-2026.xlsx
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>66929723.56999952</v>
+        <v>66929723.56999892</v>
       </c>
       <c r="C9" s="17" t="n">
-        <v>114687785.5800005</v>
+        <v>114687785.5800042</v>
       </c>
       <c r="D9" s="18">
         <f>C9-B9</f>
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>71837429.11999629</v>
+        <v>71837429.11999349</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>122601380.8499953</v>
+        <v>122601380.8499931</v>
       </c>
       <c r="D10" s="18">
         <f>C10-B10</f>
@@ -2038,10 +2038,10 @@
         <v/>
       </c>
       <c r="M4" s="17" t="n">
-        <v>20455158.43000022</v>
+        <v>20455158.42999977</v>
       </c>
       <c r="N4" s="17" t="n">
-        <v>40444611.76999984</v>
+        <v>40444611.77000166</v>
       </c>
       <c r="O4" s="19">
         <f>N4/M4-1</f>
@@ -2111,10 +2111,10 @@
         <v/>
       </c>
       <c r="M5" s="17" t="n">
-        <v>28347121.58999878</v>
+        <v>28347121.58999873</v>
       </c>
       <c r="N5" s="17" t="n">
-        <v>44784483.14999981</v>
+        <v>44784483.15000093</v>
       </c>
       <c r="O5" s="19">
         <f>N5/M5-1</f>
@@ -2184,10 +2184,10 @@
         <v/>
       </c>
       <c r="M6" s="17" t="n">
-        <v>18127443.55000052</v>
+        <v>18127443.55000043</v>
       </c>
       <c r="N6" s="17" t="n">
-        <v>29458690.66000083</v>
+        <v>29458690.66000156</v>
       </c>
       <c r="O6" s="19">
         <f>N6/M6-1</f>
@@ -3784,10 +3784,10 @@
         <v/>
       </c>
       <c r="F4" s="34" t="n">
-        <v>18.50432497000304</v>
+        <v>18.504324970003</v>
       </c>
       <c r="G4" s="34" t="n">
-        <v>32.38086690000116</v>
+        <v>32.38086690000143</v>
       </c>
       <c r="H4" s="44">
         <f>G4/F4-1</f>
@@ -3804,7 +3804,7 @@
         <v/>
       </c>
       <c r="L4" s="19" t="n">
-        <v>0.3747245332288727</v>
+        <v>0.3747245332283555</v>
       </c>
       <c r="M4" s="45" t="n">
         <v>3</v>
@@ -3832,7 +3832,7 @@
         <v/>
       </c>
       <c r="F5" s="34" t="n">
-        <v>10.02370844000004</v>
+        <v>10.02370844000002</v>
       </c>
       <c r="G5" s="34" t="n">
         <v>15.50422909000002</v>
@@ -3852,7 +3852,7 @@
         <v/>
       </c>
       <c r="L5" s="19" t="n">
-        <v>0.5770282964719355</v>
+        <v>0.5770282964719915</v>
       </c>
       <c r="M5" s="45" t="n">
         <v>-1</v>
@@ -3880,10 +3880,10 @@
         <v/>
       </c>
       <c r="F6" s="34" t="n">
-        <v>14.49106598999973</v>
+        <v>14.49106598999975</v>
       </c>
       <c r="G6" s="34" t="n">
-        <v>23.14058788999988</v>
+        <v>23.14058788999985</v>
       </c>
       <c r="H6" s="44">
         <f>G6/F6-1</f>
@@ -3900,7 +3900,7 @@
         <v/>
       </c>
       <c r="L6" s="19" t="n">
-        <v>0.4921459875658387</v>
+        <v>0.4921459875657994</v>
       </c>
       <c r="M6" s="45" t="n">
         <v>1</v>
@@ -3928,7 +3928,7 @@
         <v/>
       </c>
       <c r="F7" s="34" t="n">
-        <v>0.02740152000000001</v>
+        <v>0.02740152</v>
       </c>
       <c r="G7" s="34" t="n">
         <v>0.07535017999999999</v>
@@ -3981,7 +3981,7 @@
         <v>11.13631267999999</v>
       </c>
       <c r="G8" s="34" t="n">
-        <v>16.74884972000005</v>
+        <v>16.74884972000006</v>
       </c>
       <c r="H8" s="44">
         <f>G8/F8-1</f>
@@ -3998,7 +3998,7 @@
         <v/>
       </c>
       <c r="L8" s="19" t="n">
-        <v>0.6655996445022936</v>
+        <v>0.6655996445023169</v>
       </c>
       <c r="M8" s="45" t="n">
         <v>1</v>
@@ -4026,10 +4026,10 @@
         <v/>
       </c>
       <c r="F9" s="34" t="n">
-        <v>1.475290260000008</v>
+        <v>1.475290260000007</v>
       </c>
       <c r="G9" s="34" t="n">
-        <v>2.616103030000005</v>
+        <v>2.616103030000004</v>
       </c>
       <c r="H9" s="44">
         <f>G9/F9-1</f>
@@ -4046,7 +4046,7 @@
         <v/>
       </c>
       <c r="L9" s="19" t="n">
-        <v>1.258006023303505</v>
+        <v>1.258006023303477</v>
       </c>
       <c r="M9" s="40" t="inlineStr">
         <is>
@@ -4076,10 +4076,10 @@
         <v/>
       </c>
       <c r="F10" s="34" t="n">
-        <v>11.66512254</v>
+        <v>11.66512253999998</v>
       </c>
       <c r="G10" s="34" t="n">
-        <v>22.35794457999996</v>
+        <v>22.35794457999991</v>
       </c>
       <c r="H10" s="44">
         <f>G10/F10-1</f>
@@ -4096,7 +4096,7 @@
         <v/>
       </c>
       <c r="L10" s="19" t="n">
-        <v>0.4621370345582259</v>
+        <v>0.4621370345582261</v>
       </c>
       <c r="M10" s="45" t="n">
         <v>6</v>
@@ -4124,7 +4124,7 @@
         <v/>
       </c>
       <c r="F11" s="34" t="n">
-        <v>0.6921173300000001</v>
+        <v>0.69211733</v>
       </c>
       <c r="G11" s="34" t="n">
         <v>1.18767378</v>
@@ -4144,7 +4144,7 @@
         <v/>
       </c>
       <c r="L11" s="19" t="n">
-        <v>0.4636366398909457</v>
+        <v>0.4636366398909484</v>
       </c>
       <c r="M11" s="40" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>1.942142249999998</v>
       </c>
       <c r="G12" s="34" t="n">
-        <v>6.643827519999996</v>
+        <v>6.643827520000004</v>
       </c>
       <c r="H12" s="44">
         <f>G12/F12-1</f>
@@ -4194,7 +4194,7 @@
         <v/>
       </c>
       <c r="L12" s="19" t="n">
-        <v>1.769093453522586</v>
+        <v>1.769093453522581</v>
       </c>
       <c r="M12" s="45" t="n">
         <v>2</v>
@@ -4225,7 +4225,7 @@
         <v>0.2846255699999998</v>
       </c>
       <c r="G13" s="34" t="n">
-        <v>0.4203621899999997</v>
+        <v>0.4203621899999999</v>
       </c>
       <c r="H13" s="44">
         <f>G13/F13-1</f>
@@ -4242,7 +4242,7 @@
         <v/>
       </c>
       <c r="L13" s="19" t="n">
-        <v>0.5224217348514231</v>
+        <v>0.5224217348514237</v>
       </c>
       <c r="M13" s="40" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v/>
       </c>
       <c r="L14" s="19" t="n">
-        <v>0.4008427609025746</v>
+        <v>0.4008427609025784</v>
       </c>
       <c r="M14" s="40" t="inlineStr">
         <is>
@@ -4322,10 +4322,10 @@
         <v/>
       </c>
       <c r="F15" s="34" t="n">
-        <v>0.2656298399999997</v>
+        <v>0.2656298399999998</v>
       </c>
       <c r="G15" s="34" t="n">
-        <v>0.3784858199999996</v>
+        <v>0.3784858199999995</v>
       </c>
       <c r="H15" s="44">
         <f>G15/F15-1</f>
@@ -4342,7 +4342,7 @@
         <v/>
       </c>
       <c r="L15" s="19" t="n">
-        <v>0.4999858989104842</v>
+        <v>0.4999858989104868</v>
       </c>
       <c r="M15" s="40" t="inlineStr">
         <is>
@@ -5056,10 +5056,10 @@
         <v/>
       </c>
       <c r="E4" s="17" t="n">
-        <v>316059798.2202603</v>
+        <v>316059798.2203017</v>
       </c>
       <c r="F4" s="17" t="n">
-        <v>489433287.7801732</v>
+        <v>489433287.7802197</v>
       </c>
       <c r="G4" s="19">
         <f>F4/E4-1</f>
@@ -5083,10 +5083,10 @@
         <v/>
       </c>
       <c r="E5" s="17" t="n">
-        <v>136108071.4500001</v>
+        <v>136108071.4499997</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>105575646.1100003</v>
+        <v>105575646.1100001</v>
       </c>
       <c r="G5" s="19">
         <f>F5/E5-1</f>

--- a/briefings/sezon-kadro-20260902/verimlilik-2026.xlsx
+++ b/briefings/sezon-kadro-20260902/verimlilik-2026.xlsx
@@ -16,7 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aylik" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yillar" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Oca-Agu" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yontem" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Norm" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yontem" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -203,7 +204,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -277,6 +278,8 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -1180,6 +1183,266 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Norm kadro (11.08.2026, sezon dışı) ile gerçek kadrolu karşılaştırması</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Mağaza</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Norm (sezon dışı)</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Kadrolu 30.06</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>Norm farkı 30.06</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>Kadrolu 31.08</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>Norm farkı 31.08</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Sezonluk 31.08</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Toplam 31.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Özlüce</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="D4" s="53">
+        <f>C4-B4</f>
+        <v/>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="F4" s="53">
+        <f>E4-B4</f>
+        <v/>
+      </c>
+      <c r="G4" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="H4" s="17">
+        <f>E4+G4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Fsm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="D5" s="53">
+        <f>C5-B5</f>
+        <v/>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="F5" s="53">
+        <f>E5-B5</f>
+        <v/>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H5" s="17">
+        <f>E5+G5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>İst. Yolu</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="D6" s="53">
+        <f>C6-B6</f>
+        <v/>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="F6" s="53">
+        <f>E6-B6</f>
+        <v/>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="H6" s="17">
+        <f>E6+G6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Heykel</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="D7" s="53">
+        <f>C7-B7</f>
+        <v/>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="F7" s="53">
+        <f>E7-B7</f>
+        <v/>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H7" s="17">
+        <f>E7+G7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="36" t="inlineStr">
+        <is>
+          <t>TOPLAM</t>
+        </is>
+      </c>
+      <c r="B8" s="21">
+        <f>SUM(B4:B7)</f>
+        <v/>
+      </c>
+      <c r="C8" s="21">
+        <f>SUM(C4:C7)</f>
+        <v/>
+      </c>
+      <c r="D8" s="30">
+        <f>C8-B8</f>
+        <v/>
+      </c>
+      <c r="E8" s="21">
+        <f>SUM(E4:E7)</f>
+        <v/>
+      </c>
+      <c r="F8" s="30">
+        <f>E8-B8</f>
+        <v/>
+      </c>
+      <c r="G8" s="21">
+        <f>SUM(G4:G7)</f>
+        <v/>
+      </c>
+      <c r="H8" s="54">
+        <f>E8+G8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>NORM SEZON DISI kadroyu tanimlar -&gt; sezonluk personel norma DAHIL DEGIL; kiyas yalniz KADROLU ile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>Norm kaynagi: norm-kadro-20260811.json (11.08.2026). Yonetim parametresi, Zirve'den sorgulanmaz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>KAPSAM DISI: Şura norm tablosunda yok.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="32" t="inlineStr">
+        <is>
+          <t>Eksi fark = normun ALTINDA calisiliyor. Toplamda 31.08'de norm 145, gercek kadrolu 137.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1195,72 +1458,72 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="53" t="inlineStr">
+      <c r="A3" s="55" t="inlineStr">
         <is>
           <t>Baslik</t>
         </is>
       </c>
-      <c r="B3" s="54" t="inlineStr">
+      <c r="B3" s="56" t="inlineStr">
         <is>
           <t>Kişi başı iş hacmi — sezon 2026 vs 2025</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="53" t="inlineStr">
+      <c r="A4" s="55" t="inlineStr">
         <is>
           <t>Kesim tarihi</t>
         </is>
       </c>
-      <c r="B4" s="54" t="inlineStr">
+      <c r="B4" s="56" t="inlineStr">
         <is>
           <t>otomatik (veri sonu, okul-hizalı pencerede)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="53" t="inlineStr">
+      <c r="A5" s="55" t="inlineStr">
         <is>
           <t>Pencere</t>
         </is>
       </c>
-      <c r="B5" s="54" t="inlineStr">
+      <c r="B5" s="56" t="inlineStr">
         <is>
           <t>Okul açılışına hizalı — 2025: 01.07.2025 – 25.08.2025 · 2026: 07.07.2026 – 31.08.2026 (her iki yıl 56 gün; açılış 20250908 ve 20260914, gün ofseti -69..-14)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="53" t="inlineStr">
+      <c r="A6" s="55" t="inlineStr">
         <is>
           <t>Kadro kaynagi</t>
         </is>
       </c>
-      <c r="B6" s="54" t="inlineStr">
+      <c r="B6" s="56" t="inlineStr">
         <is>
           <t>Zirve BKM_GENEL.dbo.vw_PersonelDepartman — as-of Igt &lt;= T AND (Ict IS NULL OR Ict &gt;= T), sp_PersonelKarsilastirma_Ozet ile birebir</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="53" t="inlineStr">
+      <c r="A7" s="55" t="inlineStr">
         <is>
           <t>Is hacmi kaynagi</t>
         </is>
       </c>
-      <c r="B7" s="54" t="inlineStr">
+      <c r="B7" s="56" t="inlineStr">
         <is>
           <t>DerinSIS irs/irsAyr eTip=100 (POS satışı), Sınav Okulları/Kıyafet hariç, iade netlenmiş</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="53" t="inlineStr">
+      <c r="A8" s="55" t="inlineStr">
         <is>
           <t>Cekirdek SQL</t>
         </is>
       </c>
-      <c r="B8" s="54" t="inlineStr">
+      <c r="B8" s="56" t="inlineStr">
         <is>
           <t>sorgular/2026-09-02-kadro-vs-is-hacmi-savunma.sql (blok 11)</t>
         </is>
@@ -1274,49 +1537,49 @@
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="B11" s="55" t="inlineStr">
+      <c r="B11" s="57" t="inlineStr">
         <is>
           <t>• Ürün adedi enflasyondan bağımsız — kadro kıyasında birincil ölçüt. Ciro ikincil (fiyat endeksi +%19,8, Fisher, eşleşen ürün).</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="B12" s="55" t="inlineStr">
+      <c r="B12" s="57" t="inlineStr">
         <is>
           <t>• Kıyas okul açılışına hizalı yapılır. Takvim tarihine göre kıyas 2026'da yapay düşüş gösterir: açılış 8 Eylül 2025'ten 14 Eylül 2026'ya, 6 gün kaydı.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="B13" s="55" t="inlineStr">
+      <c r="B13" s="57" t="inlineStr">
         <is>
           <t>• İş hacmi EncoreMerkez POS'tan DEĞİL DerinSIS'ten alınır: POS Temmuz 2025'te değişti (ENPOS → EncoreMerkez), EncoreMerkez'in 2025 tabanı eksik.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="B14" s="55" t="inlineStr">
+      <c r="B14" s="57" t="inlineStr">
         <is>
           <t>• Heykel ve Şura POS raporlamasında yok — mağaza sayfası üç POS mağazası (FSM · Özlüce · İst. Yolu). Beş mağaza kadro hareketi Özet'te ayrı.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="B15" s="55" t="inlineStr">
+      <c r="B15" s="57" t="inlineStr">
         <is>
           <t>• Kadro = o tarihte fiilen çalışan kişi (sezonluk + kadrolu). Kişi başı oranlar kasiyer değil TÜM mağaza kadrosu üzerinden.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="B16" s="55" t="inlineStr">
+      <c r="B16" s="57" t="inlineStr">
         <is>
           <t>• Fiş sayısı bu kaynakta yok: eTip 100 günlük özet belgedir (bir gün = bir belge).</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
-      <c r="B17" s="55" t="inlineStr">
+      <c r="B17" s="57" t="inlineStr">
         <is>
           <t>• Kıdem → verimlilik testi NEGATİF çıktı: aynı kasiyerin öğrenme eğrisi düz (220 → 256 → 242 fiş/gün), mağaza kıdem sıralaması verimlilikle uyuşmuyor. 'Tecrübeli 1 kişi = acemi 3 kişi' iddiası bu veriyle savunulamaz.</t>
         </is>
@@ -1480,10 +1743,10 @@
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>66929723.56999892</v>
+        <v>66929723.56999967</v>
       </c>
       <c r="C9" s="17" t="n">
-        <v>114687785.5800042</v>
+        <v>114687785.5800021</v>
       </c>
       <c r="D9" s="18">
         <f>C9-B9</f>
@@ -1501,10 +1764,10 @@
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>71837429.11999349</v>
+        <v>71837429.11999415</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>122601380.8499931</v>
+        <v>122601380.8499947</v>
       </c>
       <c r="D10" s="18">
         <f>C10-B10</f>
@@ -2038,10 +2301,10 @@
         <v/>
       </c>
       <c r="M4" s="17" t="n">
-        <v>20455158.42999977</v>
+        <v>20455158.42999995</v>
       </c>
       <c r="N4" s="17" t="n">
-        <v>40444611.77000166</v>
+        <v>40444611.77000087</v>
       </c>
       <c r="O4" s="19">
         <f>N4/M4-1</f>
@@ -2111,10 +2374,10 @@
         <v/>
       </c>
       <c r="M5" s="17" t="n">
-        <v>28347121.58999873</v>
+        <v>28347121.58999935</v>
       </c>
       <c r="N5" s="17" t="n">
-        <v>44784483.15000093</v>
+        <v>44784483.15000021</v>
       </c>
       <c r="O5" s="19">
         <f>N5/M5-1</f>
@@ -2184,10 +2447,10 @@
         <v/>
       </c>
       <c r="M6" s="17" t="n">
-        <v>18127443.55000043</v>
+        <v>18127443.55000037</v>
       </c>
       <c r="N6" s="17" t="n">
-        <v>29458690.66000156</v>
+        <v>29458690.66000102</v>
       </c>
       <c r="O6" s="19">
         <f>N6/M6-1</f>
@@ -3784,10 +4047,10 @@
         <v/>
       </c>
       <c r="F4" s="34" t="n">
-        <v>18.504324970003</v>
+        <v>18.50432497000138</v>
       </c>
       <c r="G4" s="34" t="n">
-        <v>32.38086690000143</v>
+        <v>32.38086690000177</v>
       </c>
       <c r="H4" s="44">
         <f>G4/F4-1</f>
@@ -3804,7 +4067,7 @@
         <v/>
       </c>
       <c r="L4" s="19" t="n">
-        <v>0.3747245332283555</v>
+        <v>0.3747245332285545</v>
       </c>
       <c r="M4" s="45" t="n">
         <v>3</v>
@@ -3832,10 +4095,10 @@
         <v/>
       </c>
       <c r="F5" s="34" t="n">
-        <v>10.02370844000002</v>
+        <v>10.02370844</v>
       </c>
       <c r="G5" s="34" t="n">
-        <v>15.50422909000002</v>
+        <v>15.50422908999999</v>
       </c>
       <c r="H5" s="44">
         <f>G5/F5-1</f>
@@ -3852,7 +4115,7 @@
         <v/>
       </c>
       <c r="L5" s="19" t="n">
-        <v>0.5770282964719915</v>
+        <v>0.5770282964720117</v>
       </c>
       <c r="M5" s="45" t="n">
         <v>-1</v>
@@ -3883,7 +4146,7 @@
         <v>14.49106598999975</v>
       </c>
       <c r="G6" s="34" t="n">
-        <v>23.14058788999985</v>
+        <v>23.14058788999981</v>
       </c>
       <c r="H6" s="44">
         <f>G6/F6-1</f>
@@ -3900,7 +4163,7 @@
         <v/>
       </c>
       <c r="L6" s="19" t="n">
-        <v>0.4921459875657994</v>
+        <v>0.4921459875658309</v>
       </c>
       <c r="M6" s="45" t="n">
         <v>1</v>
@@ -3948,7 +4211,7 @@
         <v/>
       </c>
       <c r="L7" s="19" t="n">
-        <v>1.797673394233622</v>
+        <v>1.797673394233621</v>
       </c>
       <c r="M7" s="40" t="inlineStr">
         <is>
@@ -3978,10 +4241,10 @@
         <v/>
       </c>
       <c r="F8" s="34" t="n">
-        <v>11.13631267999999</v>
+        <v>11.13631268000001</v>
       </c>
       <c r="G8" s="34" t="n">
-        <v>16.74884972000006</v>
+        <v>16.74884972000007</v>
       </c>
       <c r="H8" s="44">
         <f>G8/F8-1</f>
@@ -3998,7 +4261,7 @@
         <v/>
       </c>
       <c r="L8" s="19" t="n">
-        <v>0.6655996445023169</v>
+        <v>0.66559964450229</v>
       </c>
       <c r="M8" s="45" t="n">
         <v>1</v>
@@ -4029,7 +4292,7 @@
         <v>1.475290260000007</v>
       </c>
       <c r="G9" s="34" t="n">
-        <v>2.616103030000004</v>
+        <v>2.616103030000003</v>
       </c>
       <c r="H9" s="44">
         <f>G9/F9-1</f>
@@ -4046,7 +4309,7 @@
         <v/>
       </c>
       <c r="L9" s="19" t="n">
-        <v>1.258006023303477</v>
+        <v>1.258006023303463</v>
       </c>
       <c r="M9" s="40" t="inlineStr">
         <is>
@@ -4079,7 +4342,7 @@
         <v>11.66512253999998</v>
       </c>
       <c r="G10" s="34" t="n">
-        <v>22.35794457999991</v>
+        <v>22.35794457999997</v>
       </c>
       <c r="H10" s="44">
         <f>G10/F10-1</f>
@@ -4096,7 +4359,7 @@
         <v/>
       </c>
       <c r="L10" s="19" t="n">
-        <v>0.4621370345582261</v>
+        <v>0.4621370345582292</v>
       </c>
       <c r="M10" s="45" t="n">
         <v>6</v>
@@ -4127,7 +4390,7 @@
         <v>0.69211733</v>
       </c>
       <c r="G11" s="34" t="n">
-        <v>1.18767378</v>
+        <v>1.187673780000001</v>
       </c>
       <c r="H11" s="44">
         <f>G11/F11-1</f>
@@ -4144,7 +4407,7 @@
         <v/>
       </c>
       <c r="L11" s="19" t="n">
-        <v>0.4636366398909484</v>
+        <v>0.4636366398909268</v>
       </c>
       <c r="M11" s="40" t="inlineStr">
         <is>
@@ -4177,7 +4440,7 @@
         <v>1.942142249999998</v>
       </c>
       <c r="G12" s="34" t="n">
-        <v>6.643827520000004</v>
+        <v>6.643827519999995</v>
       </c>
       <c r="H12" s="44">
         <f>G12/F12-1</f>
@@ -4194,7 +4457,7 @@
         <v/>
       </c>
       <c r="L12" s="19" t="n">
-        <v>1.769093453522581</v>
+        <v>1.769093453522592</v>
       </c>
       <c r="M12" s="45" t="n">
         <v>2</v>
@@ -4225,7 +4488,7 @@
         <v>0.2846255699999998</v>
       </c>
       <c r="G13" s="34" t="n">
-        <v>0.4203621899999999</v>
+        <v>0.4203621899999998</v>
       </c>
       <c r="H13" s="44">
         <f>G13/F13-1</f>
@@ -4275,7 +4538,7 @@
         <v>1.257655950000001</v>
       </c>
       <c r="G14" s="34" t="n">
-        <v>0.9961937400000003</v>
+        <v>0.9961937400000002</v>
       </c>
       <c r="H14" s="44">
         <f>G14/F14-1</f>
@@ -4292,7 +4555,7 @@
         <v/>
       </c>
       <c r="L14" s="19" t="n">
-        <v>0.4008427609025784</v>
+        <v>0.4008427609025702</v>
       </c>
       <c r="M14" s="40" t="inlineStr">
         <is>
@@ -4342,7 +4605,7 @@
         <v/>
       </c>
       <c r="L15" s="19" t="n">
-        <v>0.4999858989104868</v>
+        <v>0.4999858989104873</v>
       </c>
       <c r="M15" s="40" t="inlineStr">
         <is>
@@ -5056,10 +5319,10 @@
         <v/>
       </c>
       <c r="E4" s="17" t="n">
-        <v>316059798.2203017</v>
+        <v>316059798.220339</v>
       </c>
       <c r="F4" s="17" t="n">
-        <v>489433287.7802197</v>
+        <v>489433287.7802692</v>
       </c>
       <c r="G4" s="19">
         <f>F4/E4-1</f>
@@ -5083,10 +5346,10 @@
         <v/>
       </c>
       <c r="E5" s="17" t="n">
-        <v>136108071.4499997</v>
+        <v>136108071.4499994</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>105575646.1100001</v>
+        <v>105575646.1100002</v>
       </c>
       <c r="G5" s="19">
         <f>F5/E5-1</f>

--- a/briefings/sezon-kadro-20260902/verimlilik-2026.xlsx
+++ b/briefings/sezon-kadro-20260902/verimlilik-2026.xlsx
@@ -204,7 +204,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -279,7 +279,10 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -1183,17 +1186,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1211,37 +1216,47 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Norm (sezon dışı)</t>
+          <t>Norm kadrolu</t>
         </is>
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>Kadrolu 30.06</t>
+          <t>Kadrolu 31.08</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>Norm farkı 30.06</t>
+          <t>Kadrolu farkı</t>
         </is>
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t>Kadrolu 31.08</t>
+          <t>Norm sezonluk</t>
         </is>
       </c>
       <c r="F3" s="13" t="inlineStr">
         <is>
-          <t>Norm farkı 31.08</t>
+          <t>Sezonluk 31.08</t>
         </is>
       </c>
       <c r="G3" s="13" t="inlineStr">
         <is>
-          <t>Sezonluk 31.08</t>
+          <t>Sezonluk farkı</t>
         </is>
       </c>
       <c r="H3" s="13" t="inlineStr">
         <is>
-          <t>Toplam 31.08</t>
+          <t>NORM TOPLAM</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>GERÇEK TOPLAM</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t>TOPLAM FARK</t>
         </is>
       </c>
     </row>
@@ -1255,24 +1270,30 @@
         <v>45</v>
       </c>
       <c r="C4" s="17" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D4" s="53">
         <f>C4-B4</f>
         <v/>
       </c>
       <c r="E4" s="17" t="n">
-        <v>41</v>
-      </c>
-      <c r="F4" s="53">
-        <f>E4-B4</f>
-        <v/>
-      </c>
-      <c r="G4" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="F4" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="H4" s="17">
-        <f>E4+G4</f>
+      <c r="G4" s="53">
+        <f>F4-E4</f>
+        <v/>
+      </c>
+      <c r="H4" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="I4" s="17" t="n">
+        <v>54</v>
+      </c>
+      <c r="J4" s="30">
+        <f>I4-H4</f>
         <v/>
       </c>
     </row>
@@ -1286,24 +1307,30 @@
         <v>37</v>
       </c>
       <c r="C5" s="17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5" s="53">
         <f>C5-B5</f>
         <v/>
       </c>
       <c r="E5" s="17" t="n">
-        <v>34</v>
-      </c>
-      <c r="F5" s="53">
-        <f>E5-B5</f>
-        <v/>
-      </c>
-      <c r="G5" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="H5" s="17">
-        <f>E5+G5</f>
+      <c r="G5" s="53">
+        <f>F5-E5</f>
+        <v/>
+      </c>
+      <c r="H5" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="I5" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="J5" s="30">
+        <f>I5-H5</f>
         <v/>
       </c>
     </row>
@@ -1317,24 +1344,30 @@
         <v>33</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" s="53">
         <f>C6-B6</f>
         <v/>
       </c>
       <c r="E6" s="17" t="n">
-        <v>36</v>
-      </c>
-      <c r="F6" s="53">
-        <f>E6-B6</f>
-        <v/>
-      </c>
-      <c r="G6" s="17" t="n">
         <v>25</v>
       </c>
-      <c r="H6" s="17">
-        <f>E6+G6</f>
+      <c r="F6" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="G6" s="53">
+        <f>F6-E6</f>
+        <v/>
+      </c>
+      <c r="H6" s="17" t="n">
+        <v>58</v>
+      </c>
+      <c r="I6" s="17" t="n">
+        <v>61</v>
+      </c>
+      <c r="J6" s="30">
+        <f>I6-H6</f>
         <v/>
       </c>
     </row>
@@ -1348,24 +1381,30 @@
         <v>30</v>
       </c>
       <c r="C7" s="17" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D7" s="53">
         <f>C7-B7</f>
         <v/>
       </c>
       <c r="E7" s="17" t="n">
-        <v>26</v>
-      </c>
-      <c r="F7" s="53">
-        <f>E7-B7</f>
-        <v/>
-      </c>
-      <c r="G7" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="F7" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="H7" s="17">
-        <f>E7+G7</f>
+      <c r="G7" s="53">
+        <f>F7-E7</f>
+        <v/>
+      </c>
+      <c r="H7" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="I7" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="J7" s="30">
+        <f>I7-H7</f>
         <v/>
       </c>
     </row>
@@ -1391,42 +1430,460 @@
         <f>SUM(E4:E7)</f>
         <v/>
       </c>
-      <c r="F8" s="30">
-        <f>E8-B8</f>
-        <v/>
-      </c>
-      <c r="G8" s="21">
-        <f>SUM(G4:G7)</f>
-        <v/>
-      </c>
-      <c r="H8" s="54">
-        <f>E8+G8</f>
+      <c r="F8" s="21">
+        <f>SUM(F4:F7)</f>
+        <v/>
+      </c>
+      <c r="G8" s="30">
+        <f>F8-E8</f>
+        <v/>
+      </c>
+      <c r="H8" s="21">
+        <f>SUM(H4:H7)</f>
+        <v/>
+      </c>
+      <c r="I8" s="21">
+        <f>SUM(I4:I7)</f>
+        <v/>
+      </c>
+      <c r="J8" s="30">
+        <f>I8-H8</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="47" t="inlineStr">
+        <is>
+          <t>BÖLÜM BAZINDA NORM AÇIĞI</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="54" t="inlineStr">
+        <is>
+          <t>Bölüm</t>
+        </is>
+      </c>
+      <c r="B11" s="54" t="inlineStr">
+        <is>
+          <t>Norm</t>
+        </is>
+      </c>
+      <c r="C11" s="54" t="inlineStr">
+        <is>
+          <t>Kadrolu 31.08</t>
+        </is>
+      </c>
+      <c r="D11" s="54" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="E11" s="54" t="inlineStr">
+        <is>
+          <t>Fazla</t>
+        </is>
+      </c>
+      <c r="F11" s="54" t="inlineStr">
+        <is>
+          <t>Sezonluk 31.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Çocuk</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="D12" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>Kültür</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D13" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Mağaza</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="D14" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>İdari̇ İşler</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>Akademi̇</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="D16" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>Oyun Alani</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>Muhasebe</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>Kasa</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="D19" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>Mal Kabul</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C20" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>Yardimci Ki̇tap</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="C21" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" s="17" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>Kiyafet</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>Oyuncak</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C23" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>Kirtasi̇ye</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="17" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>Etki̇nli̇k</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="36" t="inlineStr">
+        <is>
+          <t>TOPLAM</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="n">
+        <v>145</v>
+      </c>
+      <c r="C26" s="21" t="n">
+        <v>137</v>
+      </c>
+      <c r="D26" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="E26" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="F26" s="21" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="32" t="inlineStr">
+        <is>
+          <t>⚠ BOLUM acigi (15) MAGAZA acigindan (11) BUYUK: magaza icinde bir bolumun fazlasi baska bolumun acigini maskeler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="32" t="inlineStr">
         <is>
           <t>NORM SEZON DISI kadroyu tanimlar -&gt; sezonluk personel norma DAHIL DEGIL; kiyas yalniz KADROLU ile.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="32" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="32" t="inlineStr">
         <is>
           <t>Norm kaynagi: norm-kadro-20260811.json (11.08.2026). Yonetim parametresi, Zirve'den sorgulanmaz.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="32" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="32" t="inlineStr">
         <is>
           <t>KAPSAM DISI: Şura norm tablosunda yok.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="32" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="32" t="inlineStr">
         <is>
           <t>Eksi fark = normun ALTINDA calisiliyor. Toplamda 31.08'de norm 145, gercek kadrolu 137.</t>
         </is>
@@ -1458,72 +1915,72 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="55" t="inlineStr">
+      <c r="A3" s="56" t="inlineStr">
         <is>
           <t>Baslik</t>
         </is>
       </c>
-      <c r="B3" s="56" t="inlineStr">
+      <c r="B3" s="57" t="inlineStr">
         <is>
           <t>Kişi başı iş hacmi — sezon 2026 vs 2025</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="55" t="inlineStr">
+      <c r="A4" s="56" t="inlineStr">
         <is>
           <t>Kesim tarihi</t>
         </is>
       </c>
-      <c r="B4" s="56" t="inlineStr">
+      <c r="B4" s="57" t="inlineStr">
         <is>
           <t>otomatik (veri sonu, okul-hizalı pencerede)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="55" t="inlineStr">
+      <c r="A5" s="56" t="inlineStr">
         <is>
           <t>Pencere</t>
         </is>
       </c>
-      <c r="B5" s="56" t="inlineStr">
+      <c r="B5" s="57" t="inlineStr">
         <is>
           <t>Okul açılışına hizalı — 2025: 01.07.2025 – 25.08.2025 · 2026: 07.07.2026 – 31.08.2026 (her iki yıl 56 gün; açılış 20250908 ve 20260914, gün ofseti -69..-14)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="55" t="inlineStr">
+      <c r="A6" s="56" t="inlineStr">
         <is>
           <t>Kadro kaynagi</t>
         </is>
       </c>
-      <c r="B6" s="56" t="inlineStr">
+      <c r="B6" s="57" t="inlineStr">
         <is>
           <t>Zirve BKM_GENEL.dbo.vw_PersonelDepartman — as-of Igt &lt;= T AND (Ict IS NULL OR Ict &gt;= T), sp_PersonelKarsilastirma_Ozet ile birebir</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="55" t="inlineStr">
+      <c r="A7" s="56" t="inlineStr">
         <is>
           <t>Is hacmi kaynagi</t>
         </is>
       </c>
-      <c r="B7" s="56" t="inlineStr">
+      <c r="B7" s="57" t="inlineStr">
         <is>
           <t>DerinSIS irs/irsAyr eTip=100 (POS satışı), Sınav Okulları/Kıyafet hariç, iade netlenmiş</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="55" t="inlineStr">
+      <c r="A8" s="56" t="inlineStr">
         <is>
           <t>Cekirdek SQL</t>
         </is>
       </c>
-      <c r="B8" s="56" t="inlineStr">
+      <c r="B8" s="57" t="inlineStr">
         <is>
           <t>sorgular/2026-09-02-kadro-vs-is-hacmi-savunma.sql (blok 11)</t>
         </is>
@@ -1537,49 +1994,49 @@
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="B11" s="57" t="inlineStr">
+      <c r="B11" s="58" t="inlineStr">
         <is>
           <t>• Ürün adedi enflasyondan bağımsız — kadro kıyasında birincil ölçüt. Ciro ikincil (fiyat endeksi +%19,8, Fisher, eşleşen ürün).</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="B12" s="57" t="inlineStr">
+      <c r="B12" s="58" t="inlineStr">
         <is>
           <t>• Kıyas okul açılışına hizalı yapılır. Takvim tarihine göre kıyas 2026'da yapay düşüş gösterir: açılış 8 Eylül 2025'ten 14 Eylül 2026'ya, 6 gün kaydı.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="B13" s="57" t="inlineStr">
+      <c r="B13" s="58" t="inlineStr">
         <is>
           <t>• İş hacmi EncoreMerkez POS'tan DEĞİL DerinSIS'ten alınır: POS Temmuz 2025'te değişti (ENPOS → EncoreMerkez), EncoreMerkez'in 2025 tabanı eksik.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="B14" s="57" t="inlineStr">
+      <c r="B14" s="58" t="inlineStr">
         <is>
           <t>• Heykel ve Şura POS raporlamasında yok — mağaza sayfası üç POS mağazası (FSM · Özlüce · İst. Yolu). Beş mağaza kadro hareketi Özet'te ayrı.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="B15" s="57" t="inlineStr">
+      <c r="B15" s="58" t="inlineStr">
         <is>
           <t>• Kadro = o tarihte fiilen çalışan kişi (sezonluk + kadrolu). Kişi başı oranlar kasiyer değil TÜM mağaza kadrosu üzerinden.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="B16" s="57" t="inlineStr">
+      <c r="B16" s="58" t="inlineStr">
         <is>
           <t>• Fiş sayısı bu kaynakta yok: eTip 100 günlük özet belgedir (bir gün = bir belge).</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
-      <c r="B17" s="57" t="inlineStr">
+      <c r="B17" s="58" t="inlineStr">
         <is>
           <t>• Kıdem → verimlilik testi NEGATİF çıktı: aynı kasiyerin öğrenme eğrisi düz (220 → 256 → 242 fiş/gün), mağaza kıdem sıralaması verimlilikle uyuşmuyor. 'Tecrübeli 1 kişi = acemi 3 kişi' iddiası bu veriyle savunulamaz.</t>
         </is>
@@ -1743,10 +2200,10 @@
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>66929723.56999967</v>
+        <v>66929723.56999896</v>
       </c>
       <c r="C9" s="17" t="n">
-        <v>114687785.5800021</v>
+        <v>114687785.5800008</v>
       </c>
       <c r="D9" s="18">
         <f>C9-B9</f>
@@ -1764,10 +2221,10 @@
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>71837429.11999415</v>
+        <v>71837429.11999592</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>122601380.8499947</v>
+        <v>122601380.8499953</v>
       </c>
       <c r="D10" s="18">
         <f>C10-B10</f>
@@ -2301,10 +2758,10 @@
         <v/>
       </c>
       <c r="M4" s="17" t="n">
-        <v>20455158.42999995</v>
+        <v>20455158.43000012</v>
       </c>
       <c r="N4" s="17" t="n">
-        <v>40444611.77000087</v>
+        <v>40444611.76999988</v>
       </c>
       <c r="O4" s="19">
         <f>N4/M4-1</f>
@@ -2374,10 +2831,10 @@
         <v/>
       </c>
       <c r="M5" s="17" t="n">
-        <v>28347121.58999935</v>
+        <v>28347121.58999896</v>
       </c>
       <c r="N5" s="17" t="n">
-        <v>44784483.15000021</v>
+        <v>44784483.15000012</v>
       </c>
       <c r="O5" s="19">
         <f>N5/M5-1</f>
@@ -2447,10 +2904,10 @@
         <v/>
       </c>
       <c r="M6" s="17" t="n">
-        <v>18127443.55000037</v>
+        <v>18127443.54999987</v>
       </c>
       <c r="N6" s="17" t="n">
-        <v>29458690.66000102</v>
+        <v>29458690.66000081</v>
       </c>
       <c r="O6" s="19">
         <f>N6/M6-1</f>
@@ -4047,10 +4504,10 @@
         <v/>
       </c>
       <c r="F4" s="34" t="n">
-        <v>18.50432497000138</v>
+        <v>18.5043249700003</v>
       </c>
       <c r="G4" s="34" t="n">
-        <v>32.38086690000177</v>
+        <v>32.38086690000193</v>
       </c>
       <c r="H4" s="44">
         <f>G4/F4-1</f>
@@ -4067,7 +4524,7 @@
         <v/>
       </c>
       <c r="L4" s="19" t="n">
-        <v>0.3747245332285545</v>
+        <v>0.3747245332281872</v>
       </c>
       <c r="M4" s="45" t="n">
         <v>3</v>
@@ -4095,10 +4552,10 @@
         <v/>
       </c>
       <c r="F5" s="34" t="n">
-        <v>10.02370844</v>
+        <v>10.02370844000004</v>
       </c>
       <c r="G5" s="34" t="n">
-        <v>15.50422908999999</v>
+        <v>15.50422908999997</v>
       </c>
       <c r="H5" s="44">
         <f>G5/F5-1</f>
@@ -4115,7 +4572,7 @@
         <v/>
       </c>
       <c r="L5" s="19" t="n">
-        <v>0.5770282964720117</v>
+        <v>0.5770282964719697</v>
       </c>
       <c r="M5" s="45" t="n">
         <v>-1</v>
@@ -4143,10 +4600,10 @@
         <v/>
       </c>
       <c r="F6" s="34" t="n">
-        <v>14.49106598999975</v>
+        <v>14.49106598999981</v>
       </c>
       <c r="G6" s="34" t="n">
-        <v>23.14058788999981</v>
+        <v>23.1405878899998</v>
       </c>
       <c r="H6" s="44">
         <f>G6/F6-1</f>
@@ -4163,7 +4620,7 @@
         <v/>
       </c>
       <c r="L6" s="19" t="n">
-        <v>0.4921459875658309</v>
+        <v>0.4921459875657817</v>
       </c>
       <c r="M6" s="45" t="n">
         <v>1</v>
@@ -4241,10 +4698,10 @@
         <v/>
       </c>
       <c r="F8" s="34" t="n">
-        <v>11.13631268000001</v>
+        <v>11.13631267999999</v>
       </c>
       <c r="G8" s="34" t="n">
-        <v>16.74884972000007</v>
+        <v>16.74884972000006</v>
       </c>
       <c r="H8" s="44">
         <f>G8/F8-1</f>
@@ -4261,7 +4718,7 @@
         <v/>
       </c>
       <c r="L8" s="19" t="n">
-        <v>0.66559964450229</v>
+        <v>0.6655996445022265</v>
       </c>
       <c r="M8" s="45" t="n">
         <v>1</v>
@@ -4292,7 +4749,7 @@
         <v>1.475290260000007</v>
       </c>
       <c r="G9" s="34" t="n">
-        <v>2.616103030000003</v>
+        <v>2.616103030000001</v>
       </c>
       <c r="H9" s="44">
         <f>G9/F9-1</f>
@@ -4309,7 +4766,7 @@
         <v/>
       </c>
       <c r="L9" s="19" t="n">
-        <v>1.258006023303463</v>
+        <v>1.258006023303461</v>
       </c>
       <c r="M9" s="40" t="inlineStr">
         <is>
@@ -4339,10 +4796,10 @@
         <v/>
       </c>
       <c r="F10" s="34" t="n">
-        <v>11.66512253999998</v>
+        <v>11.66512253999999</v>
       </c>
       <c r="G10" s="34" t="n">
-        <v>22.35794457999997</v>
+        <v>22.35794457999999</v>
       </c>
       <c r="H10" s="44">
         <f>G10/F10-1</f>
@@ -4359,7 +4816,7 @@
         <v/>
       </c>
       <c r="L10" s="19" t="n">
-        <v>0.4621370345582292</v>
+        <v>0.4621370345582101</v>
       </c>
       <c r="M10" s="45" t="n">
         <v>6</v>
@@ -4387,10 +4844,10 @@
         <v/>
       </c>
       <c r="F11" s="34" t="n">
-        <v>0.69211733</v>
+        <v>0.6921173299999999</v>
       </c>
       <c r="G11" s="34" t="n">
-        <v>1.187673780000001</v>
+        <v>1.18767378</v>
       </c>
       <c r="H11" s="44">
         <f>G11/F11-1</f>
@@ -4407,7 +4864,7 @@
         <v/>
       </c>
       <c r="L11" s="19" t="n">
-        <v>0.4636366398909268</v>
+        <v>0.4636366398909451</v>
       </c>
       <c r="M11" s="40" t="inlineStr">
         <is>
@@ -4437,10 +4894,10 @@
         <v/>
       </c>
       <c r="F12" s="34" t="n">
-        <v>1.942142249999998</v>
+        <v>1.942142249999999</v>
       </c>
       <c r="G12" s="34" t="n">
-        <v>6.643827519999995</v>
+        <v>6.643827519999999</v>
       </c>
       <c r="H12" s="44">
         <f>G12/F12-1</f>
@@ -4457,7 +4914,7 @@
         <v/>
       </c>
       <c r="L12" s="19" t="n">
-        <v>1.769093453522592</v>
+        <v>1.76909345352258</v>
       </c>
       <c r="M12" s="45" t="n">
         <v>2</v>
@@ -4485,10 +4942,10 @@
         <v/>
       </c>
       <c r="F13" s="34" t="n">
-        <v>0.2846255699999998</v>
+        <v>0.28462557</v>
       </c>
       <c r="G13" s="34" t="n">
-        <v>0.4203621899999998</v>
+        <v>0.4203621899999997</v>
       </c>
       <c r="H13" s="44">
         <f>G13/F13-1</f>
@@ -4505,7 +4962,7 @@
         <v/>
       </c>
       <c r="L13" s="19" t="n">
-        <v>0.5224217348514237</v>
+        <v>0.522421734851424</v>
       </c>
       <c r="M13" s="40" t="inlineStr">
         <is>
@@ -4538,7 +4995,7 @@
         <v>1.257655950000001</v>
       </c>
       <c r="G14" s="34" t="n">
-        <v>0.9961937400000002</v>
+        <v>0.9961937400000003</v>
       </c>
       <c r="H14" s="44">
         <f>G14/F14-1</f>
@@ -4555,7 +5012,7 @@
         <v/>
       </c>
       <c r="L14" s="19" t="n">
-        <v>0.4008427609025702</v>
+        <v>0.4008427609025618</v>
       </c>
       <c r="M14" s="40" t="inlineStr">
         <is>
@@ -4585,10 +5042,10 @@
         <v/>
       </c>
       <c r="F15" s="34" t="n">
-        <v>0.2656298399999998</v>
+        <v>0.2656298399999997</v>
       </c>
       <c r="G15" s="34" t="n">
-        <v>0.3784858199999995</v>
+        <v>0.3784858199999996</v>
       </c>
       <c r="H15" s="44">
         <f>G15/F15-1</f>
@@ -4605,7 +5062,7 @@
         <v/>
       </c>
       <c r="L15" s="19" t="n">
-        <v>0.4999858989104873</v>
+        <v>0.4999858989104884</v>
       </c>
       <c r="M15" s="40" t="inlineStr">
         <is>
@@ -5319,10 +5776,10 @@
         <v/>
       </c>
       <c r="E4" s="17" t="n">
-        <v>316059798.220339</v>
+        <v>316059798.2201345</v>
       </c>
       <c r="F4" s="17" t="n">
-        <v>489433287.7802692</v>
+        <v>489433287.7802142</v>
       </c>
       <c r="G4" s="19">
         <f>F4/E4-1</f>
@@ -5346,10 +5803,10 @@
         <v/>
       </c>
       <c r="E5" s="17" t="n">
-        <v>136108071.4499994</v>
+        <v>136108071.4499997</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>105575646.1100002</v>
+        <v>105575646.11</v>
       </c>
       <c r="G5" s="19">
         <f>F5/E5-1</f>

--- a/briefings/sezon-kadro-20260902/verimlilik-2026.xlsx
+++ b/briefings/sezon-kadro-20260902/verimlilik-2026.xlsx
@@ -1589,14 +1589,14 @@
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>Akademi̇</t>
+          <t>Kasa</t>
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C16" s="17" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D16" s="55" t="n">
         <v>1</v>
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="F16" s="17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>Oyun Alani</t>
+          <t>Muhasebe</t>
         </is>
       </c>
       <c r="B17" s="17" t="n">
@@ -1637,7 +1637,7 @@
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>Muhasebe</t>
+          <t>Oyun Alani</t>
         </is>
       </c>
       <c r="B18" s="17" t="n">
@@ -1661,14 +1661,14 @@
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>Kasa</t>
+          <t>Akademi̇</t>
         </is>
       </c>
       <c r="B19" s="17" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C19" s="17" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D19" s="55" t="n">
         <v>1</v>
@@ -1679,20 +1679,20 @@
         </is>
       </c>
       <c r="F19" s="17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>Mal Kabul</t>
+          <t>Kiyafet</t>
         </is>
       </c>
       <c r="B20" s="17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C20" s="17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
@@ -1705,20 +1705,20 @@
         </is>
       </c>
       <c r="F20" s="17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Yardimci Ki̇tap</t>
+          <t>Kirtasi̇ye</t>
         </is>
       </c>
       <c r="B21" s="17" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C21" s="17" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
@@ -1726,23 +1726,23 @@
         </is>
       </c>
       <c r="E21" s="17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F21" s="17" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>Kiyafet</t>
+          <t>Mal Kabul</t>
         </is>
       </c>
       <c r="B22" s="17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C22" s="17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
@@ -1755,46 +1755,44 @@
         </is>
       </c>
       <c r="F22" s="17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>Oyuncak</t>
+          <t>Yardimci Ki̇tap</t>
         </is>
       </c>
       <c r="B23" s="17" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C23" s="17" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D23" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E23" s="17" t="n">
+        <v>3</v>
       </c>
       <c r="F23" s="17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>Kirtasi̇ye</t>
+          <t>Etki̇nli̇k</t>
         </is>
       </c>
       <c r="B24" s="17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C24" s="17" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
@@ -1802,31 +1800,33 @@
         </is>
       </c>
       <c r="E24" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F24" s="17" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>Etki̇nli̇k</t>
+          <t>Oyuncak</t>
         </is>
       </c>
       <c r="B25" s="17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C25" s="17" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D25" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E25" s="17" t="n">
-        <v>3</v>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F25" s="17" t="n">
         <v>0</v>
@@ -2200,10 +2200,10 @@
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>66929723.56999896</v>
+        <v>66929723.56999852</v>
       </c>
       <c r="C9" s="17" t="n">
-        <v>114687785.5800008</v>
+        <v>114687785.58</v>
       </c>
       <c r="D9" s="18">
         <f>C9-B9</f>
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>71837429.11999592</v>
+        <v>71837429.11999343</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>122601380.8499953</v>
+        <v>122601380.8499947</v>
       </c>
       <c r="D10" s="18">
         <f>C10-B10</f>
@@ -2758,10 +2758,10 @@
         <v/>
       </c>
       <c r="M4" s="17" t="n">
-        <v>20455158.43000012</v>
+        <v>20455158.42999981</v>
       </c>
       <c r="N4" s="17" t="n">
-        <v>40444611.76999988</v>
+        <v>40444611.76999976</v>
       </c>
       <c r="O4" s="19">
         <f>N4/M4-1</f>
@@ -2831,10 +2831,10 @@
         <v/>
       </c>
       <c r="M5" s="17" t="n">
-        <v>28347121.58999896</v>
+        <v>28347121.58999882</v>
       </c>
       <c r="N5" s="17" t="n">
-        <v>44784483.15000012</v>
+        <v>44784483.14999945</v>
       </c>
       <c r="O5" s="19">
         <f>N5/M5-1</f>
@@ -2904,10 +2904,10 @@
         <v/>
       </c>
       <c r="M6" s="17" t="n">
-        <v>18127443.54999987</v>
+        <v>18127443.54999989</v>
       </c>
       <c r="N6" s="17" t="n">
-        <v>29458690.66000081</v>
+        <v>29458690.66000078</v>
       </c>
       <c r="O6" s="19">
         <f>N6/M6-1</f>
@@ -4504,10 +4504,10 @@
         <v/>
       </c>
       <c r="F4" s="34" t="n">
-        <v>18.5043249700003</v>
+        <v>18.5043249700029</v>
       </c>
       <c r="G4" s="34" t="n">
-        <v>32.38086690000193</v>
+        <v>32.38086690000142</v>
       </c>
       <c r="H4" s="44">
         <f>G4/F4-1</f>
@@ -4524,7 +4524,7 @@
         <v/>
       </c>
       <c r="L4" s="19" t="n">
-        <v>0.3747245332281872</v>
+        <v>0.3747245332289066</v>
       </c>
       <c r="M4" s="45" t="n">
         <v>3</v>
@@ -4552,10 +4552,10 @@
         <v/>
       </c>
       <c r="F5" s="34" t="n">
-        <v>10.02370844000004</v>
+        <v>10.02370844000001</v>
       </c>
       <c r="G5" s="34" t="n">
-        <v>15.50422908999997</v>
+        <v>15.50422909000001</v>
       </c>
       <c r="H5" s="44">
         <f>G5/F5-1</f>
@@ -4572,7 +4572,7 @@
         <v/>
       </c>
       <c r="L5" s="19" t="n">
-        <v>0.5770282964719697</v>
+        <v>0.5770282964720019</v>
       </c>
       <c r="M5" s="45" t="n">
         <v>-1</v>
@@ -4600,10 +4600,10 @@
         <v/>
       </c>
       <c r="F6" s="34" t="n">
-        <v>14.49106598999981</v>
+        <v>14.49106598999973</v>
       </c>
       <c r="G6" s="34" t="n">
-        <v>23.1405878899998</v>
+        <v>23.14058788999986</v>
       </c>
       <c r="H6" s="44">
         <f>G6/F6-1</f>
@@ -4620,7 +4620,7 @@
         <v/>
       </c>
       <c r="L6" s="19" t="n">
-        <v>0.4921459875657817</v>
+        <v>0.4921459875658136</v>
       </c>
       <c r="M6" s="45" t="n">
         <v>1</v>
@@ -4648,7 +4648,7 @@
         <v/>
       </c>
       <c r="F7" s="34" t="n">
-        <v>0.02740152</v>
+        <v>0.02740152000000001</v>
       </c>
       <c r="G7" s="34" t="n">
         <v>0.07535017999999999</v>
@@ -4698,7 +4698,7 @@
         <v/>
       </c>
       <c r="F8" s="34" t="n">
-        <v>11.13631267999999</v>
+        <v>11.13631268</v>
       </c>
       <c r="G8" s="34" t="n">
         <v>16.74884972000006</v>
@@ -4718,7 +4718,7 @@
         <v/>
       </c>
       <c r="L8" s="19" t="n">
-        <v>0.6655996445022265</v>
+        <v>0.6655996445023109</v>
       </c>
       <c r="M8" s="45" t="n">
         <v>1</v>
@@ -4746,10 +4746,10 @@
         <v/>
       </c>
       <c r="F9" s="34" t="n">
-        <v>1.475290260000007</v>
+        <v>1.475290260000008</v>
       </c>
       <c r="G9" s="34" t="n">
-        <v>2.616103030000001</v>
+        <v>2.616103030000003</v>
       </c>
       <c r="H9" s="44">
         <f>G9/F9-1</f>
@@ -4766,7 +4766,7 @@
         <v/>
       </c>
       <c r="L9" s="19" t="n">
-        <v>1.258006023303461</v>
+        <v>1.258006023303491</v>
       </c>
       <c r="M9" s="40" t="inlineStr">
         <is>
@@ -4796,10 +4796,10 @@
         <v/>
       </c>
       <c r="F10" s="34" t="n">
-        <v>11.66512253999999</v>
+        <v>11.66512254</v>
       </c>
       <c r="G10" s="34" t="n">
-        <v>22.35794457999999</v>
+        <v>22.35794457999994</v>
       </c>
       <c r="H10" s="44">
         <f>G10/F10-1</f>
@@ -4816,7 +4816,7 @@
         <v/>
       </c>
       <c r="L10" s="19" t="n">
-        <v>0.4621370345582101</v>
+        <v>0.4621370345582292</v>
       </c>
       <c r="M10" s="45" t="n">
         <v>6</v>
@@ -4844,10 +4844,10 @@
         <v/>
       </c>
       <c r="F11" s="34" t="n">
-        <v>0.6921173299999999</v>
+        <v>0.69211733</v>
       </c>
       <c r="G11" s="34" t="n">
-        <v>1.18767378</v>
+        <v>1.187673780000001</v>
       </c>
       <c r="H11" s="44">
         <f>G11/F11-1</f>
@@ -4864,7 +4864,7 @@
         <v/>
       </c>
       <c r="L11" s="19" t="n">
-        <v>0.4636366398909451</v>
+        <v>0.4636366398909368</v>
       </c>
       <c r="M11" s="40" t="inlineStr">
         <is>
@@ -4894,10 +4894,10 @@
         <v/>
       </c>
       <c r="F12" s="34" t="n">
-        <v>1.942142249999999</v>
+        <v>1.942142249999998</v>
       </c>
       <c r="G12" s="34" t="n">
-        <v>6.643827519999999</v>
+        <v>6.643827519999992</v>
       </c>
       <c r="H12" s="44">
         <f>G12/F12-1</f>
@@ -4914,7 +4914,7 @@
         <v/>
       </c>
       <c r="L12" s="19" t="n">
-        <v>1.76909345352258</v>
+        <v>1.769093453522593</v>
       </c>
       <c r="M12" s="45" t="n">
         <v>2</v>
@@ -4942,7 +4942,7 @@
         <v/>
       </c>
       <c r="F13" s="34" t="n">
-        <v>0.28462557</v>
+        <v>0.2846255699999998</v>
       </c>
       <c r="G13" s="34" t="n">
         <v>0.4203621899999997</v>
@@ -4962,7 +4962,7 @@
         <v/>
       </c>
       <c r="L13" s="19" t="n">
-        <v>0.522421734851424</v>
+        <v>0.5224217348514228</v>
       </c>
       <c r="M13" s="40" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>1.257655950000001</v>
       </c>
       <c r="G14" s="34" t="n">
-        <v>0.9961937400000003</v>
+        <v>0.9961937400000004</v>
       </c>
       <c r="H14" s="44">
         <f>G14/F14-1</f>
@@ -5012,7 +5012,7 @@
         <v/>
       </c>
       <c r="L14" s="19" t="n">
-        <v>0.4008427609025618</v>
+        <v>0.4008427609025746</v>
       </c>
       <c r="M14" s="40" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>0.2656298399999997</v>
       </c>
       <c r="G15" s="34" t="n">
-        <v>0.3784858199999996</v>
+        <v>0.3784858199999995</v>
       </c>
       <c r="H15" s="44">
         <f>G15/F15-1</f>
@@ -5062,7 +5062,7 @@
         <v/>
       </c>
       <c r="L15" s="19" t="n">
-        <v>0.4999858989104884</v>
+        <v>0.4999858989104862</v>
       </c>
       <c r="M15" s="40" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>32.14602051000339</v>
       </c>
       <c r="F5" s="34" t="n">
-        <v>55.81932909000083</v>
+        <v>55.81932909000084</v>
       </c>
       <c r="G5" s="44">
         <f>F5/E5-1</f>
@@ -5776,10 +5776,10 @@
         <v/>
       </c>
       <c r="E4" s="17" t="n">
-        <v>316059798.2201345</v>
+        <v>316059798.2201092</v>
       </c>
       <c r="F4" s="17" t="n">
-        <v>489433287.7802142</v>
+        <v>489433287.7801834</v>
       </c>
       <c r="G4" s="19">
         <f>F4/E4-1</f>
@@ -5806,7 +5806,7 @@
         <v>136108071.4499997</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>105575646.11</v>
+        <v>105575646.1100001</v>
       </c>
       <c r="G5" s="19">
         <f>F5/E5-1</f>

--- a/briefings/sezon-kadro-20260902/verimlilik-2026.xlsx
+++ b/briefings/sezon-kadro-20260902/verimlilik-2026.xlsx
@@ -1517,14 +1517,14 @@
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Kültür</t>
+          <t>Mağaza</t>
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C13" s="17" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D13" s="55" t="n">
         <v>2</v>
@@ -1535,20 +1535,20 @@
         </is>
       </c>
       <c r="F13" s="17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Mağaza</t>
+          <t>İdari̇ İşler</t>
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C14" s="17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D14" s="55" t="n">
         <v>2</v>
@@ -1565,14 +1565,14 @@
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>İdari̇ İşler</t>
+          <t>Kültür</t>
         </is>
       </c>
       <c r="B15" s="17" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C15" s="17" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D15" s="55" t="n">
         <v>2</v>
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="F15" s="17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1637,14 +1637,14 @@
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>Oyun Alani</t>
+          <t>Akademi̇</t>
         </is>
       </c>
       <c r="B18" s="17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C18" s="17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D18" s="55" t="n">
         <v>1</v>
@@ -1661,14 +1661,14 @@
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>Akademi̇</t>
+          <t>Oyun Alani</t>
         </is>
       </c>
       <c r="B19" s="17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C19" s="17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D19" s="55" t="n">
         <v>1</v>
@@ -1685,101 +1685,99 @@
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>Kiyafet</t>
+          <t>Mal Kabul</t>
         </is>
       </c>
       <c r="B20" s="17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C20" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="D20" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="F20" s="17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Kirtasi̇ye</t>
+          <t>Oyuncak</t>
         </is>
       </c>
       <c r="B21" s="17" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C21" s="17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E21" s="17" t="n">
-        <v>1</v>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F21" s="17" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>Mal Kabul</t>
+          <t>Yardimci Ki̇tap</t>
         </is>
       </c>
       <c r="B22" s="17" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C22" s="17" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E22" s="17" t="n">
+        <v>3</v>
       </c>
       <c r="F22" s="17" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>Yardimci Ki̇tap</t>
+          <t>Kirtasi̇ye</t>
         </is>
       </c>
       <c r="B23" s="17" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C23" s="17" t="n">
-        <v>21</v>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
+        <v>23</v>
+      </c>
+      <c r="D23" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E23" s="17" t="n">
-        <v>3</v>
-      </c>
       <c r="F23" s="17" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24">
@@ -1809,14 +1807,14 @@
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>Oyuncak</t>
+          <t>Kiyafet</t>
         </is>
       </c>
       <c r="B25" s="17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C25" s="17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D25" s="17" t="inlineStr">
         <is>
@@ -1829,7 +1827,7 @@
         </is>
       </c>
       <c r="F25" s="17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1842,13 +1840,13 @@
         <v>145</v>
       </c>
       <c r="C26" s="21" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D26" s="21" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E26" s="21" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F26" s="21" t="n">
         <v>58</v>
@@ -1857,7 +1855,7 @@
     <row r="28">
       <c r="A28" s="32" t="inlineStr">
         <is>
-          <t>⚠ BOLUM acigi (15) MAGAZA acigindan (11) BUYUK: magaza icinde bir bolumun fazlasi baska bolumun acigini maskeler.</t>
+          <t>⚠ BOLUM acigi (17) MAGAZA acigindan (11) BUYUK: magaza icinde bir bolumun fazlasi baska bolumun acigini maskeler.</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2198,7 @@
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>66929723.56999852</v>
+        <v>66929723.56999993</v>
       </c>
       <c r="C9" s="17" t="n">
         <v>114687785.58</v>
@@ -2221,10 +2219,10 @@
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>71837429.11999343</v>
+        <v>71837429.12000012</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>122601380.8499947</v>
+        <v>122601380.8500001</v>
       </c>
       <c r="D10" s="18">
         <f>C10-B10</f>
@@ -2758,10 +2756,10 @@
         <v/>
       </c>
       <c r="M4" s="17" t="n">
-        <v>20455158.42999981</v>
+        <v>20455158.42999999</v>
       </c>
       <c r="N4" s="17" t="n">
-        <v>40444611.76999976</v>
+        <v>40444611.77</v>
       </c>
       <c r="O4" s="19">
         <f>N4/M4-1</f>
@@ -2831,10 +2829,10 @@
         <v/>
       </c>
       <c r="M5" s="17" t="n">
-        <v>28347121.58999882</v>
+        <v>28347121.58999996</v>
       </c>
       <c r="N5" s="17" t="n">
-        <v>44784483.14999945</v>
+        <v>44784483.15000006</v>
       </c>
       <c r="O5" s="19">
         <f>N5/M5-1</f>
@@ -2904,10 +2902,10 @@
         <v/>
       </c>
       <c r="M6" s="17" t="n">
-        <v>18127443.54999989</v>
+        <v>18127443.54999998</v>
       </c>
       <c r="N6" s="17" t="n">
-        <v>29458690.66000078</v>
+        <v>29458690.65999999</v>
       </c>
       <c r="O6" s="19">
         <f>N6/M6-1</f>
@@ -4504,10 +4502,10 @@
         <v/>
       </c>
       <c r="F4" s="34" t="n">
-        <v>18.5043249700029</v>
+        <v>18.50432496999891</v>
       </c>
       <c r="G4" s="34" t="n">
-        <v>32.38086690000142</v>
+        <v>32.38086689999964</v>
       </c>
       <c r="H4" s="44">
         <f>G4/F4-1</f>
@@ -4524,7 +4522,7 @@
         <v/>
       </c>
       <c r="L4" s="19" t="n">
-        <v>0.3747245332289066</v>
+        <v>0.3747245332273854</v>
       </c>
       <c r="M4" s="45" t="n">
         <v>3</v>
@@ -4552,10 +4550,10 @@
         <v/>
       </c>
       <c r="F5" s="34" t="n">
-        <v>10.02370844000001</v>
+        <v>10.02370843999998</v>
       </c>
       <c r="G5" s="34" t="n">
-        <v>15.50422909000001</v>
+        <v>15.50422908999993</v>
       </c>
       <c r="H5" s="44">
         <f>G5/F5-1</f>
@@ -4572,7 +4570,7 @@
         <v/>
       </c>
       <c r="L5" s="19" t="n">
-        <v>0.5770282964720019</v>
+        <v>0.5770282964720066</v>
       </c>
       <c r="M5" s="45" t="n">
         <v>-1</v>
@@ -4600,10 +4598,10 @@
         <v/>
       </c>
       <c r="F6" s="34" t="n">
-        <v>14.49106598999973</v>
+        <v>14.49106599000013</v>
       </c>
       <c r="G6" s="34" t="n">
-        <v>23.14058788999986</v>
+        <v>23.14058788999988</v>
       </c>
       <c r="H6" s="44">
         <f>G6/F6-1</f>
@@ -4620,7 +4618,7 @@
         <v/>
       </c>
       <c r="L6" s="19" t="n">
-        <v>0.4921459875658136</v>
+        <v>0.4921459875659902</v>
       </c>
       <c r="M6" s="45" t="n">
         <v>1</v>
@@ -4668,7 +4666,7 @@
         <v/>
       </c>
       <c r="L7" s="19" t="n">
-        <v>1.797673394233621</v>
+        <v>1.797673394233624</v>
       </c>
       <c r="M7" s="40" t="inlineStr">
         <is>
@@ -4701,7 +4699,7 @@
         <v>11.13631268</v>
       </c>
       <c r="G8" s="34" t="n">
-        <v>16.74884972000006</v>
+        <v>16.74884971999999</v>
       </c>
       <c r="H8" s="44">
         <f>G8/F8-1</f>
@@ -4718,7 +4716,7 @@
         <v/>
       </c>
       <c r="L8" s="19" t="n">
-        <v>0.6655996445023109</v>
+        <v>0.6655996445022587</v>
       </c>
       <c r="M8" s="45" t="n">
         <v>1</v>
@@ -4746,10 +4744,10 @@
         <v/>
       </c>
       <c r="F9" s="34" t="n">
-        <v>1.475290260000008</v>
+        <v>1.47529026</v>
       </c>
       <c r="G9" s="34" t="n">
-        <v>2.616103030000003</v>
+        <v>2.616103029999998</v>
       </c>
       <c r="H9" s="44">
         <f>G9/F9-1</f>
@@ -4766,7 +4764,7 @@
         <v/>
       </c>
       <c r="L9" s="19" t="n">
-        <v>1.258006023303491</v>
+        <v>1.258006023303307</v>
       </c>
       <c r="M9" s="40" t="inlineStr">
         <is>
@@ -4796,10 +4794,10 @@
         <v/>
       </c>
       <c r="F10" s="34" t="n">
-        <v>11.66512254</v>
+        <v>11.66512254000002</v>
       </c>
       <c r="G10" s="34" t="n">
-        <v>22.35794457999994</v>
+        <v>22.35794457999999</v>
       </c>
       <c r="H10" s="44">
         <f>G10/F10-1</f>
@@ -4816,7 +4814,7 @@
         <v/>
       </c>
       <c r="L10" s="19" t="n">
-        <v>0.4621370345582292</v>
+        <v>0.4621370345582057</v>
       </c>
       <c r="M10" s="45" t="n">
         <v>6</v>
@@ -4847,7 +4845,7 @@
         <v>0.69211733</v>
       </c>
       <c r="G11" s="34" t="n">
-        <v>1.187673780000001</v>
+        <v>1.187673779999999</v>
       </c>
       <c r="H11" s="44">
         <f>G11/F11-1</f>
@@ -4864,7 +4862,7 @@
         <v/>
       </c>
       <c r="L11" s="19" t="n">
-        <v>0.4636366398909368</v>
+        <v>0.4636366398909304</v>
       </c>
       <c r="M11" s="40" t="inlineStr">
         <is>
@@ -4894,10 +4892,10 @@
         <v/>
       </c>
       <c r="F12" s="34" t="n">
-        <v>1.942142249999998</v>
+        <v>1.942142250000001</v>
       </c>
       <c r="G12" s="34" t="n">
-        <v>6.643827519999992</v>
+        <v>6.643827520000001</v>
       </c>
       <c r="H12" s="44">
         <f>G12/F12-1</f>
@@ -4914,7 +4912,7 @@
         <v/>
       </c>
       <c r="L12" s="19" t="n">
-        <v>1.769093453522593</v>
+        <v>1.769093453522601</v>
       </c>
       <c r="M12" s="45" t="n">
         <v>2</v>
@@ -4945,7 +4943,7 @@
         <v>0.2846255699999998</v>
       </c>
       <c r="G13" s="34" t="n">
-        <v>0.4203621899999997</v>
+        <v>0.4203621899999998</v>
       </c>
       <c r="H13" s="44">
         <f>G13/F13-1</f>
@@ -4962,7 +4960,7 @@
         <v/>
       </c>
       <c r="L13" s="19" t="n">
-        <v>0.5224217348514228</v>
+        <v>0.5224217348514244</v>
       </c>
       <c r="M13" s="40" t="inlineStr">
         <is>
@@ -4992,10 +4990,10 @@
         <v/>
       </c>
       <c r="F14" s="34" t="n">
-        <v>1.257655950000001</v>
+        <v>1.25765595</v>
       </c>
       <c r="G14" s="34" t="n">
-        <v>0.9961937400000004</v>
+        <v>0.9961937400000002</v>
       </c>
       <c r="H14" s="44">
         <f>G14/F14-1</f>
@@ -5012,7 +5010,7 @@
         <v/>
       </c>
       <c r="L14" s="19" t="n">
-        <v>0.4008427609025746</v>
+        <v>0.4008427609025693</v>
       </c>
       <c r="M14" s="40" t="inlineStr">
         <is>
@@ -5042,10 +5040,10 @@
         <v/>
       </c>
       <c r="F15" s="34" t="n">
-        <v>0.2656298399999997</v>
+        <v>0.2656298400000003</v>
       </c>
       <c r="G15" s="34" t="n">
-        <v>0.3784858199999995</v>
+        <v>0.37848582</v>
       </c>
       <c r="H15" s="44">
         <f>G15/F15-1</f>
@@ -5062,7 +5060,7 @@
         <v/>
       </c>
       <c r="L15" s="19" t="n">
-        <v>0.4999858989104862</v>
+        <v>0.4999858989104888</v>
       </c>
       <c r="M15" s="40" t="inlineStr">
         <is>
@@ -5240,10 +5238,10 @@
         <v/>
       </c>
       <c r="E4" s="34" t="n">
-        <v>33.37095816000334</v>
+        <v>33.37095815999883</v>
       </c>
       <c r="F4" s="34" t="n">
-        <v>49.92745520000055</v>
+        <v>49.92745519999968</v>
       </c>
       <c r="G4" s="44">
         <f>F4/E4-1</f>
@@ -5267,10 +5265,10 @@
         <v/>
       </c>
       <c r="E5" s="34" t="n">
-        <v>32.14602051000339</v>
+        <v>32.14602050999881</v>
       </c>
       <c r="F5" s="34" t="n">
-        <v>55.81932909000084</v>
+        <v>55.81932908999958</v>
       </c>
       <c r="G5" s="44">
         <f>F5/E5-1</f>
@@ -5294,10 +5292,10 @@
         <v/>
       </c>
       <c r="E6" s="34" t="n">
-        <v>61.34527556000126</v>
+        <v>61.34527556000244</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>78.15309667999897</v>
+        <v>78.15309668000015</v>
       </c>
       <c r="G6" s="44">
         <f>F6/E6-1</f>
@@ -5776,10 +5774,10 @@
         <v/>
       </c>
       <c r="E4" s="17" t="n">
-        <v>316059798.2201092</v>
+        <v>316059798.2198316</v>
       </c>
       <c r="F4" s="17" t="n">
-        <v>489433287.7801834</v>
+        <v>489433287.7799246</v>
       </c>
       <c r="G4" s="19">
         <f>F4/E4-1</f>
@@ -5803,10 +5801,10 @@
         <v/>
       </c>
       <c r="E5" s="17" t="n">
-        <v>136108071.4499997</v>
+        <v>136108071.45</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>105575646.1100001</v>
+        <v>105575646.11</v>
       </c>
       <c r="G5" s="19">
         <f>F5/E5-1</f>

--- a/briefings/sezon-kadro-20260902/verimlilik-2026.xlsx
+++ b/briefings/sezon-kadro-20260902/verimlilik-2026.xlsx
@@ -37,7 +37,7 @@
     <numFmt numFmtId="171" formatCode="+0,0%"/>
     <numFmt numFmtId="172" formatCode="0,0&quot;x&quot;"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,6 +75,10 @@
       <color rgb="00A6001A"/>
     </font>
     <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <sz val="9"/>
     </font>
     <font>
@@ -106,7 +110,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -131,6 +135,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF6E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -204,30 +213,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="171" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -283,13 +292,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1186,12 +1198,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -1211,7 +1223,7 @@
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>Mağaza</t>
+          <t>Mağaza / Grup</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
@@ -1221,7 +1233,7 @@
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>Kadrolu 31.08</t>
+          <t>Operasyonel kadrolu</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
@@ -1270,7 +1282,7 @@
         <v>45</v>
       </c>
       <c r="C4" s="17" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D4" s="53">
         <f>C4-B4</f>
@@ -1290,7 +1302,7 @@
         <v>62</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J4" s="30">
         <f>I4-H4</f>
@@ -1307,7 +1319,7 @@
         <v>37</v>
       </c>
       <c r="C5" s="17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D5" s="53">
         <f>C5-B5</f>
@@ -1327,7 +1339,7 @@
         <v>47</v>
       </c>
       <c r="I5" s="17" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J5" s="30">
         <f>I5-H5</f>
@@ -1344,7 +1356,7 @@
         <v>33</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D6" s="53">
         <f>C6-B6</f>
@@ -1364,7 +1376,7 @@
         <v>58</v>
       </c>
       <c r="I6" s="17" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="J6" s="30">
         <f>I6-H6</f>
@@ -1852,36 +1864,79 @@
         <v>58</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="56" t="inlineStr">
+        <is>
+          <t>Etkinlik (norm dışı)</t>
+        </is>
+      </c>
+      <c r="C27" s="57" t="n">
+        <v>3</v>
+      </c>
+    </row>
     <row r="28">
-      <c r="A28" s="32" t="inlineStr">
-        <is>
-          <t>⚠ BOLUM acigi (17) MAGAZA acigindan (11) BUYUK: magaza icinde bir bolumun fazlasi baska bolumun acigini maskeler.</t>
-        </is>
+      <c r="A28" s="56" t="inlineStr">
+        <is>
+          <t>Engelli (norm dışı)</t>
+        </is>
+      </c>
+      <c r="C28" s="57" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="32" t="inlineStr">
-        <is>
-          <t>NORM SEZON DISI kadroyu tanimlar -&gt; sezonluk personel norma DAHIL DEGIL; kiyas yalniz KADROLU ile.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="32" t="inlineStr">
-        <is>
-          <t>Norm kaynagi: norm-kadro-20260811.json (11.08.2026). Yonetim parametresi, Zirve'den sorgulanmaz.</t>
-        </is>
+      <c r="A29" s="58" t="inlineStr">
+        <is>
+          <t>Kayıt toplamı (İK, tüm gruplar)</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="n">
+        <v>137</v>
+      </c>
+      <c r="F29" s="17" t="n">
+        <v>58</v>
+      </c>
+      <c r="I29" s="17" t="n">
+        <v>195</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="32" t="inlineStr">
         <is>
-          <t>KAPSAM DISI: Şura norm tablosunda yok.</t>
+          <t>KURAL: norm = ENGELLI DISINDAKI personel (yonetim karari). Magaza satirlari OPERASYONEL kadroyu gosterir (kadrolu - engelli - etkinlik); en altta IK'nin kayit toplami durur.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="32" t="inlineStr">
+        <is>
+          <t>⚠ BOLUM acigi (17) MAGAZA acigindan (11) BUYUK: magaza icinde bir bolumun fazlasi baska bolumun acigini maskeler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="32" t="inlineStr">
+        <is>
+          <t>NORM SEZON DISI kadroyu tanimlar -&gt; sezonluk personel norma DAHIL DEGIL; kiyas yalniz KADROLU ile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="32" t="inlineStr">
+        <is>
+          <t>Norm kaynagi: norm-kadro-20260811.json (11.08.2026). Yonetim parametresi, Zirve'den sorgulanmaz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="32" t="inlineStr">
+        <is>
+          <t>KAPSAM DISI: Şura norm tablosunda yok.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="32" t="inlineStr">
         <is>
           <t>Eksi fark = normun ALTINDA calisiliyor. Toplamda 31.08'de norm 145, gercek kadrolu 137.</t>
         </is>
@@ -1913,72 +1968,72 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="56" t="inlineStr">
+      <c r="A3" s="59" t="inlineStr">
         <is>
           <t>Baslik</t>
         </is>
       </c>
-      <c r="B3" s="57" t="inlineStr">
+      <c r="B3" s="60" t="inlineStr">
         <is>
           <t>Kişi başı iş hacmi — sezon 2026 vs 2025</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="56" t="inlineStr">
+      <c r="A4" s="59" t="inlineStr">
         <is>
           <t>Kesim tarihi</t>
         </is>
       </c>
-      <c r="B4" s="57" t="inlineStr">
+      <c r="B4" s="60" t="inlineStr">
         <is>
           <t>otomatik (veri sonu, okul-hizalı pencerede)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="56" t="inlineStr">
+      <c r="A5" s="59" t="inlineStr">
         <is>
           <t>Pencere</t>
         </is>
       </c>
-      <c r="B5" s="57" t="inlineStr">
+      <c r="B5" s="60" t="inlineStr">
         <is>
           <t>Okul açılışına hizalı — 2025: 01.07.2025 – 25.08.2025 · 2026: 07.07.2026 – 31.08.2026 (her iki yıl 56 gün; açılış 20250908 ve 20260914, gün ofseti -69..-14)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="56" t="inlineStr">
+      <c r="A6" s="59" t="inlineStr">
         <is>
           <t>Kadro kaynagi</t>
         </is>
       </c>
-      <c r="B6" s="57" t="inlineStr">
+      <c r="B6" s="60" t="inlineStr">
         <is>
           <t>Zirve BKM_GENEL.dbo.vw_PersonelDepartman — as-of Igt &lt;= T AND (Ict IS NULL OR Ict &gt;= T), sp_PersonelKarsilastirma_Ozet ile birebir</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="56" t="inlineStr">
+      <c r="A7" s="59" t="inlineStr">
         <is>
           <t>Is hacmi kaynagi</t>
         </is>
       </c>
-      <c r="B7" s="57" t="inlineStr">
+      <c r="B7" s="60" t="inlineStr">
         <is>
           <t>DerinSIS irs/irsAyr eTip=100 (POS satışı), Sınav Okulları/Kıyafet hariç, iade netlenmiş</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="56" t="inlineStr">
+      <c r="A8" s="59" t="inlineStr">
         <is>
           <t>Cekirdek SQL</t>
         </is>
       </c>
-      <c r="B8" s="57" t="inlineStr">
+      <c r="B8" s="60" t="inlineStr">
         <is>
           <t>sorgular/2026-09-02-kadro-vs-is-hacmi-savunma.sql (blok 11)</t>
         </is>
@@ -1992,49 +2047,49 @@
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="B11" s="58" t="inlineStr">
+      <c r="B11" s="61" t="inlineStr">
         <is>
           <t>• Ürün adedi enflasyondan bağımsız — kadro kıyasında birincil ölçüt. Ciro ikincil (fiyat endeksi +%19,8, Fisher, eşleşen ürün).</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="B12" s="58" t="inlineStr">
+      <c r="B12" s="61" t="inlineStr">
         <is>
           <t>• Kıyas okul açılışına hizalı yapılır. Takvim tarihine göre kıyas 2026'da yapay düşüş gösterir: açılış 8 Eylül 2025'ten 14 Eylül 2026'ya, 6 gün kaydı.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="B13" s="58" t="inlineStr">
+      <c r="B13" s="61" t="inlineStr">
         <is>
           <t>• İş hacmi EncoreMerkez POS'tan DEĞİL DerinSIS'ten alınır: POS Temmuz 2025'te değişti (ENPOS → EncoreMerkez), EncoreMerkez'in 2025 tabanı eksik.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="B14" s="58" t="inlineStr">
+      <c r="B14" s="61" t="inlineStr">
         <is>
           <t>• Heykel ve Şura POS raporlamasında yok — mağaza sayfası üç POS mağazası (FSM · Özlüce · İst. Yolu). Beş mağaza kadro hareketi Özet'te ayrı.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="B15" s="58" t="inlineStr">
+      <c r="B15" s="61" t="inlineStr">
         <is>
           <t>• Kadro = o tarihte fiilen çalışan kişi (sezonluk + kadrolu). Kişi başı oranlar kasiyer değil TÜM mağaza kadrosu üzerinden.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="B16" s="58" t="inlineStr">
+      <c r="B16" s="61" t="inlineStr">
         <is>
           <t>• Fiş sayısı bu kaynakta yok: eTip 100 günlük özet belgedir (bir gün = bir belge).</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
-      <c r="B17" s="58" t="inlineStr">
+      <c r="B17" s="61" t="inlineStr">
         <is>
           <t>• Kıdem → verimlilik testi NEGATİF çıktı: aynı kasiyerin öğrenme eğrisi düz (220 → 256 → 242 fiş/gün), mağaza kıdem sıralaması verimlilikle uyuşmuyor. 'Tecrübeli 1 kişi = acemi 3 kişi' iddiası bu veriyle savunulamaz.</t>
         </is>

--- a/briefings/sezon-kadro-20260902/verimlilik-2026.xlsx
+++ b/briefings/sezon-kadro-20260902/verimlilik-2026.xlsx
@@ -1529,14 +1529,14 @@
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Mağaza</t>
+          <t>İdari̇ İşler</t>
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C13" s="17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D13" s="55" t="n">
         <v>2</v>
@@ -1553,14 +1553,14 @@
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>İdari̇ İşler</t>
+          <t>Mağaza</t>
         </is>
       </c>
       <c r="B14" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" s="17" t="n">
         <v>8</v>
-      </c>
-      <c r="C14" s="17" t="n">
-        <v>6</v>
       </c>
       <c r="D14" s="55" t="n">
         <v>2</v>
@@ -1601,14 +1601,14 @@
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>Kasa</t>
+          <t>Muhasebe</t>
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C16" s="17" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D16" s="55" t="n">
         <v>1</v>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F16" s="17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>Muhasebe</t>
+          <t>Oyun Alani</t>
         </is>
       </c>
       <c r="B17" s="17" t="n">
@@ -1649,14 +1649,14 @@
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>Akademi̇</t>
+          <t>Kasa</t>
         </is>
       </c>
       <c r="B18" s="17" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C18" s="17" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D18" s="55" t="n">
         <v>1</v>
@@ -1667,20 +1667,20 @@
         </is>
       </c>
       <c r="F18" s="17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>Oyun Alani</t>
+          <t>Akademi̇</t>
         </is>
       </c>
       <c r="B19" s="17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C19" s="17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D19" s="55" t="n">
         <v>1</v>
@@ -1697,48 +1697,46 @@
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>Mal Kabul</t>
+          <t>Yardimci Ki̇tap</t>
         </is>
       </c>
       <c r="B20" s="17" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C20" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="D20" s="55" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
+        <v>21</v>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="E20" s="17" t="n">
+        <v>3</v>
+      </c>
       <c r="F20" s="17" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Oyuncak</t>
+          <t>Etki̇nli̇k</t>
         </is>
       </c>
       <c r="B21" s="17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C21" s="17" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E21" s="17" t="n">
+        <v>3</v>
       </c>
       <c r="F21" s="17" t="n">
         <v>0</v>
@@ -1747,41 +1745,43 @@
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>Yardimci Ki̇tap</t>
+          <t>Mal Kabul</t>
         </is>
       </c>
       <c r="B22" s="17" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C22" s="17" t="n">
-        <v>21</v>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="D22" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E22" s="17" t="n">
-        <v>3</v>
-      </c>
       <c r="F22" s="17" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>Kirtasi̇ye</t>
+          <t>Kiyafet</t>
         </is>
       </c>
       <c r="B23" s="17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C23" s="17" t="n">
-        <v>23</v>
-      </c>
-      <c r="D23" s="55" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E23" s="17" t="inlineStr">
         <is>
@@ -1789,28 +1789,30 @@
         </is>
       </c>
       <c r="F23" s="17" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>Etki̇nli̇k</t>
+          <t>Oyuncak</t>
         </is>
       </c>
       <c r="B24" s="17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C24" s="17" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E24" s="17" t="n">
-        <v>3</v>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F24" s="17" t="n">
         <v>0</v>
@@ -1819,27 +1821,25 @@
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>Kiyafet</t>
+          <t>Kirtasi̇ye</t>
         </is>
       </c>
       <c r="B25" s="17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C25" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
+        <v>23</v>
+      </c>
+      <c r="D25" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="F25" s="17" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26">
@@ -2232,10 +2232,10 @@
         </is>
       </c>
       <c r="B8" s="17" t="n">
-        <v>574717.7</v>
+        <v>574655.7</v>
       </c>
       <c r="C8" s="17" t="n">
-        <v>775191.55</v>
+        <v>775031.55</v>
       </c>
       <c r="D8" s="18">
         <f>C8-B8</f>
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>66929723.56999993</v>
+        <v>66909340.21999995</v>
       </c>
       <c r="C9" s="17" t="n">
-        <v>114687785.58</v>
+        <v>114620580.3400001</v>
       </c>
       <c r="D9" s="18">
         <f>C9-B9</f>
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>71837429.12000012</v>
+        <v>71817045.7700001</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>122601380.8500001</v>
+        <v>122534175.6100001</v>
       </c>
       <c r="D10" s="18">
         <f>C10-B10</f>
@@ -2781,10 +2781,10 @@
         <v/>
       </c>
       <c r="E4" s="17" t="n">
-        <v>173398</v>
+        <v>173336</v>
       </c>
       <c r="F4" s="17" t="n">
-        <v>258168.5</v>
+        <v>258008.5</v>
       </c>
       <c r="G4" s="19">
         <f>F4/E4-1</f>
@@ -2811,10 +2811,10 @@
         <v/>
       </c>
       <c r="M4" s="17" t="n">
-        <v>20455158.42999999</v>
+        <v>20434775.07999999</v>
       </c>
       <c r="N4" s="17" t="n">
-        <v>40444611.77</v>
+        <v>40377406.53000002</v>
       </c>
       <c r="O4" s="19">
         <f>N4/M4-1</f>
@@ -2884,7 +2884,7 @@
         <v/>
       </c>
       <c r="M5" s="17" t="n">
-        <v>28347121.58999996</v>
+        <v>28347121.58999998</v>
       </c>
       <c r="N5" s="17" t="n">
         <v>44784483.15000006</v>
@@ -2957,10 +2957,10 @@
         <v/>
       </c>
       <c r="M6" s="17" t="n">
-        <v>18127443.54999998</v>
+        <v>18127443.54999999</v>
       </c>
       <c r="N6" s="17" t="n">
-        <v>29458690.65999999</v>
+        <v>29458690.66</v>
       </c>
       <c r="O6" s="19">
         <f>N6/M6-1</f>
@@ -4557,10 +4557,10 @@
         <v/>
       </c>
       <c r="F4" s="34" t="n">
-        <v>18.50432496999891</v>
+        <v>18.50432496999888</v>
       </c>
       <c r="G4" s="34" t="n">
-        <v>32.38086689999964</v>
+        <v>32.38086689999962</v>
       </c>
       <c r="H4" s="44">
         <f>G4/F4-1</f>
@@ -4577,7 +4577,7 @@
         <v/>
       </c>
       <c r="L4" s="19" t="n">
-        <v>0.3747245332273854</v>
+        <v>0.3747245332273805</v>
       </c>
       <c r="M4" s="45" t="n">
         <v>3</v>
@@ -4605,10 +4605,10 @@
         <v/>
       </c>
       <c r="F5" s="34" t="n">
-        <v>10.02370843999998</v>
+        <v>10.02370843999997</v>
       </c>
       <c r="G5" s="34" t="n">
-        <v>15.50422908999993</v>
+        <v>15.50422908999992</v>
       </c>
       <c r="H5" s="44">
         <f>G5/F5-1</f>
@@ -4625,7 +4625,7 @@
         <v/>
       </c>
       <c r="L5" s="19" t="n">
-        <v>0.5770282964720066</v>
+        <v>0.5770282964720101</v>
       </c>
       <c r="M5" s="45" t="n">
         <v>-1</v>
@@ -4656,7 +4656,7 @@
         <v>14.49106599000013</v>
       </c>
       <c r="G6" s="34" t="n">
-        <v>23.14058788999988</v>
+        <v>23.14058788999989</v>
       </c>
       <c r="H6" s="44">
         <f>G6/F6-1</f>
@@ -4673,7 +4673,7 @@
         <v/>
       </c>
       <c r="L6" s="19" t="n">
-        <v>0.4921459875659902</v>
+        <v>0.4921459875659884</v>
       </c>
       <c r="M6" s="45" t="n">
         <v>1</v>
@@ -4701,7 +4701,7 @@
         <v/>
       </c>
       <c r="F7" s="34" t="n">
-        <v>0.02740152000000001</v>
+        <v>0.02740152</v>
       </c>
       <c r="G7" s="34" t="n">
         <v>0.07535017999999999</v>
@@ -4721,7 +4721,7 @@
         <v/>
       </c>
       <c r="L7" s="19" t="n">
-        <v>1.797673394233624</v>
+        <v>1.797673394233623</v>
       </c>
       <c r="M7" s="40" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v/>
       </c>
       <c r="L8" s="19" t="n">
-        <v>0.6655996445022587</v>
+        <v>0.6655996445022589</v>
       </c>
       <c r="M8" s="45" t="n">
         <v>1</v>
@@ -4799,10 +4799,10 @@
         <v/>
       </c>
       <c r="F9" s="34" t="n">
-        <v>1.47529026</v>
+        <v>1.475290259999999</v>
       </c>
       <c r="G9" s="34" t="n">
-        <v>2.616103029999998</v>
+        <v>2.616103029999999</v>
       </c>
       <c r="H9" s="44">
         <f>G9/F9-1</f>
@@ -4819,7 +4819,7 @@
         <v/>
       </c>
       <c r="L9" s="19" t="n">
-        <v>1.258006023303307</v>
+        <v>1.258006023303308</v>
       </c>
       <c r="M9" s="40" t="inlineStr">
         <is>
@@ -4839,37 +4839,37 @@
         </is>
       </c>
       <c r="C10" s="17" t="n">
-        <v>38847</v>
+        <v>38785</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>54032</v>
+        <v>53872</v>
       </c>
       <c r="E10" s="44">
         <f>D10/C10-1</f>
         <v/>
       </c>
       <c r="F10" s="34" t="n">
-        <v>11.66512254000002</v>
+        <v>11.64473919000002</v>
       </c>
       <c r="G10" s="34" t="n">
-        <v>22.35794457999999</v>
+        <v>22.29073934</v>
       </c>
       <c r="H10" s="44">
         <f>G10/F10-1</f>
         <v/>
       </c>
       <c r="I10" s="17" t="n">
-        <v>218946</v>
+        <v>218692</v>
       </c>
       <c r="J10" s="17" t="n">
-        <v>266564</v>
+        <v>266398</v>
       </c>
       <c r="K10" s="19">
         <f>IF(OR(I10="—",J10="—"),"",J10/I10-1)</f>
         <v/>
       </c>
       <c r="L10" s="19" t="n">
-        <v>0.4621370345582057</v>
+        <v>0.4631940216117374</v>
       </c>
       <c r="M10" s="45" t="n">
         <v>6</v>
@@ -4900,7 +4900,7 @@
         <v>0.69211733</v>
       </c>
       <c r="G11" s="34" t="n">
-        <v>1.187673779999999</v>
+        <v>1.18767378</v>
       </c>
       <c r="H11" s="44">
         <f>G11/F11-1</f>
@@ -4917,7 +4917,7 @@
         <v/>
       </c>
       <c r="L11" s="19" t="n">
-        <v>0.4636366398909304</v>
+        <v>0.4636366398909308</v>
       </c>
       <c r="M11" s="40" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>1.942142250000001</v>
       </c>
       <c r="G12" s="34" t="n">
-        <v>6.643827520000001</v>
+        <v>6.643827520000002</v>
       </c>
       <c r="H12" s="44">
         <f>G12/F12-1</f>
@@ -4998,7 +4998,7 @@
         <v>0.2846255699999998</v>
       </c>
       <c r="G13" s="34" t="n">
-        <v>0.4203621899999998</v>
+        <v>0.4203621900000001</v>
       </c>
       <c r="H13" s="44">
         <f>G13/F13-1</f>
@@ -5015,7 +5015,7 @@
         <v/>
       </c>
       <c r="L13" s="19" t="n">
-        <v>0.5224217348514244</v>
+        <v>0.5224217348514235</v>
       </c>
       <c r="M13" s="40" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>1.25765595</v>
       </c>
       <c r="G14" s="34" t="n">
-        <v>0.9961937400000002</v>
+        <v>0.9961937399999998</v>
       </c>
       <c r="H14" s="44">
         <f>G14/F14-1</f>
@@ -5065,7 +5065,7 @@
         <v/>
       </c>
       <c r="L14" s="19" t="n">
-        <v>0.4008427609025693</v>
+        <v>0.40084276090257</v>
       </c>
       <c r="M14" s="40" t="inlineStr">
         <is>
@@ -5095,10 +5095,10 @@
         <v/>
       </c>
       <c r="F15" s="34" t="n">
-        <v>0.2656298400000003</v>
+        <v>0.2656298400000001</v>
       </c>
       <c r="G15" s="34" t="n">
-        <v>0.37848582</v>
+        <v>0.3784858199999998</v>
       </c>
       <c r="H15" s="44">
         <f>G15/F15-1</f>
@@ -5115,7 +5115,7 @@
         <v/>
       </c>
       <c r="L15" s="19" t="n">
-        <v>0.4999858989104888</v>
+        <v>0.4999858989104884</v>
       </c>
       <c r="M15" s="40" t="inlineStr">
         <is>
@@ -5293,10 +5293,10 @@
         <v/>
       </c>
       <c r="E4" s="34" t="n">
-        <v>33.37095815999883</v>
+        <v>33.37095815999876</v>
       </c>
       <c r="F4" s="34" t="n">
-        <v>49.92745519999968</v>
+        <v>49.92745519999966</v>
       </c>
       <c r="G4" s="44">
         <f>F4/E4-1</f>
@@ -5313,7 +5313,7 @@
         <v>269478</v>
       </c>
       <c r="C5" s="17" t="n">
-        <v>367353</v>
+        <v>367352</v>
       </c>
       <c r="D5" s="44">
         <f>C5/B5-1</f>
@@ -5323,7 +5323,7 @@
         <v>32.14602050999881</v>
       </c>
       <c r="F5" s="34" t="n">
-        <v>55.81932908999958</v>
+        <v>55.8190090899996</v>
       </c>
       <c r="G5" s="44">
         <f>F5/E5-1</f>
@@ -5337,20 +5337,20 @@
         </is>
       </c>
       <c r="B6" s="17" t="n">
-        <v>458508.7</v>
+        <v>458258.7</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>483658.55</v>
+        <v>483499.55</v>
       </c>
       <c r="D6" s="44">
         <f>C6/B6-1</f>
         <v/>
       </c>
       <c r="E6" s="34" t="n">
-        <v>61.34527556000244</v>
+        <v>61.26123198000229</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>78.15309668000015</v>
+        <v>78.0862114400001</v>
       </c>
       <c r="G6" s="44">
         <f>F6/E6-1</f>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>adet +%34.6 · ciro +%67.7</t>
+          <t>adet +%34.6 · ciro +%67.6</t>
         </is>
       </c>
       <c r="C11" s="48" t="n"/>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>458.509 adet · 61.3 M TL</t>
+          <t>458.259 adet · 61.3 M TL</t>
         </is>
       </c>
       <c r="C12" s="48" t="n"/>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>483.659 adet · 78.2 M TL  (adet +%5.5)</t>
+          <t>483.500 adet · 78.1 M TL  (adet +%5.5)</t>
         </is>
       </c>
       <c r="C13" s="48" t="n"/>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="B14" s="51" t="inlineStr">
         <is>
-          <t>617.297 adet · 102.9 M TL</t>
+          <t>616.873 adet · 102.7 M TL</t>
         </is>
       </c>
       <c r="C14" s="48" t="n"/>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="B15" s="51" t="inlineStr">
         <is>
-          <t>133.638 adet · 24.7 M TL</t>
+          <t>133.374 adet · 24.6 M TL</t>
         </is>
       </c>
       <c r="C15" s="48" t="n"/>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>431.358 adet · 56.9 M TL</t>
+          <t>430.919 adet · 56.8 M TL</t>
         </is>
       </c>
       <c r="C16" s="48" t="n"/>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="B17" s="51" t="inlineStr">
         <is>
-          <t>580.744 adet · 95.5 M TL</t>
+          <t>580.071 adet · 95.2 M TL</t>
         </is>
       </c>
       <c r="C17" s="48" t="n"/>
@@ -5534,7 +5534,7 @@
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Yöntem: 2026 günleri 2025'in 6 gün öncesine denk gelir (açılış 08.09.2025 → 14.09.2026). Hizalı 27 günde ölçülen büyüme (adet %34.6 · ciro %67.7) 2025 Ağustos toplamına uygulanarak kayma-arındırılmış Ağustos bulunur. VARSAYIM: talep kaybı yok, yalnız zamanlama kaydı. Bugünün verisi HARİÇ (eTip 100 gün içinde yeniden yazılır); son tam gün 01.09.2026.</t>
+          <t>Yöntem: 2026 günleri 2025'in 6 gün öncesine denk gelir (açılış 08.09.2025 → 14.09.2026). Hizalı 27 günde ölçülen büyüme (adet %34.6 · ciro %67.6) 2025 Ağustos toplamına uygulanarak kayma-arındırılmış Ağustos bulunur. VARSAYIM: talep kaybı yok, yalnız zamanlama kaydı. Bugünün verisi HARİÇ (eTip 100 gün içinde yeniden yazılır); son tam gün 01.09.2026.</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
         <v>60</v>
       </c>
       <c r="C4" s="17" t="n">
-        <v>2064284.43</v>
+        <v>2062663.43</v>
       </c>
       <c r="D4" s="52">
         <f>C4/B4</f>
@@ -5667,7 +5667,7 @@
         <v>91</v>
       </c>
       <c r="C5" s="17" t="n">
-        <v>2296833.43</v>
+        <v>2295719.43</v>
       </c>
       <c r="D5" s="52">
         <f>C5/B5</f>
@@ -5686,7 +5686,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>2752385.04</v>
+        <v>2752131.04</v>
       </c>
       <c r="D6" s="52">
         <f>C6/B6</f>
@@ -5705,7 +5705,7 @@
         <v>111</v>
       </c>
       <c r="C7" s="17" t="n">
-        <v>3607308.91</v>
+        <v>3607142.91</v>
       </c>
       <c r="D7" s="52">
         <f>C7/B7</f>
@@ -5819,20 +5819,20 @@
         </is>
       </c>
       <c r="B4" s="17" t="n">
-        <v>2752385.04</v>
+        <v>2752131.04</v>
       </c>
       <c r="C4" s="17" t="n">
-        <v>3607308.91</v>
+        <v>3607142.91</v>
       </c>
       <c r="D4" s="19">
         <f>C4/B4-1</f>
         <v/>
       </c>
       <c r="E4" s="17" t="n">
-        <v>316059798.2198316</v>
+        <v>315972605.8798317</v>
       </c>
       <c r="F4" s="17" t="n">
-        <v>489433287.7799246</v>
+        <v>489364071.8499244</v>
       </c>
       <c r="G4" s="19">
         <f>F4/E4-1</f>
@@ -5846,20 +5846,20 @@
         </is>
       </c>
       <c r="B5" s="17" t="n">
-        <v>33584</v>
+        <v>33838</v>
       </c>
       <c r="C5" s="17" t="n">
-        <v>21693</v>
+        <v>21859</v>
       </c>
       <c r="D5" s="19">
         <f>C5/B5-1</f>
         <v/>
       </c>
       <c r="E5" s="17" t="n">
-        <v>136108071.45</v>
+        <v>136195263.79</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>105575646.11</v>
+        <v>105644862.04</v>
       </c>
       <c r="G5" s="19">
         <f>F5/E5-1</f>

--- a/briefings/sezon-kadro-20260902/verimlilik-2026.xlsx
+++ b/briefings/sezon-kadro-20260902/verimlilik-2026.xlsx
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Aynı dönemde elleçlenen ürün adedi %35 arttı.</t>
+          <t>Aynı dönemde elleçlenen ürün adedi arttı.</t>
         </is>
       </c>
       <c r="C11" s="7">
@@ -1057,7 +1057,7 @@
     <row r="12" ht="26" customHeight="1">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>574.718 → 775.192 adet. Adet enflasyondan etkilenmez — fiilen kasadan geçen, rafa dizilen mal.</t>
+          <t>Adet enflasyondan etkilenmez — fiilen kasadan geçen, rafa dizilen mal.</t>
         </is>
       </c>
     </row>
@@ -1069,18 +1069,18 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Ciro %71 arttı.</t>
+          <t>Ciro arttı.</t>
         </is>
       </c>
       <c r="C13" s="7">
-        <f>'Ozet'!E10</f>
+        <f>'Ozet'!E9</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>71,8 milyon → 122,6 milyon ₺ (KDV dahil, iadeler düşülmüş).</t>
+          <t>KDV dahil, iadeler düşülmüş.</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Kişi başı ürün 4.019 → 4.845 adet; günlük 71,8 → 86,5 adet.</t>
+          <t>Kişi başı ürün adedi ve günlük adet birlikte yükseldi.</t>
         </is>
       </c>
     </row>
@@ -1119,14 +1119,14 @@
         </is>
       </c>
       <c r="C17" s="8">
-        <f>'Ozet'!B17</f>
+        <f>'Ozet'!B16</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Ürün adedi +%34,9 · kadro +%11,9.</t>
+          <t>Ürün adedi ÷ kadro büyümesi (ciro oranı değil).</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
     <row r="20" ht="26" customHeight="1">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Yönetim +0 · Mal Kabul +0 · İdari İşler +0. Artış: Yardımcı Kitap +6 · Kırtasiye +3 · Kasa +2.</t>
+          <t>Yönetim · Mal Kabul · İdari İşler kadrosu değişmedi; artış satış ve kasa reyonlarında.</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
     <row r="22" ht="26" customHeight="1">
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Sınav Okulları Ocak–Ağustos cirosu −%22,4 küçüldü; mağaza tarafı +%54,9 büyüdü.</t>
+          <t>Sınav Okulları Ocak–Ağustos cirosu küçüldü; mağaza tarafı büyüdü.</t>
         </is>
       </c>
     </row>
@@ -1529,14 +1529,14 @@
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>İdari̇ İşler</t>
+          <t>Mağaza</t>
         </is>
       </c>
       <c r="B13" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" s="17" t="n">
         <v>8</v>
-      </c>
-      <c r="C13" s="17" t="n">
-        <v>6</v>
       </c>
       <c r="D13" s="55" t="n">
         <v>2</v>
@@ -1553,14 +1553,14 @@
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Mağaza</t>
+          <t>İdari̇ İşler</t>
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C14" s="17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D14" s="55" t="n">
         <v>2</v>
@@ -1697,65 +1697,67 @@
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>Yardimci Ki̇tap</t>
+          <t>Kirtasi̇ye</t>
         </is>
       </c>
       <c r="B20" s="17" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C20" s="17" t="n">
-        <v>21</v>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
+        <v>23</v>
+      </c>
+      <c r="D20" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E20" s="17" t="n">
-        <v>3</v>
-      </c>
       <c r="F20" s="17" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Etki̇nli̇k</t>
+          <t>Mal Kabul</t>
         </is>
       </c>
       <c r="B21" s="17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C21" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="D21" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E21" s="17" t="n">
-        <v>3</v>
-      </c>
       <c r="F21" s="17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>Mal Kabul</t>
+          <t>Oyuncak</t>
         </is>
       </c>
       <c r="B22" s="17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C22" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="D22" s="55" t="n">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
@@ -1763,7 +1765,7 @@
         </is>
       </c>
       <c r="F22" s="17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1795,51 +1797,49 @@
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>Oyuncak</t>
+          <t>Yardimci Ki̇tap</t>
         </is>
       </c>
       <c r="B24" s="17" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C24" s="17" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E24" s="17" t="n">
+        <v>3</v>
       </c>
       <c r="F24" s="17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>Kirtasi̇ye</t>
+          <t>Etki̇nli̇k</t>
         </is>
       </c>
       <c r="B25" s="17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C25" s="17" t="n">
-        <v>23</v>
-      </c>
-      <c r="D25" s="55" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="E25" s="17" t="n">
+        <v>3</v>
+      </c>
       <c r="F25" s="17" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1910,7 +1910,7 @@
     <row r="32">
       <c r="A32" s="32" t="inlineStr">
         <is>
-          <t>⚠ BOLUM acigi (17) MAGAZA acigindan (11) BUYUK: magaza icinde bir bolumun fazlasi baska bolumun acigini maskeler.</t>
+          <t>⚠ BOLUM acigi (17) MAGAZA acigindan (14) BUYUK: magaza icinde bir bolumun fazlasi baska bolumun acigini maskeler.</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1938,7 @@
     <row r="36">
       <c r="A36" s="32" t="inlineStr">
         <is>
-          <t>Eksi fark = normun ALTINDA calisiliyor. Toplamda 31.08'de norm 145, gercek kadrolu 137.</t>
+          <t>Eksi fark = normun ALTINDA calisiliyor. 31.08'de norm 145, OPERASYONEL kadrolu 131 (kayit 137 - engelli/etkinlik). Ustteki tablo operasyonel rakami gosterir.</t>
         </is>
       </c>
     </row>
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>66909340.21999995</v>
+        <v>66909340.21999996</v>
       </c>
       <c r="C9" s="17" t="n">
-        <v>114620580.3400001</v>
+        <v>114620580.34</v>
       </c>
       <c r="D9" s="18">
         <f>C9-B9</f>
@@ -2814,7 +2814,7 @@
         <v>20434775.07999999</v>
       </c>
       <c r="N4" s="17" t="n">
-        <v>40377406.53000002</v>
+        <v>40377406.53</v>
       </c>
       <c r="O4" s="19">
         <f>N4/M4-1</f>
@@ -2887,7 +2887,7 @@
         <v>28347121.58999998</v>
       </c>
       <c r="N5" s="17" t="n">
-        <v>44784483.15000006</v>
+        <v>44784483.15000005</v>
       </c>
       <c r="O5" s="19">
         <f>N5/M5-1</f>
@@ -2960,7 +2960,7 @@
         <v>18127443.54999999</v>
       </c>
       <c r="N6" s="17" t="n">
-        <v>29458690.66</v>
+        <v>29458690.65999999</v>
       </c>
       <c r="O6" s="19">
         <f>N6/M6-1</f>
@@ -4557,10 +4557,10 @@
         <v/>
       </c>
       <c r="F4" s="34" t="n">
-        <v>18.50432496999888</v>
+        <v>18.50432496999893</v>
       </c>
       <c r="G4" s="34" t="n">
-        <v>32.38086689999962</v>
+        <v>32.38086689999965</v>
       </c>
       <c r="H4" s="44">
         <f>G4/F4-1</f>
@@ -4577,7 +4577,7 @@
         <v/>
       </c>
       <c r="L4" s="19" t="n">
-        <v>0.3747245332273805</v>
+        <v>0.3747245332273823</v>
       </c>
       <c r="M4" s="45" t="n">
         <v>3</v>
@@ -4605,10 +4605,10 @@
         <v/>
       </c>
       <c r="F5" s="34" t="n">
-        <v>10.02370843999997</v>
+        <v>10.02370843999998</v>
       </c>
       <c r="G5" s="34" t="n">
-        <v>15.50422908999992</v>
+        <v>15.50422908999993</v>
       </c>
       <c r="H5" s="44">
         <f>G5/F5-1</f>
@@ -4625,7 +4625,7 @@
         <v/>
       </c>
       <c r="L5" s="19" t="n">
-        <v>0.5770282964720101</v>
+        <v>0.5770282964720093</v>
       </c>
       <c r="M5" s="45" t="n">
         <v>-1</v>
@@ -4673,7 +4673,7 @@
         <v/>
       </c>
       <c r="L6" s="19" t="n">
-        <v>0.4921459875659884</v>
+        <v>0.4921459875659908</v>
       </c>
       <c r="M6" s="45" t="n">
         <v>1</v>
@@ -4704,7 +4704,7 @@
         <v>0.02740152</v>
       </c>
       <c r="G7" s="34" t="n">
-        <v>0.07535017999999999</v>
+        <v>0.07535018</v>
       </c>
       <c r="H7" s="44">
         <f>G7/F7-1</f>
@@ -4721,7 +4721,7 @@
         <v/>
       </c>
       <c r="L7" s="19" t="n">
-        <v>1.797673394233623</v>
+        <v>1.797673394233622</v>
       </c>
       <c r="M7" s="40" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v/>
       </c>
       <c r="L8" s="19" t="n">
-        <v>0.6655996445022589</v>
+        <v>0.6655996445022598</v>
       </c>
       <c r="M8" s="45" t="n">
         <v>1</v>
@@ -4799,10 +4799,10 @@
         <v/>
       </c>
       <c r="F9" s="34" t="n">
-        <v>1.475290259999999</v>
+        <v>1.47529026</v>
       </c>
       <c r="G9" s="34" t="n">
-        <v>2.616103029999999</v>
+        <v>2.616103029999998</v>
       </c>
       <c r="H9" s="44">
         <f>G9/F9-1</f>
@@ -4819,7 +4819,7 @@
         <v/>
       </c>
       <c r="L9" s="19" t="n">
-        <v>1.258006023303308</v>
+        <v>1.25800602330331</v>
       </c>
       <c r="M9" s="40" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>11.64473919000002</v>
       </c>
       <c r="G10" s="34" t="n">
-        <v>22.29073934</v>
+        <v>22.29073933999999</v>
       </c>
       <c r="H10" s="44">
         <f>G10/F10-1</f>
@@ -4869,7 +4869,7 @@
         <v/>
       </c>
       <c r="L10" s="19" t="n">
-        <v>0.4631940216117374</v>
+        <v>0.4631940216117372</v>
       </c>
       <c r="M10" s="45" t="n">
         <v>6</v>
@@ -4897,7 +4897,7 @@
         <v/>
       </c>
       <c r="F11" s="34" t="n">
-        <v>0.69211733</v>
+        <v>0.6921173299999999</v>
       </c>
       <c r="G11" s="34" t="n">
         <v>1.18767378</v>
@@ -4950,7 +4950,7 @@
         <v>1.942142250000001</v>
       </c>
       <c r="G12" s="34" t="n">
-        <v>6.643827520000002</v>
+        <v>6.643827520000004</v>
       </c>
       <c r="H12" s="44">
         <f>G12/F12-1</f>
@@ -4967,7 +4967,7 @@
         <v/>
       </c>
       <c r="L12" s="19" t="n">
-        <v>1.769093453522601</v>
+        <v>1.769093453522603</v>
       </c>
       <c r="M12" s="45" t="n">
         <v>2</v>
@@ -4995,7 +4995,7 @@
         <v/>
       </c>
       <c r="F13" s="34" t="n">
-        <v>0.2846255699999998</v>
+        <v>0.2846255699999999</v>
       </c>
       <c r="G13" s="34" t="n">
         <v>0.4203621900000001</v>
@@ -5015,7 +5015,7 @@
         <v/>
       </c>
       <c r="L13" s="19" t="n">
-        <v>0.5224217348514235</v>
+        <v>0.5224217348514231</v>
       </c>
       <c r="M13" s="40" t="inlineStr">
         <is>
@@ -5095,10 +5095,10 @@
         <v/>
       </c>
       <c r="F15" s="34" t="n">
-        <v>0.2656298400000001</v>
+        <v>0.2656298400000002</v>
       </c>
       <c r="G15" s="34" t="n">
-        <v>0.3784858199999998</v>
+        <v>0.37848582</v>
       </c>
       <c r="H15" s="44">
         <f>G15/F15-1</f>
@@ -5115,7 +5115,7 @@
         <v/>
       </c>
       <c r="L15" s="19" t="n">
-        <v>0.4999858989104884</v>
+        <v>0.4999858989104882</v>
       </c>
       <c r="M15" s="40" t="inlineStr">
         <is>
@@ -5293,10 +5293,10 @@
         <v/>
       </c>
       <c r="E4" s="34" t="n">
-        <v>33.37095815999876</v>
+        <v>33.37095815999879</v>
       </c>
       <c r="F4" s="34" t="n">
-        <v>49.92745519999966</v>
+        <v>49.92745519999962</v>
       </c>
       <c r="G4" s="44">
         <f>F4/E4-1</f>
@@ -5320,10 +5320,10 @@
         <v/>
       </c>
       <c r="E5" s="34" t="n">
-        <v>32.14602050999881</v>
+        <v>32.14602050999878</v>
       </c>
       <c r="F5" s="34" t="n">
-        <v>55.8190090899996</v>
+        <v>55.81900908999955</v>
       </c>
       <c r="G5" s="44">
         <f>F5/E5-1</f>
@@ -5347,10 +5347,10 @@
         <v/>
       </c>
       <c r="E6" s="34" t="n">
-        <v>61.26123198000229</v>
+        <v>61.26123198000237</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>78.0862114400001</v>
+        <v>78.08621144000027</v>
       </c>
       <c r="G6" s="44">
         <f>F6/E6-1</f>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>01.08 – 26.08.2025  vs  07.08 – 01.09.2026  (26 gün)</t>
+          <t>01.08 – 27.08.2025  vs  07.08 – 02.09.2026  (27 gün)</t>
         </is>
       </c>
       <c r="C10" s="48" t="n"/>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>adet +%34.6 · ciro +%67.6</t>
+          <t>adet +%34.2 · ciro +%66.0</t>
         </is>
       </c>
       <c r="C11" s="48" t="n"/>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="B14" s="51" t="inlineStr">
         <is>
-          <t>616.873 adet · 102.7 M TL</t>
+          <t>614.956 adet · 101.7 M TL</t>
         </is>
       </c>
       <c r="C14" s="48" t="n"/>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="B15" s="51" t="inlineStr">
         <is>
-          <t>133.374 adet · 24.6 M TL</t>
+          <t>131.456 adet · 23.6 M TL</t>
         </is>
       </c>
       <c r="C15" s="48" t="n"/>
@@ -5500,12 +5500,12 @@
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>Okul öncesi dalga — 2025 gerçekleşen (27.08 - 07.09.2025)</t>
+          <t>Okul öncesi dalga — 2025 gerçekleşen (28.08 - 07.09.2025)</t>
         </is>
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>430.919 adet · 56.8 M TL</t>
+          <t>412.212 adet · 54.1 M TL</t>
         </is>
       </c>
       <c r="C16" s="48" t="n"/>
@@ -5517,12 +5517,12 @@
     <row r="17">
       <c r="A17" s="50" t="inlineStr">
         <is>
-          <t>Okul öncesi dalga — 2026 beklenen (02.09 - 13.09.2026)</t>
+          <t>Okul öncesi dalga — 2026 beklenen (03.09 - 13.09.2026)</t>
         </is>
       </c>
       <c r="B17" s="51" t="inlineStr">
         <is>
-          <t>580.071 adet · 95.2 M TL</t>
+          <t>553.164 adet · 89.8 M TL</t>
         </is>
       </c>
       <c r="C17" s="48" t="n"/>
@@ -5534,7 +5534,7 @@
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Yöntem: 2026 günleri 2025'in 6 gün öncesine denk gelir (açılış 08.09.2025 → 14.09.2026). Hizalı 27 günde ölçülen büyüme (adet %34.6 · ciro %67.6) 2025 Ağustos toplamına uygulanarak kayma-arındırılmış Ağustos bulunur. VARSAYIM: talep kaybı yok, yalnız zamanlama kaydı. Bugünün verisi HARİÇ (eTip 100 gün içinde yeniden yazılır); son tam gün 01.09.2026.</t>
+          <t>Yöntem: 2026 günleri 2025'in 6 gün öncesine denk gelir (açılış 08.09.2025 → 14.09.2026). Hizalı 27 günde ölçülen büyüme (adet %34.2 · ciro %66.0) 2025 Ağustos toplamına uygulanarak kayma-arındırılmış Ağustos bulunur. VARSAYIM: talep kaybı yok, yalnız zamanlama kaydı. Bugünün verisi HARİÇ (eTip 100 gün içinde yeniden yazılır); son tam gün 02.09.2026.</t>
         </is>
       </c>
     </row>
@@ -5829,10 +5829,10 @@
         <v/>
       </c>
       <c r="E4" s="17" t="n">
-        <v>315972605.8798317</v>
+        <v>315972605.8798305</v>
       </c>
       <c r="F4" s="17" t="n">
-        <v>489364071.8499244</v>
+        <v>489364071.8499242</v>
       </c>
       <c r="G4" s="19">
         <f>F4/E4-1</f>

--- a/briefings/sezon-kadro-20260902/verimlilik-2026.xlsx
+++ b/briefings/sezon-kadro-20260902/verimlilik-2026.xlsx
@@ -224,7 +224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -312,6 +312,7 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1991,7 +1992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N57"/>
+  <dimension ref="A1:R77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2008,14 +2009,14 @@
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>Personel maliyeti ve ciro orani — ESAS PENCERE: Tem · referans: 01-07 ay (Oca–Tem), her iki yıl · uc POS magazasi (İst. Yolu · Özlüce · Fsm)</t>
+          <t>Personel maliyeti ve ciro orani — SEZON Tem–Eki (kiyas: Tem) · yil geneli: 01-07 ay (Oca–Tem), her iki yıl · uc POS magazasi (İst. Yolu · Özlüce · Fsm)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="59" t="inlineStr">
         <is>
-          <t>⚠ SEZON PENCERESİ EKSİK: Ağu ayı bordrosu henüz koşmadı (2026 yılı). Sezon karşılaştırması Tem ayı/ayları ile sınırlıdır; Ağustos bordrosu işlendiğinde bu blok kendiliğinden tamamlanır. Yıl geneli için «kümülatif» pencereye bakılır.</t>
+          <t>⚠ 2026 SEZONU HENÜZ TAMAMLANMADI. Sezon = Tem–Eki ayları; Ağu, Eyl, Eki ayı/ayları için bordro henüz işlenmedi (Ağustos bordrosu koşmadı, Eylül–Ekim daha gelmedi). Karşılaştırma tamamlanan ortak ay(lar) ile sınırlıdır: Tem. Geçen yılın TAM sezonu ayrıca referans olarak verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2293,7 @@
         <v>242487002.9100002</v>
       </c>
       <c r="F12" s="17" t="n">
-        <v>388687036.5200024</v>
+        <v>388687036.5200025</v>
       </c>
       <c r="G12" s="44">
         <f>F12/E12-1</f>
@@ -2400,7 +2401,7 @@
         <v>0.1284870034509182</v>
       </c>
       <c r="F16" s="62" t="n">
-        <v>0.1214791247887943</v>
+        <v>0.1214791247887942</v>
       </c>
       <c r="G16" s="63">
         <f>F16-E16</f>
@@ -2417,797 +2418,1381 @@
     <row r="19">
       <c r="A19" s="47" t="inlineStr">
         <is>
-          <t>AYLIK KIRILIM — uc POS magazasi (* = sezon ayi)</t>
+          <t>GECEN YILIN TAM SEZONU (2025, Tem–Eki) — 2026 sezonu tamamlaninca ayni pencerede kiyas</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="54" t="inlineStr">
-        <is>
-          <t>Ay</t>
-        </is>
-      </c>
-      <c r="B20" s="54" t="inlineStr">
-        <is>
-          <t>FTE 2025</t>
-        </is>
-      </c>
-      <c r="C20" s="54" t="inlineStr">
-        <is>
-          <t>FTE 2026</t>
-        </is>
-      </c>
-      <c r="D20" s="54" t="inlineStr">
-        <is>
-          <t>FTE Δ</t>
-        </is>
-      </c>
-      <c r="E20" s="54" t="inlineStr">
-        <is>
-          <t>Maliyet 2025</t>
-        </is>
-      </c>
-      <c r="F20" s="54" t="inlineStr">
-        <is>
-          <t>Maliyet 2026</t>
-        </is>
-      </c>
-      <c r="G20" s="54" t="inlineStr">
-        <is>
-          <t>Maliyet Δ</t>
-        </is>
-      </c>
-      <c r="H20" s="54" t="inlineStr">
-        <is>
-          <t>FM saat 2025</t>
-        </is>
-      </c>
-      <c r="I20" s="54" t="inlineStr">
-        <is>
-          <t>FM saat 2026</t>
-        </is>
-      </c>
-      <c r="J20" s="54" t="inlineStr">
-        <is>
-          <t>Oran 2025</t>
-        </is>
-      </c>
-      <c r="K20" s="54" t="inlineStr">
-        <is>
-          <t>Oran 2026</t>
-        </is>
-      </c>
-      <c r="L20" s="54" t="inlineStr">
-        <is>
-          <t>Kayit 2025</t>
-        </is>
-      </c>
-      <c r="M20" s="54" t="inlineStr">
-        <is>
-          <t>Kayit 2026</t>
-        </is>
-      </c>
-      <c r="N20" s="54" t="inlineStr">
-        <is>
-          <t>Ort. prim gunu 2026</t>
-        </is>
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>FTE (tam zaman esdeger)</t>
+        </is>
+      </c>
+      <c r="B20" s="34" t="n">
+        <v>458.7333333333333</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Oca</t>
+          <t xml:space="preserve">  — kadrolu FTE</t>
         </is>
       </c>
       <c r="B21" s="34" t="n">
-        <v>107.4666666666667</v>
-      </c>
-      <c r="C21" s="34" t="n">
-        <v>109.9333333333333</v>
-      </c>
-      <c r="D21" s="19">
-        <f>C21/B21-1</f>
-        <v/>
-      </c>
-      <c r="E21" s="17" t="n">
-        <v>4474024.3825</v>
-      </c>
-      <c r="F21" s="17" t="n">
-        <v>6217410.875</v>
-      </c>
-      <c r="G21" s="19">
-        <f>F21/E21-1</f>
-        <v/>
-      </c>
-      <c r="H21" s="34" t="n">
-        <v>620</v>
-      </c>
-      <c r="I21" s="34" t="n">
-        <v>727.5</v>
-      </c>
-      <c r="J21" s="42" t="n">
-        <v>0.1064043589756458</v>
-      </c>
-      <c r="K21" s="42" t="n">
-        <v>0.09342797291737971</v>
-      </c>
-      <c r="L21" s="17" t="n">
-        <v>117</v>
-      </c>
-      <c r="M21" s="17" t="n">
-        <v>121</v>
-      </c>
-      <c r="N21" s="34" t="n">
-        <v>27.25619834710744</v>
+        <v>382.0666666666667</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>Şub</t>
+          <t xml:space="preserve">  — sezonluk FTE</t>
         </is>
       </c>
       <c r="B22" s="34" t="n">
-        <v>100.7</v>
-      </c>
-      <c r="C22" s="34" t="n">
-        <v>110.9333333333333</v>
-      </c>
-      <c r="D22" s="19">
-        <f>C22/B22-1</f>
-        <v/>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>4224075.9997</v>
-      </c>
-      <c r="F22" s="17" t="n">
-        <v>6437880.404999999</v>
-      </c>
-      <c r="G22" s="19">
-        <f>F22/E22-1</f>
-        <v/>
-      </c>
-      <c r="H22" s="34" t="n">
-        <v>46</v>
-      </c>
-      <c r="I22" s="34" t="n">
-        <v>65</v>
-      </c>
-      <c r="J22" s="42" t="n">
-        <v>0.1097139082641927</v>
-      </c>
-      <c r="K22" s="42" t="n">
-        <v>0.1128809843841212</v>
-      </c>
-      <c r="L22" s="17" t="n">
-        <v>116</v>
-      </c>
-      <c r="M22" s="17" t="n">
-        <v>123</v>
-      </c>
-      <c r="N22" s="34" t="n">
-        <v>27.05691056910569</v>
+        <v>76.66666666666667</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="B23" s="34" t="n">
-        <v>102.8</v>
-      </c>
-      <c r="C23" s="34" t="n">
-        <v>112.5666666666667</v>
-      </c>
-      <c r="D23" s="19">
-        <f>C23/B23-1</f>
-        <v/>
-      </c>
-      <c r="E23" s="17" t="n">
-        <v>4600008.1925</v>
-      </c>
-      <c r="F23" s="17" t="n">
-        <v>6842756.383199999</v>
-      </c>
-      <c r="G23" s="19">
-        <f>F23/E23-1</f>
-        <v/>
-      </c>
-      <c r="H23" s="34" t="n">
-        <v>1361.5</v>
-      </c>
-      <c r="I23" s="34" t="n">
-        <v>1681</v>
-      </c>
-      <c r="J23" s="42" t="n">
-        <v>0.1388245899802142</v>
-      </c>
-      <c r="K23" s="42" t="n">
-        <v>0.1170292741229824</v>
-      </c>
-      <c r="L23" s="17" t="n">
-        <v>112</v>
-      </c>
-      <c r="M23" s="17" t="n">
-        <v>119</v>
-      </c>
-      <c r="N23" s="34" t="n">
-        <v>28.3781512605042</v>
+          <t>Personel maliyeti</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="n">
+        <v>21304639.3619</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>Nis</t>
-        </is>
-      </c>
-      <c r="B24" s="34" t="n">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="C24" s="34" t="n">
-        <v>110.0333333333333</v>
-      </c>
-      <c r="D24" s="19">
-        <f>C24/B24-1</f>
-        <v/>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>4282833.829500001</v>
-      </c>
-      <c r="F24" s="17" t="n">
-        <v>7013152.140000001</v>
-      </c>
-      <c r="G24" s="19">
-        <f>F24/E24-1</f>
-        <v/>
-      </c>
-      <c r="H24" s="34" t="n">
-        <v>746</v>
-      </c>
-      <c r="I24" s="34" t="n">
-        <v>786.5</v>
-      </c>
-      <c r="J24" s="42" t="n">
-        <v>0.1150222758867225</v>
-      </c>
-      <c r="K24" s="42" t="n">
-        <v>0.1323692598350995</v>
-      </c>
-      <c r="L24" s="17" t="n">
-        <v>114</v>
-      </c>
-      <c r="M24" s="17" t="n">
-        <v>124</v>
-      </c>
-      <c r="N24" s="34" t="n">
-        <v>26.62096774193548</v>
+          <t>Ciro (KDV haric)</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n">
+        <v>602003224.0700146</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="B25" s="34" t="n">
-        <v>93.86666666666667</v>
-      </c>
-      <c r="C25" s="34" t="n">
-        <v>112.0333333333333</v>
-      </c>
-      <c r="D25" s="19">
-        <f>C25/B25-1</f>
-        <v/>
-      </c>
-      <c r="E25" s="17" t="n">
-        <v>4743646.205499999</v>
-      </c>
-      <c r="F25" s="17" t="n">
-        <v>7453386.71</v>
-      </c>
-      <c r="G25" s="19">
-        <f>F25/E25-1</f>
-        <v/>
-      </c>
-      <c r="H25" s="34" t="n">
-        <v>1144.5</v>
-      </c>
-      <c r="I25" s="34" t="n">
-        <v>3553.01</v>
-      </c>
-      <c r="J25" s="42" t="n">
-        <v>0.1596487262755276</v>
-      </c>
-      <c r="K25" s="42" t="n">
-        <v>0.1384843301196873</v>
-      </c>
-      <c r="L25" s="17" t="n">
-        <v>107</v>
-      </c>
-      <c r="M25" s="17" t="n">
-        <v>124</v>
-      </c>
-      <c r="N25" s="34" t="n">
-        <v>27.10483870967742</v>
+          <t>Maliyet / ciro orani</t>
+        </is>
+      </c>
+      <c r="B25" s="65" t="n">
+        <v>0.0353895768495456</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>Haz</t>
+          <t>Fazla mesai (saat)</t>
         </is>
       </c>
       <c r="B26" s="34" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="C26" s="34" t="n">
-        <v>108.2333333333333</v>
-      </c>
-      <c r="D26" s="19">
-        <f>C26/B26-1</f>
-        <v/>
-      </c>
-      <c r="E26" s="17" t="n">
-        <v>4445571.3025</v>
-      </c>
-      <c r="F26" s="17" t="n">
-        <v>6470405.039999999</v>
-      </c>
-      <c r="G26" s="19">
-        <f>F26/E26-1</f>
-        <v/>
-      </c>
-      <c r="H26" s="34" t="n">
-        <v>1767.5</v>
-      </c>
-      <c r="I26" s="34" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="J26" s="42" t="n">
-        <v>0.1425960097198796</v>
-      </c>
-      <c r="K26" s="42" t="n">
-        <v>0.1392147694382981</v>
-      </c>
-      <c r="L26" s="17" t="n">
-        <v>105</v>
-      </c>
-      <c r="M26" s="17" t="n">
-        <v>118</v>
-      </c>
-      <c r="N26" s="34" t="n">
-        <v>27.51694915254237</v>
+        <v>7393</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="inlineStr">
-        <is>
-          <t>Tem*</t>
-        </is>
-      </c>
-      <c r="B27" s="65" t="n">
-        <v>97.13333333333333</v>
-      </c>
-      <c r="C27" s="65" t="n">
-        <v>112.4333333333333</v>
-      </c>
-      <c r="D27" s="19">
-        <f>C27/B27-1</f>
-        <v/>
-      </c>
-      <c r="E27" s="66" t="n">
-        <v>4386268.467500001</v>
-      </c>
-      <c r="F27" s="66" t="n">
-        <v>6782369.460000002</v>
-      </c>
-      <c r="G27" s="19">
-        <f>F27/E27-1</f>
-        <v/>
-      </c>
-      <c r="H27" s="65" t="n">
-        <v>643</v>
-      </c>
-      <c r="I27" s="65" t="n">
-        <v>783</v>
-      </c>
-      <c r="J27" s="42" t="n">
-        <v>0.1429703378344554</v>
-      </c>
-      <c r="K27" s="42" t="n">
-        <v>0.1271160646389757</v>
-      </c>
-      <c r="L27" s="66" t="n">
-        <v>110</v>
-      </c>
-      <c r="M27" s="66" t="n">
-        <v>127</v>
-      </c>
-      <c r="N27" s="65" t="n">
-        <v>26.55905511811024</v>
+      <c r="A27" s="64" t="inlineStr">
+        <is>
+          <t>SEZONUN SEKLI: sezonda ciro birkac kat artarken kadro ayni oranda artmaz -&gt; maliyet/ciro orani sezon aylarinda sezon disina gore COK dusuktur. Bu yuzden sezon ile yil-geneli oranlari BIRBIRIYLE kiyaslanmaz.</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="47" t="inlineStr">
         <is>
-          <t>SUBE BAZINDA MALIYET VE FAZLA MESAI (bes magaza)</t>
+          <t>KADROLU / SEZONLUK AYRIMI — uc POS magazasi</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="54" t="inlineStr">
         <is>
-          <t>Sube</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="B30" s="54" t="inlineStr">
         <is>
-          <t>FTE 2025</t>
+          <t>SEZON FTE 2025</t>
         </is>
       </c>
       <c r="C30" s="54" t="inlineStr">
         <is>
-          <t>FTE 2026</t>
+          <t>SEZON FTE 2026</t>
         </is>
       </c>
       <c r="D30" s="54" t="inlineStr">
         <is>
-          <t>Maliyet 2025</t>
+          <t>SEZON maliyet 2025</t>
         </is>
       </c>
       <c r="E30" s="54" t="inlineStr">
         <is>
-          <t>Maliyet 2026</t>
+          <t>SEZON maliyet 2026</t>
         </is>
       </c>
       <c r="F30" s="54" t="inlineStr">
         <is>
-          <t>Maliyet Δ</t>
+          <t>FTE basi maliyet 2026</t>
         </is>
       </c>
       <c r="G30" s="54" t="inlineStr">
         <is>
-          <t>FM saat 2025</t>
+          <t>KUM. FTE 2025</t>
         </is>
       </c>
       <c r="H30" s="54" t="inlineStr">
         <is>
-          <t>FM saat 2026</t>
+          <t>KUM. FTE 2026</t>
         </is>
       </c>
       <c r="I30" s="54" t="inlineStr">
         <is>
-          <t>FM tutar 2026</t>
+          <t>KUM. maliyet 2026</t>
+        </is>
+      </c>
+      <c r="J30" s="54" t="inlineStr">
+        <is>
+          <t>SEZON FM saat 2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>Fsm</t>
+          <t>Kadrolu</t>
         </is>
       </c>
       <c r="B31" s="34" t="n">
-        <v>238.3333333333333</v>
+        <v>93.76666666666667</v>
       </c>
       <c r="C31" s="34" t="n">
-        <v>247.8</v>
+        <v>110.9</v>
       </c>
       <c r="D31" s="17" t="n">
-        <v>10505479.13700001</v>
+        <v>4266773.578500001</v>
       </c>
       <c r="E31" s="17" t="n">
-        <v>15336984.19000001</v>
-      </c>
-      <c r="F31" s="19">
-        <f>E31/D31-1</f>
-        <v/>
+        <v>6711440.170000002</v>
+      </c>
+      <c r="F31" s="17" t="n">
+        <v>60517.94562669072</v>
       </c>
       <c r="G31" s="34" t="n">
-        <v>2010</v>
+        <v>693.7</v>
       </c>
       <c r="H31" s="34" t="n">
-        <v>2084</v>
+        <v>755.5333333333333</v>
       </c>
       <c r="I31" s="17" t="n">
-        <v>323297.7100000001</v>
+        <v>46178811.43319999</v>
+      </c>
+      <c r="J31" s="34" t="n">
+        <v>775.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
         <is>
-          <t>Heykel</t>
+          <t>Sezonluk</t>
         </is>
       </c>
       <c r="B32" s="34" t="n">
-        <v>198.8666666666667</v>
+        <v>3.366666666666667</v>
       </c>
       <c r="C32" s="34" t="n">
-        <v>196.3</v>
+        <v>1.533333333333333</v>
       </c>
       <c r="D32" s="17" t="n">
-        <v>8934645.077999998</v>
+        <v>119494.889</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>12368114.50640001</v>
-      </c>
-      <c r="F32" s="19">
-        <f>E32/D32-1</f>
-        <v/>
+        <v>70929.29000000001</v>
+      </c>
+      <c r="F32" s="17" t="n">
+        <v>46258.23260869565</v>
       </c>
       <c r="G32" s="34" t="n">
-        <v>1608</v>
+        <v>3.366666666666667</v>
       </c>
       <c r="H32" s="34" t="n">
-        <v>1606.5</v>
+        <v>20.63333333333333</v>
       </c>
       <c r="I32" s="17" t="n">
-        <v>252249.6700000001</v>
+        <v>1038549.58</v>
+      </c>
+      <c r="J32" s="34" t="n">
+        <v>7.5</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>Özlüce</t>
-        </is>
-      </c>
-      <c r="B33" s="34" t="n">
-        <v>264.6333333333333</v>
-      </c>
-      <c r="C33" s="34" t="n">
-        <v>290.9</v>
-      </c>
-      <c r="D33" s="17" t="n">
-        <v>12022817.438</v>
-      </c>
-      <c r="E33" s="17" t="n">
-        <v>17601765.7182</v>
-      </c>
-      <c r="F33" s="19">
-        <f>E33/D33-1</f>
-        <v/>
-      </c>
-      <c r="G33" s="34" t="n">
-        <v>2518</v>
-      </c>
-      <c r="H33" s="34" t="n">
-        <v>3144</v>
-      </c>
-      <c r="I33" s="17" t="n">
-        <v>499150.3099999993</v>
+      <c r="A33" s="36" t="inlineStr">
+        <is>
+          <t>TOPLAM</t>
+        </is>
+      </c>
+      <c r="B33" s="38" t="n">
+        <v>97.13333333333333</v>
+      </c>
+      <c r="C33" s="38" t="n">
+        <v>112.4333333333333</v>
+      </c>
+      <c r="D33" s="21" t="n">
+        <v>4386268.467500001</v>
+      </c>
+      <c r="E33" s="21" t="n">
+        <v>6782369.460000002</v>
+      </c>
+      <c r="F33" s="21" t="n">
+        <v>60323.47577823897</v>
+      </c>
+      <c r="G33" s="38" t="n">
+        <v>697.0666666666666</v>
+      </c>
+      <c r="H33" s="38" t="n">
+        <v>776.1666666666666</v>
+      </c>
+      <c r="I33" s="21" t="n">
+        <v>47217361.01320001</v>
+      </c>
+      <c r="J33" s="38" t="n">
+        <v>783</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
-        <is>
-          <t>İst. Yolu</t>
-        </is>
-      </c>
-      <c r="B34" s="34" t="n">
-        <v>194.1</v>
-      </c>
-      <c r="C34" s="34" t="n">
-        <v>237.4666666666667</v>
-      </c>
-      <c r="D34" s="17" t="n">
-        <v>8628131.804699995</v>
-      </c>
-      <c r="E34" s="17" t="n">
-        <v>14278611.10500001</v>
-      </c>
-      <c r="F34" s="19">
-        <f>E34/D34-1</f>
-        <v/>
-      </c>
-      <c r="G34" s="34" t="n">
-        <v>1800.5</v>
-      </c>
-      <c r="H34" s="34" t="n">
-        <v>2400.51</v>
-      </c>
-      <c r="I34" s="17" t="n">
-        <v>361480.5099999998</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="16" t="inlineStr">
-        <is>
-          <t>Şura</t>
-        </is>
-      </c>
-      <c r="B35" s="34" t="n">
-        <v>60.06666666666667</v>
-      </c>
-      <c r="C35" s="34" t="n">
-        <v>76.86666666666666</v>
-      </c>
-      <c r="D35" s="17" t="n">
-        <v>3016259.480500001</v>
-      </c>
-      <c r="E35" s="17" t="n">
-        <v>5701231.434999999</v>
-      </c>
-      <c r="F35" s="19">
-        <f>E35/D35-1</f>
-        <v/>
-      </c>
-      <c r="G35" s="34" t="n">
-        <v>277</v>
-      </c>
-      <c r="H35" s="34" t="n">
-        <v>212.5</v>
-      </c>
-      <c r="I35" s="17" t="n">
-        <v>37862.25999999999</v>
+      <c r="A34" s="64" t="inlineStr">
+        <is>
+          <t>⚠ Segment ayraci `vw_PersonelDepartman.Kadro` = BUGUNKU durum (tarihlenmiyor): gecmiste sezonluk calisip kadroya gecen kisi GECMIS ayda da KADROLU gorunur. Ayrica sezonluk alimin buyuk kismi AGUSTOS'ta; Agustos bordrosu islenince sezonluk agirligi gercek seviyesine cikar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="47" t="inlineStr">
+        <is>
+          <t>AYLIK KIRILIM — uc POS magazasi (* = sezon ayi Tem–Eki; 2026 icin bordrosu kosmamis aylar bos)</t>
+        </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="47" t="inlineStr">
-        <is>
-          <t>FAZLA MESAI VE YASAL SINIR (4857 s.K. m.41 — yillik 270 saat)</t>
+      <c r="A37" s="54" t="inlineStr">
+        <is>
+          <t>Ay</t>
+        </is>
+      </c>
+      <c r="B37" s="54" t="inlineStr">
+        <is>
+          <t>FTE 2025</t>
+        </is>
+      </c>
+      <c r="C37" s="54" t="inlineStr">
+        <is>
+          <t>FTE 2026</t>
+        </is>
+      </c>
+      <c r="D37" s="54" t="inlineStr">
+        <is>
+          <t>FTE Δ</t>
+        </is>
+      </c>
+      <c r="E37" s="54" t="inlineStr">
+        <is>
+          <t>Maliyet 2025</t>
+        </is>
+      </c>
+      <c r="F37" s="54" t="inlineStr">
+        <is>
+          <t>Maliyet 2026</t>
+        </is>
+      </c>
+      <c r="G37" s="54" t="inlineStr">
+        <is>
+          <t>Maliyet Δ</t>
+        </is>
+      </c>
+      <c r="H37" s="54" t="inlineStr">
+        <is>
+          <t>FM saat 2025</t>
+        </is>
+      </c>
+      <c r="I37" s="54" t="inlineStr">
+        <is>
+          <t>FM saat 2026</t>
+        </is>
+      </c>
+      <c r="J37" s="54" t="inlineStr">
+        <is>
+          <t>Oran 2025</t>
+        </is>
+      </c>
+      <c r="K37" s="54" t="inlineStr">
+        <is>
+          <t>Oran 2026</t>
+        </is>
+      </c>
+      <c r="L37" s="54" t="inlineStr">
+        <is>
+          <t>Kayit 2025</t>
+        </is>
+      </c>
+      <c r="M37" s="54" t="inlineStr">
+        <is>
+          <t>Kayit 2026</t>
+        </is>
+      </c>
+      <c r="N37" s="54" t="inlineStr">
+        <is>
+          <t>Ort. prim gunu 2026</t>
+        </is>
+      </c>
+      <c r="O37" s="54" t="inlineStr">
+        <is>
+          <t>Kadrolu FTE 2025</t>
+        </is>
+      </c>
+      <c r="P37" s="54" t="inlineStr">
+        <is>
+          <t>Kadrolu FTE 2026</t>
+        </is>
+      </c>
+      <c r="Q37" s="54" t="inlineStr">
+        <is>
+          <t>Sezonluk FTE 2025</t>
+        </is>
+      </c>
+      <c r="R37" s="54" t="inlineStr">
+        <is>
+          <t>Sezonluk FTE 2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
         <is>
-          <t>Fiili FM saat 2025 (uc POS)</t>
+          <t>Oca</t>
         </is>
       </c>
       <c r="B38" s="34" t="n">
-        <v>643</v>
+        <v>107.4666666666667</v>
+      </c>
+      <c r="C38" s="34" t="n">
+        <v>109.9333333333333</v>
+      </c>
+      <c r="D38" s="19">
+        <f>C38/B38-1</f>
+        <v/>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>4474024.3825</v>
+      </c>
+      <c r="F38" s="17" t="n">
+        <v>6217410.874999999</v>
+      </c>
+      <c r="G38" s="19">
+        <f>F38/E38-1</f>
+        <v/>
+      </c>
+      <c r="H38" s="34" t="n">
+        <v>620</v>
+      </c>
+      <c r="I38" s="34" t="n">
+        <v>727.5</v>
+      </c>
+      <c r="J38" s="42" t="n">
+        <v>0.1064043589756458</v>
+      </c>
+      <c r="K38" s="42" t="n">
+        <v>0.09342797291737968</v>
+      </c>
+      <c r="L38" s="17" t="n">
+        <v>117</v>
+      </c>
+      <c r="M38" s="17" t="n">
+        <v>121</v>
+      </c>
+      <c r="N38" s="34" t="n">
+        <v>27.25619834710744</v>
+      </c>
+      <c r="O38" s="34" t="n">
+        <v>107.4666666666667</v>
+      </c>
+      <c r="P38" s="34" t="n">
+        <v>105.9666666666667</v>
+      </c>
+      <c r="Q38" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="34" t="n">
+        <v>3.966666666666667</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>Fiili FM saat 2026 (uc POS)</t>
+          <t>Şub</t>
         </is>
       </c>
       <c r="B39" s="34" t="n">
-        <v>783</v>
+        <v>100.7</v>
+      </c>
+      <c r="C39" s="34" t="n">
+        <v>110.9333333333333</v>
+      </c>
+      <c r="D39" s="19">
+        <f>C39/B39-1</f>
+        <v/>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>4224075.9997</v>
+      </c>
+      <c r="F39" s="17" t="n">
+        <v>6437880.404999999</v>
+      </c>
+      <c r="G39" s="19">
+        <f>F39/E39-1</f>
+        <v/>
+      </c>
+      <c r="H39" s="34" t="n">
+        <v>46</v>
+      </c>
+      <c r="I39" s="34" t="n">
+        <v>65</v>
+      </c>
+      <c r="J39" s="42" t="n">
+        <v>0.1097139082641927</v>
+      </c>
+      <c r="K39" s="42" t="n">
+        <v>0.1128809843841212</v>
+      </c>
+      <c r="L39" s="17" t="n">
+        <v>116</v>
+      </c>
+      <c r="M39" s="17" t="n">
+        <v>123</v>
+      </c>
+      <c r="N39" s="34" t="n">
+        <v>27.05691056910569</v>
+      </c>
+      <c r="O39" s="34" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="P39" s="34" t="n">
+        <v>107.0333333333333</v>
+      </c>
+      <c r="Q39" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" s="34" t="n">
+        <v>3.9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
         <is>
-          <t>Kisi basi YILLIK FM 2025 (saat)</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="B40" s="34" t="n">
-        <v>79.43719972546329</v>
+        <v>102.8</v>
+      </c>
+      <c r="C40" s="34" t="n">
+        <v>112.5666666666667</v>
+      </c>
+      <c r="D40" s="19">
+        <f>C40/B40-1</f>
+        <v/>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>4600008.1925</v>
+      </c>
+      <c r="F40" s="17" t="n">
+        <v>6842756.383199998</v>
+      </c>
+      <c r="G40" s="19">
+        <f>F40/E40-1</f>
+        <v/>
+      </c>
+      <c r="H40" s="34" t="n">
+        <v>1361.5</v>
+      </c>
+      <c r="I40" s="34" t="n">
+        <v>1681</v>
+      </c>
+      <c r="J40" s="42" t="n">
+        <v>0.1388245899802142</v>
+      </c>
+      <c r="K40" s="42" t="n">
+        <v>0.1170292741229823</v>
+      </c>
+      <c r="L40" s="17" t="n">
+        <v>112</v>
+      </c>
+      <c r="M40" s="17" t="n">
+        <v>119</v>
+      </c>
+      <c r="N40" s="34" t="n">
+        <v>28.3781512605042</v>
+      </c>
+      <c r="O40" s="34" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="P40" s="34" t="n">
+        <v>108.5666666666667</v>
+      </c>
+      <c r="Q40" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="34" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>Kisi basi YILLIK FM 2026 (saat)</t>
+          <t>Nis</t>
         </is>
       </c>
       <c r="B41" s="34" t="n">
-        <v>83.56952268010673</v>
+        <v>97.59999999999999</v>
+      </c>
+      <c r="C41" s="34" t="n">
+        <v>110.0333333333333</v>
+      </c>
+      <c r="D41" s="19">
+        <f>C41/B41-1</f>
+        <v/>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>4282833.829500001</v>
+      </c>
+      <c r="F41" s="17" t="n">
+        <v>7013152.140000001</v>
+      </c>
+      <c r="G41" s="19">
+        <f>F41/E41-1</f>
+        <v/>
+      </c>
+      <c r="H41" s="34" t="n">
+        <v>746</v>
+      </c>
+      <c r="I41" s="34" t="n">
+        <v>786.5</v>
+      </c>
+      <c r="J41" s="42" t="n">
+        <v>0.1150222758867225</v>
+      </c>
+      <c r="K41" s="42" t="n">
+        <v>0.1323692598350995</v>
+      </c>
+      <c r="L41" s="17" t="n">
+        <v>114</v>
+      </c>
+      <c r="M41" s="17" t="n">
+        <v>124</v>
+      </c>
+      <c r="N41" s="34" t="n">
+        <v>26.62096774193548</v>
+      </c>
+      <c r="O41" s="34" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="P41" s="34" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="Q41" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="34" t="n">
+        <v>3.133333333333333</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="16" t="inlineStr">
         <is>
-          <t>Yillik sinir hizinda kisi-ay 2025</t>
-        </is>
-      </c>
-      <c r="B42" s="17" t="n">
-        <v>1</v>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="B42" s="34" t="n">
+        <v>93.86666666666667</v>
+      </c>
+      <c r="C42" s="34" t="n">
+        <v>112.0333333333333</v>
+      </c>
+      <c r="D42" s="19">
+        <f>C42/B42-1</f>
+        <v/>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>4743646.205499999</v>
+      </c>
+      <c r="F42" s="17" t="n">
+        <v>7453386.71</v>
+      </c>
+      <c r="G42" s="19">
+        <f>F42/E42-1</f>
+        <v/>
+      </c>
+      <c r="H42" s="34" t="n">
+        <v>1144.5</v>
+      </c>
+      <c r="I42" s="34" t="n">
+        <v>3553.01</v>
+      </c>
+      <c r="J42" s="42" t="n">
+        <v>0.1596487262755276</v>
+      </c>
+      <c r="K42" s="42" t="n">
+        <v>0.1384843301196873</v>
+      </c>
+      <c r="L42" s="17" t="n">
+        <v>107</v>
+      </c>
+      <c r="M42" s="17" t="n">
+        <v>124</v>
+      </c>
+      <c r="N42" s="34" t="n">
+        <v>27.10483870967742</v>
+      </c>
+      <c r="O42" s="34" t="n">
+        <v>93.86666666666667</v>
+      </c>
+      <c r="P42" s="34" t="n">
+        <v>109.1666666666667</v>
+      </c>
+      <c r="Q42" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" s="34" t="n">
+        <v>2.866666666666667</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
         <is>
-          <t>Yillik sinir hizinda kisi-ay 2026</t>
-        </is>
-      </c>
-      <c r="B43" s="17" t="n">
-        <v>2</v>
+          <t>Haz</t>
+        </is>
+      </c>
+      <c r="B43" s="34" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="C43" s="34" t="n">
+        <v>108.2333333333333</v>
+      </c>
+      <c r="D43" s="19">
+        <f>C43/B43-1</f>
+        <v/>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>4445571.3025</v>
+      </c>
+      <c r="F43" s="17" t="n">
+        <v>6470405.039999998</v>
+      </c>
+      <c r="G43" s="19">
+        <f>F43/E43-1</f>
+        <v/>
+      </c>
+      <c r="H43" s="34" t="n">
+        <v>1767.5</v>
+      </c>
+      <c r="I43" s="34" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="J43" s="42" t="n">
+        <v>0.1425960097198796</v>
+      </c>
+      <c r="K43" s="42" t="n">
+        <v>0.139214769438298</v>
+      </c>
+      <c r="L43" s="17" t="n">
+        <v>105</v>
+      </c>
+      <c r="M43" s="17" t="n">
+        <v>118</v>
+      </c>
+      <c r="N43" s="34" t="n">
+        <v>27.51694915254237</v>
+      </c>
+      <c r="O43" s="34" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="P43" s="34" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q43" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" s="34" t="n">
+        <v>1.233333333333333</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="16" t="inlineStr">
-        <is>
-          <t>VARSAYIM: kadro 2025 seviyesinde kalsaydi eksik kisi-ay</t>
-        </is>
-      </c>
-      <c r="B44" s="17" t="n">
-        <v>17</v>
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>Tem*</t>
+        </is>
+      </c>
+      <c r="B44" s="66" t="n">
+        <v>97.13333333333333</v>
+      </c>
+      <c r="C44" s="66" t="n">
+        <v>112.4333333333333</v>
+      </c>
+      <c r="D44" s="19">
+        <f>C44/B44-1</f>
+        <v/>
+      </c>
+      <c r="E44" s="67" t="n">
+        <v>4386268.467500001</v>
+      </c>
+      <c r="F44" s="67" t="n">
+        <v>6782369.460000002</v>
+      </c>
+      <c r="G44" s="19">
+        <f>F44/E44-1</f>
+        <v/>
+      </c>
+      <c r="H44" s="66" t="n">
+        <v>643</v>
+      </c>
+      <c r="I44" s="66" t="n">
+        <v>783</v>
+      </c>
+      <c r="J44" s="42" t="n">
+        <v>0.1429703378344554</v>
+      </c>
+      <c r="K44" s="42" t="n">
+        <v>0.1271160646389757</v>
+      </c>
+      <c r="L44" s="67" t="n">
+        <v>110</v>
+      </c>
+      <c r="M44" s="67" t="n">
+        <v>127</v>
+      </c>
+      <c r="N44" s="66" t="n">
+        <v>26.55905511811024</v>
+      </c>
+      <c r="O44" s="66" t="n">
+        <v>93.76666666666667</v>
+      </c>
+      <c r="P44" s="66" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="Q44" s="66" t="n">
+        <v>3.366666666666667</v>
+      </c>
+      <c r="R44" s="66" t="n">
+        <v>1.533333333333333</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="inlineStr">
-        <is>
-          <t>VARSAYIM: gereken EK fazla mesai (saat)</t>
-        </is>
-      </c>
-      <c r="B45" s="34" t="n">
-        <v>2983.500000000002</v>
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>Ağu*</t>
+        </is>
+      </c>
+      <c r="B45" s="66" t="n">
+        <v>120.6333333333333</v>
+      </c>
+      <c r="C45" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D45" s="19">
+        <f>C45/B45-1</f>
+        <v/>
+      </c>
+      <c r="E45" s="67" t="n">
+        <v>5442547.3939</v>
+      </c>
+      <c r="F45" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="19">
+        <f>F45/E45-1</f>
+        <v/>
+      </c>
+      <c r="H45" s="66" t="n">
+        <v>2139.5</v>
+      </c>
+      <c r="I45" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J45" s="42" t="n">
+        <v>0.02912397700580437</v>
+      </c>
+      <c r="K45" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L45" s="67" t="n">
+        <v>152</v>
+      </c>
+      <c r="M45" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N45" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O45" s="66" t="n">
+        <v>94.13333333333334</v>
+      </c>
+      <c r="P45" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q45" s="66" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="R45" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>VARSAYIM: kisi basi YILLIK FM (saat)</t>
-        </is>
-      </c>
-      <c r="B46" s="67" t="n">
-        <v>465.3191489361705</v>
+          <t>Eyl*</t>
+        </is>
+      </c>
+      <c r="B46" s="66" t="n">
+        <v>132.8333333333333</v>
+      </c>
+      <c r="C46" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D46" s="19">
+        <f>C46/B46-1</f>
+        <v/>
+      </c>
+      <c r="E46" s="67" t="n">
+        <v>6568880.7995</v>
+      </c>
+      <c r="F46" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="19">
+        <f>F46/E46-1</f>
+        <v/>
+      </c>
+      <c r="H46" s="66" t="n">
+        <v>3495</v>
+      </c>
+      <c r="I46" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J46" s="42" t="n">
+        <v>0.02098348810480835</v>
+      </c>
+      <c r="K46" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L46" s="67" t="n">
+        <v>154</v>
+      </c>
+      <c r="M46" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N46" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O46" s="66" t="n">
+        <v>95.76666666666667</v>
+      </c>
+      <c r="P46" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q46" s="66" t="n">
+        <v>37.06666666666666</v>
+      </c>
+      <c r="R46" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
+          <t>Eki*</t>
+        </is>
+      </c>
+      <c r="B47" s="66" t="n">
+        <v>108.1333333333333</v>
+      </c>
+      <c r="C47" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D47" s="19">
+        <f>C47/B47-1</f>
+        <v/>
+      </c>
+      <c r="E47" s="67" t="n">
+        <v>4906942.701</v>
+      </c>
+      <c r="F47" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="19">
+        <f>F47/E47-1</f>
+        <v/>
+      </c>
+      <c r="H47" s="66" t="n">
+        <v>1115.5</v>
+      </c>
+      <c r="I47" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J47" s="42" t="n">
+        <v>0.06872611463187885</v>
+      </c>
+      <c r="K47" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L47" s="67" t="n">
+        <v>122</v>
+      </c>
+      <c r="M47" s="67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N47" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O47" s="66" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="P47" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q47" s="66" t="n">
+        <v>9.733333333333333</v>
+      </c>
+      <c r="R47" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="47" t="inlineStr">
+        <is>
+          <t>SUBE BAZINDA MALIYET VE FAZLA MESAI (bes magaza)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="54" t="inlineStr">
+        <is>
+          <t>Sube</t>
+        </is>
+      </c>
+      <c r="B50" s="54" t="inlineStr">
+        <is>
+          <t>FTE 2025</t>
+        </is>
+      </c>
+      <c r="C50" s="54" t="inlineStr">
+        <is>
+          <t>FTE 2026</t>
+        </is>
+      </c>
+      <c r="D50" s="54" t="inlineStr">
+        <is>
+          <t>Maliyet 2025</t>
+        </is>
+      </c>
+      <c r="E50" s="54" t="inlineStr">
+        <is>
+          <t>Maliyet 2026</t>
+        </is>
+      </c>
+      <c r="F50" s="54" t="inlineStr">
+        <is>
+          <t>Maliyet Δ</t>
+        </is>
+      </c>
+      <c r="G50" s="54" t="inlineStr">
+        <is>
+          <t>FM saat 2025</t>
+        </is>
+      </c>
+      <c r="H50" s="54" t="inlineStr">
+        <is>
+          <t>FM saat 2026</t>
+        </is>
+      </c>
+      <c r="I50" s="54" t="inlineStr">
+        <is>
+          <t>FM tutar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>Fsm</t>
+        </is>
+      </c>
+      <c r="B51" s="34" t="n">
+        <v>238.3333333333333</v>
+      </c>
+      <c r="C51" s="34" t="n">
+        <v>247.8</v>
+      </c>
+      <c r="D51" s="17" t="n">
+        <v>10505479.13700001</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>15336984.19000001</v>
+      </c>
+      <c r="F51" s="19">
+        <f>E51/D51-1</f>
+        <v/>
+      </c>
+      <c r="G51" s="34" t="n">
+        <v>2010</v>
+      </c>
+      <c r="H51" s="34" t="n">
+        <v>2084</v>
+      </c>
+      <c r="I51" s="17" t="n">
+        <v>323297.7100000001</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>Heykel</t>
+        </is>
+      </c>
+      <c r="B52" s="34" t="n">
+        <v>198.8666666666667</v>
+      </c>
+      <c r="C52" s="34" t="n">
+        <v>196.3</v>
+      </c>
+      <c r="D52" s="17" t="n">
+        <v>8934645.077999998</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>12368114.50640001</v>
+      </c>
+      <c r="F52" s="19">
+        <f>E52/D52-1</f>
+        <v/>
+      </c>
+      <c r="G52" s="34" t="n">
+        <v>1608</v>
+      </c>
+      <c r="H52" s="34" t="n">
+        <v>1606.5</v>
+      </c>
+      <c r="I52" s="17" t="n">
+        <v>252249.6700000001</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>Özlüce</t>
+        </is>
+      </c>
+      <c r="B53" s="34" t="n">
+        <v>264.6333333333333</v>
+      </c>
+      <c r="C53" s="34" t="n">
+        <v>290.9</v>
+      </c>
+      <c r="D53" s="17" t="n">
+        <v>12022817.438</v>
+      </c>
+      <c r="E53" s="17" t="n">
+        <v>17601765.7182</v>
+      </c>
+      <c r="F53" s="19">
+        <f>E53/D53-1</f>
+        <v/>
+      </c>
+      <c r="G53" s="34" t="n">
+        <v>2518</v>
+      </c>
+      <c r="H53" s="34" t="n">
+        <v>3144</v>
+      </c>
+      <c r="I53" s="17" t="n">
+        <v>499150.3099999993</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="16" t="inlineStr">
+        <is>
+          <t>İst. Yolu</t>
+        </is>
+      </c>
+      <c r="B54" s="34" t="n">
+        <v>194.1</v>
+      </c>
+      <c r="C54" s="34" t="n">
+        <v>237.4666666666667</v>
+      </c>
+      <c r="D54" s="17" t="n">
+        <v>8628131.804699995</v>
+      </c>
+      <c r="E54" s="17" t="n">
+        <v>14278611.10500001</v>
+      </c>
+      <c r="F54" s="19">
+        <f>E54/D54-1</f>
+        <v/>
+      </c>
+      <c r="G54" s="34" t="n">
+        <v>1800.5</v>
+      </c>
+      <c r="H54" s="34" t="n">
+        <v>2400.51</v>
+      </c>
+      <c r="I54" s="17" t="n">
+        <v>361480.5099999998</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>Şura</t>
+        </is>
+      </c>
+      <c r="B55" s="34" t="n">
+        <v>60.06666666666667</v>
+      </c>
+      <c r="C55" s="34" t="n">
+        <v>76.86666666666666</v>
+      </c>
+      <c r="D55" s="17" t="n">
+        <v>3016259.480500001</v>
+      </c>
+      <c r="E55" s="17" t="n">
+        <v>5701231.434999999</v>
+      </c>
+      <c r="F55" s="19">
+        <f>E55/D55-1</f>
+        <v/>
+      </c>
+      <c r="G55" s="34" t="n">
+        <v>277</v>
+      </c>
+      <c r="H55" s="34" t="n">
+        <v>212.5</v>
+      </c>
+      <c r="I55" s="17" t="n">
+        <v>37862.25999999999</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="47" t="inlineStr">
+        <is>
+          <t>FAZLA MESAI VE YASAL SINIR (4857 s.K. m.41 — yillik 270 saat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="16" t="inlineStr">
+        <is>
+          <t>Fiili FM saat 2025 (uc POS)</t>
+        </is>
+      </c>
+      <c r="B58" s="34" t="n">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="16" t="inlineStr">
+        <is>
+          <t>Fiili FM saat 2026 (uc POS)</t>
+        </is>
+      </c>
+      <c r="B59" s="34" t="n">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="16" t="inlineStr">
+        <is>
+          <t>Kisi basi YILLIK FM 2025 (saat)</t>
+        </is>
+      </c>
+      <c r="B60" s="34" t="n">
+        <v>79.43719972546329</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="16" t="inlineStr">
+        <is>
+          <t>Kisi basi YILLIK FM 2026 (saat)</t>
+        </is>
+      </c>
+      <c r="B61" s="34" t="n">
+        <v>83.56952268010673</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="16" t="inlineStr">
+        <is>
+          <t>Yillik sinir hizinda kisi-ay 2025</t>
+        </is>
+      </c>
+      <c r="B62" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="16" t="inlineStr">
+        <is>
+          <t>Yillik sinir hizinda kisi-ay 2026</t>
+        </is>
+      </c>
+      <c r="B63" s="17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="16" t="inlineStr">
+        <is>
+          <t>VARSAYIM: kadro 2025 seviyesinde kalsaydi eksik kisi-ay</t>
+        </is>
+      </c>
+      <c r="B64" s="17" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="16" t="inlineStr">
+        <is>
+          <t>VARSAYIM: gereken EK fazla mesai (saat)</t>
+        </is>
+      </c>
+      <c r="B65" s="34" t="n">
+        <v>2983.500000000002</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="20" t="inlineStr">
+        <is>
+          <t>VARSAYIM: kisi basi YILLIK FM (saat)</t>
+        </is>
+      </c>
+      <c r="B66" s="68" t="n">
+        <v>465.3191489361705</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="20" t="inlineStr">
+        <is>
           <t>YASAL UST SINIR (saat/yil/kisi)</t>
         </is>
       </c>
-      <c r="B47" s="67" t="n">
+      <c r="B67" s="68" t="n">
         <v>270</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="32" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="32" t="inlineStr">
         <is>
           <t>FORMUL: Personel maliyeti = Brüt Toplam (Bt) + İşveren SGK Hissesi (Isskk) + İşveren İşsizlik Payı (Iisk) — Zirve bordro vw_PuanBil, yönetimin kendi bordro kontrol raporundaki formül.</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="32" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="32" t="inlineStr">
         <is>
           <t>OLCU BIRIMI **FTE** (tam zaman esdeger) = SGK prim gunu / 30. Bordro SATIRI (kayit) yaniltir: ay icinde 1 gun calisan da 1 sayilir; sezonluk giris/cikis yogun oldugu icin sisme en cok sezon ayinda olur. Kayit sayisi ve ortalama prim gunu seffaflik icin ayri satirlarda/kolonlarda durur.</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="32" t="inlineStr">
-        <is>
-          <t>PENCERE: SEZON penceresi esastır (Tem); KÜMÜLATİF pencere (01-07 ay (Oca–Tem), her iki yıl) yıl geneli referansıdır. Aylık kırılım kadro ve maliyet artışının hangi ayda oluştuğunu gösterir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="32" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="32" t="inlineStr">
+        <is>
+          <t>PENCERE: SEZON = Tem–Eki (Temmuz hazırlık; asıl hacim ve sezonluk kadro Ağustos–Ekim). 2026 sezonu henüz tamamlanmadığı için KIYAS tamamlanan ortak ay(lar) ile yapılır: Tem. KÜMÜLATİF pencere (01-07 ay (Oca–Tem), her iki yıl) yıl geneli referansıdır; aylık kırılım artışın hangi ayda oluştuğunu gösterir; geçen yılın tam sezonu ayrı blokta durur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="32" t="inlineStr">
         <is>
           <t>SEZON ESAS: kadro sezonda (01.07-31.08) artiyor -&gt; maliyet/FM kiyasi SEZON penceresinde yapilir. Kumulatif (yilbasindan itibaren) pencere sezonu sulandirir, referans olarak durur.</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="32" t="inlineStr">
-        <is>
-          <t>⚠ ⚠ SEZON PENCERESİ EKSİK: Ağu ayı bordrosu henüz koşmadı (2026 yılı). Sezon karşılaştırması Tem ayı/ayları ile sınırlıdır; Ağustos bordrosu işlendiğinde bu blok kendiliğinden tamamlanır. Yıl geneli için «kümülatif» pencereye bakılır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="32" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="32" t="inlineStr">
+        <is>
+          <t>⚠ ⚠ 2026 SEZONU HENÜZ TAMAMLANMADI. Sezon = Tem–Eki ayları; Ağu, Eyl, Eki ayı/ayları için bordro henüz işlenmedi (Ağustos bordrosu koşmadı, Eylül–Ekim daha gelmedi). Karşılaştırma tamamlanan ortak ay(lar) ile sınırlıdır: Tem. Geçen yılın TAM sezonu ayrıca referans olarak verilmiştir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="32" t="inlineStr">
         <is>
           <t>ORAN: maliyet/ciro yuzde PUAN olarak kiyaslanir. Ciro KDV HARIC (maliyet de KDV'siz), Sinav DAHIL (o satisi da ayni magaza personeli yapiyor).</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="32" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="32" t="inlineStr">
         <is>
           <t>K-22 VARSAYIM: SEZON penceresinde (Tem) ölçülür; birim FTE (tam zaman eşdeğer = SGK prim günü ÷ 30) — bordro satırı sayılsaydı yarım ay çalışan tam sayılır ve kapasite farkı şişerdi. İşgücü ihtiyacı FTE ile doğru orantılı kabul edilir; 15.3 FTE'lik kapasite eksiği ancak fazla mesaiyle kapanırdı (FTE başına 195 saat normal çalışma). Yasal çerçeve: 4857 s.K. m.41 yıllık 270 saat üst sınır. Yıllıklandırma: sezon ayı başına düşen fazla mesai × 12 (sezon yoğunluğunun yıla yayılması hâlinde ulaşacağı seviye).</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="32" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="32" t="inlineStr">
         <is>
           <t>⚠ Sube dagilimi personelin BUGUNKU subesine gore yapilir (bordro ayindaki subesi degil) — toplamlar dogru, sube kirilimi yer degistirenlerde kayabilir.</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="32" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="32" t="inlineStr">
         <is>
           <t>KVKK: kisi bazli ucret/maliyet YOK; tum rakamlar sube/kapsam duzeyinde toplulastirilmis.</t>
         </is>
@@ -3239,72 +3824,72 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="68" t="inlineStr">
+      <c r="A3" s="69" t="inlineStr">
         <is>
           <t>Baslik</t>
         </is>
       </c>
-      <c r="B3" s="69" t="inlineStr">
+      <c r="B3" s="70" t="inlineStr">
         <is>
           <t>Kişi başı iş hacmi — sezon 2026 vs 2025</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="68" t="inlineStr">
+      <c r="A4" s="69" t="inlineStr">
         <is>
           <t>Kesim tarihi</t>
         </is>
       </c>
-      <c r="B4" s="69" t="inlineStr">
+      <c r="B4" s="70" t="inlineStr">
         <is>
           <t>otomatik (veri sonu, okul-hizalı pencerede)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="68" t="inlineStr">
+      <c r="A5" s="69" t="inlineStr">
         <is>
           <t>Pencere</t>
         </is>
       </c>
-      <c r="B5" s="69" t="inlineStr">
+      <c r="B5" s="70" t="inlineStr">
         <is>
           <t>Okul açılışına hizalı — 2025: 01.07.2025 – 25.08.2025 · 2026: 07.07.2026 – 31.08.2026 (her iki yıl 56 gün; açılış 20250908 ve 20260914, gün ofseti -69..-14)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="68" t="inlineStr">
+      <c r="A6" s="69" t="inlineStr">
         <is>
           <t>Kadro kaynagi</t>
         </is>
       </c>
-      <c r="B6" s="69" t="inlineStr">
+      <c r="B6" s="70" t="inlineStr">
         <is>
           <t>Zirve BKM_GENEL.dbo.vw_PersonelDepartman — as-of Igt &lt;= T AND (Ict IS NULL OR Ict &gt;= T), sp_PersonelKarsilastirma_Ozet ile birebir</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="68" t="inlineStr">
+      <c r="A7" s="69" t="inlineStr">
         <is>
           <t>Is hacmi kaynagi</t>
         </is>
       </c>
-      <c r="B7" s="69" t="inlineStr">
+      <c r="B7" s="70" t="inlineStr">
         <is>
           <t>DerinSIS irs/irsAyr eTip=100 (POS satışı), Sınav Okulları/Kıyafet hariç, iade netlenmiş</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="68" t="inlineStr">
+      <c r="A8" s="69" t="inlineStr">
         <is>
           <t>Cekirdek SQL</t>
         </is>
       </c>
-      <c r="B8" s="69" t="inlineStr">
+      <c r="B8" s="70" t="inlineStr">
         <is>
           <t>sorgular/2026-09-02-kadro-vs-is-hacmi-savunma.sql (blok 11)</t>
         </is>
@@ -3318,49 +3903,49 @@
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="B11" s="70" t="inlineStr">
+      <c r="B11" s="71" t="inlineStr">
         <is>
           <t>• Ürün adedi enflasyondan bağımsız — kadro kıyasında birincil ölçüt. Ciro ikincil (fiyat endeksi +%19,8, Fisher, eşleşen ürün).</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="B12" s="70" t="inlineStr">
+      <c r="B12" s="71" t="inlineStr">
         <is>
           <t>• Kıyas okul açılışına hizalı yapılır. Takvim tarihine göre kıyas 2026'da yapay düşüş gösterir: açılış 8 Eylül 2025'ten 14 Eylül 2026'ya, 6 gün kaydı.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="B13" s="70" t="inlineStr">
+      <c r="B13" s="71" t="inlineStr">
         <is>
           <t>• İş hacmi EncoreMerkez POS'tan DEĞİL DerinSIS'ten alınır: POS Temmuz 2025'te değişti (ENPOS → EncoreMerkez), EncoreMerkez'in 2025 tabanı eksik.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="B14" s="70" t="inlineStr">
+      <c r="B14" s="71" t="inlineStr">
         <is>
           <t>• Heykel ve Şura POS raporlamasında yok — mağaza sayfası üç POS mağazası (FSM · Özlüce · İst. Yolu). Beş mağaza kadro hareketi Özet'te ayrı.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="B15" s="70" t="inlineStr">
+      <c r="B15" s="71" t="inlineStr">
         <is>
           <t>• Kadro = o tarihte fiilen çalışan kişi (sezonluk + kadrolu). Kişi başı oranlar kasiyer değil TÜM mağaza kadrosu üzerinden.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="B16" s="70" t="inlineStr">
+      <c r="B16" s="71" t="inlineStr">
         <is>
           <t>• Fiş sayısı bu kaynakta yok: eTip 100 günlük özet belgedir (bir gün = bir belge).</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
-      <c r="B17" s="70" t="inlineStr">
+      <c r="B17" s="71" t="inlineStr">
         <is>
           <t>• Kıdem → verimlilik testi NEGATİF çıktı: aynı kasiyerin öğrenme eğrisi düz (220 → 256 → 242 fiş/gün), mağaza kıdem sıralaması verimlilikle uyuşmuyor. 'Tecrübeli 1 kişi = acemi 3 kişi' iddiası bu veriyle savunulamaz.</t>
         </is>
@@ -3524,7 +4109,7 @@
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>66909340.21999994</v>
+        <v>66909340.21999995</v>
       </c>
       <c r="C9" s="17" t="n">
         <v>114620580.3400001</v>
@@ -3548,7 +4133,7 @@
         <v>71817045.77000012</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>122534175.61</v>
+        <v>122534175.6100001</v>
       </c>
       <c r="D10" s="18">
         <f>C10-B10</f>
@@ -4082,7 +4667,7 @@
         <v/>
       </c>
       <c r="M4" s="17" t="n">
-        <v>20434775.07999998</v>
+        <v>20434775.08</v>
       </c>
       <c r="N4" s="17" t="n">
         <v>40377406.53</v>
@@ -4155,7 +4740,7 @@
         <v/>
       </c>
       <c r="M5" s="17" t="n">
-        <v>28347121.58999997</v>
+        <v>28347121.58999998</v>
       </c>
       <c r="N5" s="17" t="n">
         <v>44784483.15000007</v>
@@ -4228,10 +4813,10 @@
         <v/>
       </c>
       <c r="M6" s="17" t="n">
-        <v>18127443.54999999</v>
+        <v>18127443.54999998</v>
       </c>
       <c r="N6" s="17" t="n">
-        <v>29458690.65999999</v>
+        <v>29458690.66</v>
       </c>
       <c r="O6" s="19">
         <f>N6/M6-1</f>
@@ -5828,10 +6413,10 @@
         <v/>
       </c>
       <c r="F4" s="34" t="n">
-        <v>18.50432496999895</v>
+        <v>18.50432496999892</v>
       </c>
       <c r="G4" s="34" t="n">
-        <v>32.38086689999968</v>
+        <v>32.38086689999967</v>
       </c>
       <c r="H4" s="44">
         <f>G4/F4-1</f>
@@ -5848,7 +6433,7 @@
         <v/>
       </c>
       <c r="L4" s="19" t="n">
-        <v>0.3747245332273843</v>
+        <v>0.3747245332273819</v>
       </c>
       <c r="M4" s="45" t="n">
         <v>3</v>
@@ -5879,7 +6464,7 @@
         <v>10.02370843999998</v>
       </c>
       <c r="G5" s="34" t="n">
-        <v>15.50422908999993</v>
+        <v>15.50422908999992</v>
       </c>
       <c r="H5" s="44">
         <f>G5/F5-1</f>
@@ -5896,7 +6481,7 @@
         <v/>
       </c>
       <c r="L5" s="19" t="n">
-        <v>0.5770282964720119</v>
+        <v>0.5770282964720135</v>
       </c>
       <c r="M5" s="45" t="n">
         <v>-1</v>
@@ -5924,10 +6509,10 @@
         <v/>
       </c>
       <c r="F6" s="34" t="n">
-        <v>14.49106599000013</v>
+        <v>14.49106599000014</v>
       </c>
       <c r="G6" s="34" t="n">
-        <v>23.14058788999988</v>
+        <v>23.14058788999987</v>
       </c>
       <c r="H6" s="44">
         <f>G6/F6-1</f>
@@ -5944,7 +6529,7 @@
         <v/>
       </c>
       <c r="L6" s="19" t="n">
-        <v>0.4921459875659915</v>
+        <v>0.492145987565989</v>
       </c>
       <c r="M6" s="45" t="n">
         <v>1</v>
@@ -5992,7 +6577,7 @@
         <v/>
       </c>
       <c r="L7" s="19" t="n">
-        <v>1.797673394233624</v>
+        <v>1.797673394233621</v>
       </c>
       <c r="M7" s="40" t="inlineStr">
         <is>
@@ -6025,7 +6610,7 @@
         <v>11.13631268</v>
       </c>
       <c r="G8" s="34" t="n">
-        <v>16.74884972</v>
+        <v>16.74884971999999</v>
       </c>
       <c r="H8" s="44">
         <f>G8/F8-1</f>
@@ -6042,7 +6627,7 @@
         <v/>
       </c>
       <c r="L8" s="19" t="n">
-        <v>0.6655996445022569</v>
+        <v>0.6655996445022572</v>
       </c>
       <c r="M8" s="45" t="n">
         <v>1</v>
@@ -6073,7 +6658,7 @@
         <v>1.475290259999999</v>
       </c>
       <c r="G9" s="34" t="n">
-        <v>2.616103029999998</v>
+        <v>2.616103029999999</v>
       </c>
       <c r="H9" s="44">
         <f>G9/F9-1</f>
@@ -6090,7 +6675,7 @@
         <v/>
       </c>
       <c r="L9" s="19" t="n">
-        <v>1.258006023303306</v>
+        <v>1.258006023303304</v>
       </c>
       <c r="M9" s="40" t="inlineStr">
         <is>
@@ -6123,7 +6708,7 @@
         <v>11.64473919000002</v>
       </c>
       <c r="G10" s="34" t="n">
-        <v>22.29073933999999</v>
+        <v>22.29073934000001</v>
       </c>
       <c r="H10" s="44">
         <f>G10/F10-1</f>
@@ -6140,7 +6725,7 @@
         <v/>
       </c>
       <c r="L10" s="19" t="n">
-        <v>0.463194021611737</v>
+        <v>0.4631940216117396</v>
       </c>
       <c r="M10" s="45" t="n">
         <v>6</v>
@@ -6168,7 +6753,7 @@
         <v/>
       </c>
       <c r="F11" s="34" t="n">
-        <v>0.69211733</v>
+        <v>0.6921173300000001</v>
       </c>
       <c r="G11" s="34" t="n">
         <v>1.18767378</v>
@@ -6188,7 +6773,7 @@
         <v/>
       </c>
       <c r="L11" s="19" t="n">
-        <v>0.4636366398909311</v>
+        <v>0.4636366398909313</v>
       </c>
       <c r="M11" s="40" t="inlineStr">
         <is>
@@ -6221,7 +6806,7 @@
         <v>1.942142250000001</v>
       </c>
       <c r="G12" s="34" t="n">
-        <v>6.643827519999999</v>
+        <v>6.643827520000001</v>
       </c>
       <c r="H12" s="44">
         <f>G12/F12-1</f>
@@ -6238,7 +6823,7 @@
         <v/>
       </c>
       <c r="L12" s="19" t="n">
-        <v>1.769093453522602</v>
+        <v>1.7690934535226</v>
       </c>
       <c r="M12" s="45" t="n">
         <v>2</v>
@@ -6269,7 +6854,7 @@
         <v>0.2846255699999998</v>
       </c>
       <c r="G13" s="34" t="n">
-        <v>0.42036219</v>
+        <v>0.4203621900000001</v>
       </c>
       <c r="H13" s="44">
         <f>G13/F13-1</f>
@@ -6286,7 +6871,7 @@
         <v/>
       </c>
       <c r="L13" s="19" t="n">
-        <v>0.5224217348514217</v>
+        <v>0.522421734851422</v>
       </c>
       <c r="M13" s="40" t="inlineStr">
         <is>
@@ -6319,7 +6904,7 @@
         <v>1.25765595</v>
       </c>
       <c r="G14" s="34" t="n">
-        <v>0.9961937399999998</v>
+        <v>0.9961937400000002</v>
       </c>
       <c r="H14" s="44">
         <f>G14/F14-1</f>
@@ -6336,7 +6921,7 @@
         <v/>
       </c>
       <c r="L14" s="19" t="n">
-        <v>0.40084276090257</v>
+        <v>0.4008427609025691</v>
       </c>
       <c r="M14" s="40" t="inlineStr">
         <is>
@@ -6366,7 +6951,7 @@
         <v/>
       </c>
       <c r="F15" s="34" t="n">
-        <v>0.2656298400000001</v>
+        <v>0.2656298400000003</v>
       </c>
       <c r="G15" s="34" t="n">
         <v>0.3784858199999999</v>
@@ -6564,10 +7149,10 @@
         <v/>
       </c>
       <c r="E4" s="34" t="n">
-        <v>33.37095815999886</v>
+        <v>33.37095815999884</v>
       </c>
       <c r="F4" s="34" t="n">
-        <v>49.92745519999971</v>
+        <v>49.92745519999964</v>
       </c>
       <c r="G4" s="44">
         <f>F4/E4-1</f>
@@ -6591,10 +7176,10 @@
         <v/>
       </c>
       <c r="E5" s="34" t="n">
-        <v>32.14602050999881</v>
+        <v>32.14602050999886</v>
       </c>
       <c r="F5" s="34" t="n">
-        <v>55.81900908999965</v>
+        <v>55.81900908999955</v>
       </c>
       <c r="G5" s="44">
         <f>F5/E5-1</f>
@@ -6618,10 +7203,10 @@
         <v/>
       </c>
       <c r="E6" s="34" t="n">
-        <v>61.26123198000223</v>
+        <v>61.26123198000219</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>78.08621144000023</v>
+        <v>78.08621144000018</v>
       </c>
       <c r="G6" s="44">
         <f>F6/E6-1</f>
@@ -7100,10 +7685,10 @@
         <v/>
       </c>
       <c r="E4" s="17" t="n">
-        <v>315972605.87983</v>
+        <v>315972605.8798329</v>
       </c>
       <c r="F4" s="17" t="n">
-        <v>489364071.8499247</v>
+        <v>489364071.8499241</v>
       </c>
       <c r="G4" s="19">
         <f>F4/E4-1</f>

--- a/briefings/sezon-kadro-20260902/verimlilik-2026.xlsx
+++ b/briefings/sezon-kadro-20260902/verimlilik-2026.xlsx
@@ -121,7 +121,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -151,6 +151,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFEFEF"/>
       </patternFill>
     </fill>
   </fills>
@@ -224,7 +229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -316,6 +321,12 @@
     <xf numFmtId="166" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -1992,7 +2003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R77"/>
+  <dimension ref="A1:R95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2280,20 +2291,20 @@
         </is>
       </c>
       <c r="B12" s="17" t="n">
-        <v>30679569.86000018</v>
+        <v>30679569.85999918</v>
       </c>
       <c r="C12" s="17" t="n">
-        <v>53355722.4200003</v>
+        <v>53355722.42000187</v>
       </c>
       <c r="D12" s="44">
         <f>C12/B12-1</f>
         <v/>
       </c>
       <c r="E12" s="17" t="n">
-        <v>242487002.9100002</v>
+        <v>242487002.9099963</v>
       </c>
       <c r="F12" s="17" t="n">
-        <v>388687036.5200025</v>
+        <v>388687036.5200129</v>
       </c>
       <c r="G12" s="44">
         <f>F12/E12-1</f>
@@ -2334,20 +2345,20 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>315850.067192864</v>
+        <v>315850.0671928537</v>
       </c>
       <c r="C14" s="17" t="n">
-        <v>474554.3055440288</v>
+        <v>474554.3055440427</v>
       </c>
       <c r="D14" s="44">
         <f>C14/B14-1</f>
         <v/>
       </c>
       <c r="E14" s="17" t="n">
-        <v>347867.7356206966</v>
+        <v>347867.7356206909</v>
       </c>
       <c r="F14" s="17" t="n">
-        <v>500777.8009705851</v>
+        <v>500777.8009705985</v>
       </c>
       <c r="G14" s="44">
         <f>F14/E14-1</f>
@@ -2388,20 +2399,20 @@
         </is>
       </c>
       <c r="B16" s="62" t="n">
-        <v>0.1429703378344554</v>
+        <v>0.14297033783446</v>
       </c>
       <c r="C16" s="62" t="n">
-        <v>0.1271160646389757</v>
+        <v>0.1271160646389719</v>
       </c>
       <c r="D16" s="63">
         <f>C16-B16</f>
         <v/>
       </c>
       <c r="E16" s="62" t="n">
-        <v>0.1284870034509182</v>
+        <v>0.1284870034509203</v>
       </c>
       <c r="F16" s="62" t="n">
-        <v>0.1214791247887942</v>
+        <v>0.121479124788791</v>
       </c>
       <c r="G16" s="63">
         <f>F16-E16</f>
@@ -2469,7 +2480,7 @@
         </is>
       </c>
       <c r="B24" s="17" t="n">
-        <v>602003224.0700146</v>
+        <v>602003224.0700126</v>
       </c>
     </row>
     <row r="25">
@@ -2479,7 +2490,7 @@
         </is>
       </c>
       <c r="B25" s="65" t="n">
-        <v>0.0353895768495456</v>
+        <v>0.03538957684954572</v>
       </c>
     </row>
     <row r="26">
@@ -2799,10 +2810,10 @@
         <v>727.5</v>
       </c>
       <c r="J38" s="42" t="n">
-        <v>0.1064043589756458</v>
+        <v>0.1064043589756548</v>
       </c>
       <c r="K38" s="42" t="n">
-        <v>0.09342797291737968</v>
+        <v>0.0934279729173756</v>
       </c>
       <c r="L38" s="17" t="n">
         <v>117</v>
@@ -2859,10 +2870,10 @@
         <v>65</v>
       </c>
       <c r="J39" s="42" t="n">
-        <v>0.1097139082641927</v>
+        <v>0.1097139082641947</v>
       </c>
       <c r="K39" s="42" t="n">
-        <v>0.1128809843841212</v>
+        <v>0.1128809843841146</v>
       </c>
       <c r="L39" s="17" t="n">
         <v>116</v>
@@ -2919,10 +2930,10 @@
         <v>1681</v>
       </c>
       <c r="J40" s="42" t="n">
-        <v>0.1388245899802142</v>
+        <v>0.1388245899802121</v>
       </c>
       <c r="K40" s="42" t="n">
-        <v>0.1170292741229823</v>
+        <v>0.1170292741229818</v>
       </c>
       <c r="L40" s="17" t="n">
         <v>112</v>
@@ -2979,10 +2990,10 @@
         <v>786.5</v>
       </c>
       <c r="J41" s="42" t="n">
-        <v>0.1150222758867225</v>
+        <v>0.1150222758867227</v>
       </c>
       <c r="K41" s="42" t="n">
-        <v>0.1323692598350995</v>
+        <v>0.1323692598351018</v>
       </c>
       <c r="L41" s="17" t="n">
         <v>114</v>
@@ -3039,10 +3050,10 @@
         <v>3553.01</v>
       </c>
       <c r="J42" s="42" t="n">
-        <v>0.1596487262755276</v>
+        <v>0.1596487262755285</v>
       </c>
       <c r="K42" s="42" t="n">
-        <v>0.1384843301196873</v>
+        <v>0.1384843301196848</v>
       </c>
       <c r="L42" s="17" t="n">
         <v>107</v>
@@ -3099,10 +3110,10 @@
         <v>32.5</v>
       </c>
       <c r="J43" s="42" t="n">
-        <v>0.1425960097198796</v>
+        <v>0.1425960097198744</v>
       </c>
       <c r="K43" s="42" t="n">
-        <v>0.139214769438298</v>
+        <v>0.1392147694382914</v>
       </c>
       <c r="L43" s="17" t="n">
         <v>105</v>
@@ -3159,10 +3170,10 @@
         <v>783</v>
       </c>
       <c r="J44" s="42" t="n">
-        <v>0.1429703378344554</v>
+        <v>0.14297033783446</v>
       </c>
       <c r="K44" s="42" t="n">
-        <v>0.1271160646389757</v>
+        <v>0.1271160646389719</v>
       </c>
       <c r="L44" s="67" t="n">
         <v>110</v>
@@ -3225,7 +3236,7 @@
         </is>
       </c>
       <c r="J45" s="42" t="n">
-        <v>0.02912397700580437</v>
+        <v>0.02912397700580454</v>
       </c>
       <c r="K45" s="42" t="inlineStr">
         <is>
@@ -3301,7 +3312,7 @@
         </is>
       </c>
       <c r="J46" s="42" t="n">
-        <v>0.02098348810480835</v>
+        <v>0.02098348810480769</v>
       </c>
       <c r="K46" s="42" t="inlineStr">
         <is>
@@ -3377,7 +3388,7 @@
         </is>
       </c>
       <c r="J47" s="42" t="n">
-        <v>0.06872611463187885</v>
+        <v>0.06872611463188823</v>
       </c>
       <c r="K47" s="42" t="inlineStr">
         <is>
@@ -3736,63 +3747,445 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="32" t="inlineStr">
+      <c r="A69" s="47" t="inlineStr">
+        <is>
+          <t>SEZONUN KALANI — TAHMIN (02.09.2026 sonrasi tahmindir)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="54" t="inlineStr">
+        <is>
+          <t>Ay</t>
+        </is>
+      </c>
+      <c r="B70" s="54" t="inlineStr">
+        <is>
+          <t>Ciro tipi</t>
+        </is>
+      </c>
+      <c r="C70" s="54" t="inlineStr">
+        <is>
+          <t>Maliyet tipi</t>
+        </is>
+      </c>
+      <c r="D70" s="54" t="inlineStr">
+        <is>
+          <t>Ciro 2025 (gercek)</t>
+        </is>
+      </c>
+      <c r="E70" s="54" t="inlineStr">
+        <is>
+          <t>Ciro 2026</t>
+        </is>
+      </c>
+      <c r="F70" s="54" t="inlineStr">
+        <is>
+          <t>Ciro Δ</t>
+        </is>
+      </c>
+      <c r="G70" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  gerceklesen</t>
+        </is>
+      </c>
+      <c r="H70" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  tahmin</t>
+        </is>
+      </c>
+      <c r="I70" s="54" t="inlineStr">
+        <is>
+          <t>Tahmin gunu</t>
+        </is>
+      </c>
+      <c r="J70" s="54" t="inlineStr">
+        <is>
+          <t>FTE 2025</t>
+        </is>
+      </c>
+      <c r="K70" s="54" t="inlineStr">
+        <is>
+          <t>FTE 2026</t>
+        </is>
+      </c>
+      <c r="L70" s="54" t="inlineStr">
+        <is>
+          <t>Maliyet 2026</t>
+        </is>
+      </c>
+      <c r="M70" s="54" t="inlineStr">
+        <is>
+          <t>Maliyet/ciro 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="16" t="inlineStr">
+        <is>
+          <t>Tem</t>
+        </is>
+      </c>
+      <c r="B71" s="16" t="inlineStr">
+        <is>
+          <t>gercek</t>
+        </is>
+      </c>
+      <c r="C71" s="16" t="inlineStr">
+        <is>
+          <t>gercek</t>
+        </is>
+      </c>
+      <c r="D71" s="17" t="n">
+        <v>30679569.85999918</v>
+      </c>
+      <c r="E71" s="17" t="n">
+        <v>53355722.42000007</v>
+      </c>
+      <c r="F71" s="19">
+        <f>E71/D71-1</f>
+        <v/>
+      </c>
+      <c r="G71" s="17" t="n">
+        <v>53355722.42000007</v>
+      </c>
+      <c r="H71" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="34" t="n">
+        <v>97.13333333333333</v>
+      </c>
+      <c r="K71" s="34" t="n">
+        <v>112.4333333333333</v>
+      </c>
+      <c r="L71" s="17" t="n">
+        <v>6782369.460000002</v>
+      </c>
+      <c r="M71" s="65" t="n">
+        <v>0.1271160646389762</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="16" t="inlineStr">
+        <is>
+          <t>Ağu</t>
+        </is>
+      </c>
+      <c r="B72" s="16" t="inlineStr">
+        <is>
+          <t>gercek</t>
+        </is>
+      </c>
+      <c r="C72" s="69" t="inlineStr">
+        <is>
+          <t>TAHMIN</t>
+        </is>
+      </c>
+      <c r="D72" s="56" t="n">
+        <v>186875143.8999995</v>
+      </c>
+      <c r="E72" s="56" t="n">
+        <v>172114527.48</v>
+      </c>
+      <c r="F72" s="19">
+        <f>E72/D72-1</f>
+        <v/>
+      </c>
+      <c r="G72" s="56" t="n">
+        <v>172114527.48</v>
+      </c>
+      <c r="H72" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="70" t="n">
+        <v>120.6333333333333</v>
+      </c>
+      <c r="K72" s="70" t="n">
+        <v>139.6349462365592</v>
+      </c>
+      <c r="L72" s="56" t="n">
+        <v>8423265.297096778</v>
+      </c>
+      <c r="M72" s="71" t="n">
+        <v>0.04893988567046193</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="16" t="inlineStr">
+        <is>
+          <t>Eyl</t>
+        </is>
+      </c>
+      <c r="B73" s="69" t="inlineStr">
+        <is>
+          <t>KISMI</t>
+        </is>
+      </c>
+      <c r="C73" s="69" t="inlineStr">
+        <is>
+          <t>TAHMIN</t>
+        </is>
+      </c>
+      <c r="D73" s="56" t="n">
+        <v>313049992.7700272</v>
+      </c>
+      <c r="E73" s="56" t="n">
+        <v>631903908.94835</v>
+      </c>
+      <c r="F73" s="19">
+        <f>E73/D73-1</f>
+        <v/>
+      </c>
+      <c r="G73" s="56" t="n">
+        <v>20742785.50000001</v>
+      </c>
+      <c r="H73" s="56" t="n">
+        <v>611161123.44835</v>
+      </c>
+      <c r="I73" s="56" t="n">
+        <v>28</v>
+      </c>
+      <c r="J73" s="70" t="n">
+        <v>132.8333333333333</v>
+      </c>
+      <c r="K73" s="70" t="n">
+        <v>153.7566346373827</v>
+      </c>
+      <c r="L73" s="56" t="n">
+        <v>9275134.625291698</v>
+      </c>
+      <c r="M73" s="71" t="n">
+        <v>0.01467807762216236</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="16" t="inlineStr">
+        <is>
+          <t>Eki</t>
+        </is>
+      </c>
+      <c r="B74" s="69" t="inlineStr">
+        <is>
+          <t>TAHMIN</t>
+        </is>
+      </c>
+      <c r="C74" s="69" t="inlineStr">
+        <is>
+          <t>TAHMIN</t>
+        </is>
+      </c>
+      <c r="D74" s="56" t="n">
+        <v>71398517.53998658</v>
+      </c>
+      <c r="E74" s="56" t="n">
+        <v>133016523.3379859</v>
+      </c>
+      <c r="F74" s="19">
+        <f>E74/D74-1</f>
+        <v/>
+      </c>
+      <c r="G74" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="56" t="n">
+        <v>133016523.3379859</v>
+      </c>
+      <c r="I74" s="56" t="n">
+        <v>31</v>
+      </c>
+      <c r="J74" s="70" t="n">
+        <v>108.1333333333333</v>
+      </c>
+      <c r="K74" s="70" t="n">
+        <v>125.1660032029284</v>
+      </c>
+      <c r="L74" s="56" t="n">
+        <v>7550448.362470834</v>
+      </c>
+      <c r="M74" s="71" t="n">
+        <v>0.05676323642353558</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="20" t="inlineStr">
+        <is>
+          <t>Agu+Eyl</t>
+        </is>
+      </c>
+      <c r="B75" s="64" t="inlineStr">
+        <is>
+          <t>kayma notr</t>
+        </is>
+      </c>
+      <c r="D75" s="72" t="n">
+        <v>499925136.6700268</v>
+      </c>
+      <c r="E75" s="72" t="n">
+        <v>804018436.42835</v>
+      </c>
+      <c r="F75" s="19">
+        <f>E75/D75-1</f>
+        <v/>
+      </c>
+      <c r="J75" s="73" t="n">
+        <v>253.4666666666666</v>
+      </c>
+      <c r="K75" s="73" t="n">
+        <v>293.3915808739419</v>
+      </c>
+      <c r="L75" s="72" t="n">
+        <v>17698399.92238848</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="36" t="inlineStr">
+        <is>
+          <t>SEZON TOPLAM</t>
+        </is>
+      </c>
+      <c r="D76" s="21" t="n">
+        <v>602003224.0700126</v>
+      </c>
+      <c r="E76" s="21" t="n">
+        <v>990390682.1863359</v>
+      </c>
+      <c r="F76" s="37">
+        <f>E76/D76-1</f>
+        <v/>
+      </c>
+      <c r="J76" s="38" t="n">
+        <v>458.7333333333333</v>
+      </c>
+      <c r="K76" s="38" t="n">
+        <v>530.9909174102037</v>
+      </c>
+      <c r="L76" s="21" t="n">
+        <v>32031217.74485931</v>
+      </c>
+      <c r="M76" s="74" t="n">
+        <v>0.03234200232392012</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="59" t="inlineStr">
+        <is>
+          <t>⚠ TAKVİM AYI KIYASI KAYMAYI YANSITIR: okul 08.09.2025'de değil 14.09.2026'te açıldı — 2025'te Ağustos sonunda gerçekleşen yoğunluk 2026'da Eylül başına düştü. Bu yüzden Ağustos -8%, Eylül +102% görünür; ay ay okumak yanıltır, SEZON TOPLAMI (veya Ağustos+Eylül birlikte) esas alınır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="64" t="inlineStr">
+        <is>
+          <t>YONTEM: okul-hizalı gün eşleme (ciro) + sezon şekli×seviye (FTE) + FTE başına maliyet</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="64" t="inlineStr">
+        <is>
+          <t>VARSAYIM: Sezon şekli yıl üzerinden aynı: 2025'in gün-bazlı satış dağılımı okul açılışına hizalanarak 2026 takvimine taşındı (açılış 08.09.2025 → 14.09.2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="64" t="inlineStr">
+        <is>
+          <t>VARSAYIM: Seviye: hizalı pencerede ÖLÇÜLEN ciro büyümesi (%66.0) uygulandı — ayrı bir büyüme varsayımı yapılmadı.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="64" t="inlineStr">
+        <is>
+          <t>VARSAYIM: FTE: sezon şekli 2025'ten, seviye 2026'nın Tem ayından (katsayı 1.158).</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="64" t="inlineStr">
+        <is>
+          <t>VARSAYIM: Maliyet: tahmini FTE × 2026 Tem ayının FTE başına maliyeti (60.323 ₺). Ücret seviyesi sabit varsayıldı → zam/asgari ücret artışı olursa maliyet tahmini ALT SINIRDIR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="64" t="inlineStr">
+        <is>
+          <t>VARSAYIM: Gerçekleşen günler tahminle değiştirilmedi: 02.09.2026 tarihine kadar gerçek veri, sonrası tahmindir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="64" t="inlineStr">
+        <is>
+          <t>VARSAYIM: Bayram/tatil kayması ve mağaza açılış-kapanışı modellenmedi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="32" t="inlineStr">
         <is>
           <t>FORMUL: Personel maliyeti = Brüt Toplam (Bt) + İşveren SGK Hissesi (Isskk) + İşveren İşsizlik Payı (Iisk) — Zirve bordro vw_PuanBil, yönetimin kendi bordro kontrol raporundaki formül.</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="32" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="32" t="inlineStr">
         <is>
           <t>OLCU BIRIMI **FTE** (tam zaman esdeger) = SGK prim gunu / 30. Bordro SATIRI (kayit) yaniltir: ay icinde 1 gun calisan da 1 sayilir; sezonluk giris/cikis yogun oldugu icin sisme en cok sezon ayinda olur. Kayit sayisi ve ortalama prim gunu seffaflik icin ayri satirlarda/kolonlarda durur.</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="32" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="32" t="inlineStr">
         <is>
           <t>PENCERE: SEZON = Tem–Eki (Temmuz hazırlık; asıl hacim ve sezonluk kadro Ağustos–Ekim). 2026 sezonu henüz tamamlanmadığı için KIYAS tamamlanan ortak ay(lar) ile yapılır: Tem. KÜMÜLATİF pencere (01-07 ay (Oca–Tem), her iki yıl) yıl geneli referansıdır; aylık kırılım artışın hangi ayda oluştuğunu gösterir; geçen yılın tam sezonu ayrı blokta durur.</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="32" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="32" t="inlineStr">
         <is>
           <t>SEZON ESAS: kadro sezonda (01.07-31.08) artiyor -&gt; maliyet/FM kiyasi SEZON penceresinde yapilir. Kumulatif (yilbasindan itibaren) pencere sezonu sulandirir, referans olarak durur.</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="32" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="32" t="inlineStr">
         <is>
           <t>⚠ ⚠ 2026 SEZONU HENÜZ TAMAMLANMADI. Sezon = Tem–Eki ayları; Ağu, Eyl, Eki ayı/ayları için bordro henüz işlenmedi (Ağustos bordrosu koşmadı, Eylül–Ekim daha gelmedi). Karşılaştırma tamamlanan ortak ay(lar) ile sınırlıdır: Tem. Geçen yılın TAM sezonu ayrıca referans olarak verilmiştir.</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="32" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="32" t="inlineStr">
         <is>
           <t>ORAN: maliyet/ciro yuzde PUAN olarak kiyaslanir. Ciro KDV HARIC (maliyet de KDV'siz), Sinav DAHIL (o satisi da ayni magaza personeli yapiyor).</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="32" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="32" t="inlineStr">
         <is>
           <t>K-22 VARSAYIM: SEZON penceresinde (Tem) ölçülür; birim FTE (tam zaman eşdeğer = SGK prim günü ÷ 30) — bordro satırı sayılsaydı yarım ay çalışan tam sayılır ve kapasite farkı şişerdi. İşgücü ihtiyacı FTE ile doğru orantılı kabul edilir; 15.3 FTE'lik kapasite eksiği ancak fazla mesaiyle kapanırdı (FTE başına 195 saat normal çalışma). Yasal çerçeve: 4857 s.K. m.41 yıllık 270 saat üst sınır. Yıllıklandırma: sezon ayı başına düşen fazla mesai × 12 (sezon yoğunluğunun yıla yayılması hâlinde ulaşacağı seviye).</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="32" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="32" t="inlineStr">
         <is>
           <t>⚠ Sube dagilimi personelin BUGUNKU subesine gore yapilir (bordro ayindaki subesi degil) — toplamlar dogru, sube kirilimi yer degistirenlerde kayabilir.</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="32" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="32" t="inlineStr">
         <is>
           <t>KVKK: kisi bazli ucret/maliyet YOK; tum rakamlar sube/kapsam duzeyinde toplulastirilmis.</t>
         </is>
@@ -3824,72 +4217,72 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="69" t="inlineStr">
+      <c r="A3" s="75" t="inlineStr">
         <is>
           <t>Baslik</t>
         </is>
       </c>
-      <c r="B3" s="70" t="inlineStr">
+      <c r="B3" s="76" t="inlineStr">
         <is>
           <t>Kişi başı iş hacmi — sezon 2026 vs 2025</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="69" t="inlineStr">
+      <c r="A4" s="75" t="inlineStr">
         <is>
           <t>Kesim tarihi</t>
         </is>
       </c>
-      <c r="B4" s="70" t="inlineStr">
+      <c r="B4" s="76" t="inlineStr">
         <is>
           <t>otomatik (veri sonu, okul-hizalı pencerede)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="69" t="inlineStr">
+      <c r="A5" s="75" t="inlineStr">
         <is>
           <t>Pencere</t>
         </is>
       </c>
-      <c r="B5" s="70" t="inlineStr">
+      <c r="B5" s="76" t="inlineStr">
         <is>
           <t>Okul açılışına hizalı — 2025: 01.07.2025 – 25.08.2025 · 2026: 07.07.2026 – 31.08.2026 (her iki yıl 56 gün; açılış 20250908 ve 20260914, gün ofseti -69..-14)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="69" t="inlineStr">
+      <c r="A6" s="75" t="inlineStr">
         <is>
           <t>Kadro kaynagi</t>
         </is>
       </c>
-      <c r="B6" s="70" t="inlineStr">
+      <c r="B6" s="76" t="inlineStr">
         <is>
           <t>Zirve BKM_GENEL.dbo.vw_PersonelDepartman — as-of Igt &lt;= T AND (Ict IS NULL OR Ict &gt;= T), sp_PersonelKarsilastirma_Ozet ile birebir</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="69" t="inlineStr">
+      <c r="A7" s="75" t="inlineStr">
         <is>
           <t>Is hacmi kaynagi</t>
         </is>
       </c>
-      <c r="B7" s="70" t="inlineStr">
+      <c r="B7" s="76" t="inlineStr">
         <is>
           <t>DerinSIS irs/irsAyr eTip=100 (POS satışı), Sınav Okulları/Kıyafet hariç, iade netlenmiş</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="69" t="inlineStr">
+      <c r="A8" s="75" t="inlineStr">
         <is>
           <t>Cekirdek SQL</t>
         </is>
       </c>
-      <c r="B8" s="70" t="inlineStr">
+      <c r="B8" s="76" t="inlineStr">
         <is>
           <t>sorgular/2026-09-02-kadro-vs-is-hacmi-savunma.sql (blok 11)</t>
         </is>
@@ -3903,49 +4296,49 @@
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="B11" s="71" t="inlineStr">
+      <c r="B11" s="77" t="inlineStr">
         <is>
           <t>• Ürün adedi enflasyondan bağımsız — kadro kıyasında birincil ölçüt. Ciro ikincil (fiyat endeksi +%19,8, Fisher, eşleşen ürün).</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="B12" s="71" t="inlineStr">
+      <c r="B12" s="77" t="inlineStr">
         <is>
           <t>• Kıyas okul açılışına hizalı yapılır. Takvim tarihine göre kıyas 2026'da yapay düşüş gösterir: açılış 8 Eylül 2025'ten 14 Eylül 2026'ya, 6 gün kaydı.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="B13" s="71" t="inlineStr">
+      <c r="B13" s="77" t="inlineStr">
         <is>
           <t>• İş hacmi EncoreMerkez POS'tan DEĞİL DerinSIS'ten alınır: POS Temmuz 2025'te değişti (ENPOS → EncoreMerkez), EncoreMerkez'in 2025 tabanı eksik.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="B14" s="71" t="inlineStr">
+      <c r="B14" s="77" t="inlineStr">
         <is>
           <t>• Heykel ve Şura POS raporlamasında yok — mağaza sayfası üç POS mağazası (FSM · Özlüce · İst. Yolu). Beş mağaza kadro hareketi Özet'te ayrı.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="B15" s="71" t="inlineStr">
+      <c r="B15" s="77" t="inlineStr">
         <is>
           <t>• Kadro = o tarihte fiilen çalışan kişi (sezonluk + kadrolu). Kişi başı oranlar kasiyer değil TÜM mağaza kadrosu üzerinden.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="B16" s="71" t="inlineStr">
+      <c r="B16" s="77" t="inlineStr">
         <is>
           <t>• Fiş sayısı bu kaynakta yok: eTip 100 günlük özet belgedir (bir gün = bir belge).</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
-      <c r="B17" s="71" t="inlineStr">
+      <c r="B17" s="77" t="inlineStr">
         <is>
           <t>• Kıdem → verimlilik testi NEGATİF çıktı: aynı kasiyerin öğrenme eğrisi düz (220 → 256 → 242 fiş/gün), mağaza kıdem sıralaması verimlilikle uyuşmuyor. 'Tecrübeli 1 kişi = acemi 3 kişi' iddiası bu veriyle savunulamaz.</t>
         </is>
@@ -4109,10 +4502,10 @@
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>66909340.21999995</v>
+        <v>66909340.21999986</v>
       </c>
       <c r="C9" s="17" t="n">
-        <v>114620580.3400001</v>
+        <v>114620580.3400004</v>
       </c>
       <c r="D9" s="18">
         <f>C9-B9</f>
@@ -4130,10 +4523,10 @@
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>71817045.77000012</v>
+        <v>71817045.76999547</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>122534175.6100001</v>
+        <v>122534175.6099948</v>
       </c>
       <c r="D10" s="18">
         <f>C10-B10</f>
@@ -4667,10 +5060,10 @@
         <v/>
       </c>
       <c r="M4" s="17" t="n">
-        <v>20434775.08</v>
+        <v>20434775.08000033</v>
       </c>
       <c r="N4" s="17" t="n">
-        <v>40377406.53</v>
+        <v>40377406.52999959</v>
       </c>
       <c r="O4" s="19">
         <f>N4/M4-1</f>
@@ -4740,10 +5133,10 @@
         <v/>
       </c>
       <c r="M5" s="17" t="n">
-        <v>28347121.58999998</v>
+        <v>28347121.58999967</v>
       </c>
       <c r="N5" s="17" t="n">
-        <v>44784483.15000007</v>
+        <v>44784483.14999995</v>
       </c>
       <c r="O5" s="19">
         <f>N5/M5-1</f>
@@ -4813,10 +5206,10 @@
         <v/>
       </c>
       <c r="M6" s="17" t="n">
-        <v>18127443.54999998</v>
+        <v>18127443.54999987</v>
       </c>
       <c r="N6" s="17" t="n">
-        <v>29458690.66</v>
+        <v>29458690.66000083</v>
       </c>
       <c r="O6" s="19">
         <f>N6/M6-1</f>
@@ -6413,10 +6806,10 @@
         <v/>
       </c>
       <c r="F4" s="34" t="n">
-        <v>18.50432496999892</v>
+        <v>18.50432497000117</v>
       </c>
       <c r="G4" s="34" t="n">
-        <v>32.38086689999967</v>
+        <v>32.38086690000175</v>
       </c>
       <c r="H4" s="44">
         <f>G4/F4-1</f>
@@ -6433,7 +6826,7 @@
         <v/>
       </c>
       <c r="L4" s="19" t="n">
-        <v>0.3747245332273819</v>
+        <v>0.3747245332279163</v>
       </c>
       <c r="M4" s="45" t="n">
         <v>3</v>
@@ -6464,7 +6857,7 @@
         <v>10.02370843999998</v>
       </c>
       <c r="G5" s="34" t="n">
-        <v>15.50422908999992</v>
+        <v>15.50422908999997</v>
       </c>
       <c r="H5" s="44">
         <f>G5/F5-1</f>
@@ -6481,7 +6874,7 @@
         <v/>
       </c>
       <c r="L5" s="19" t="n">
-        <v>0.5770282964720135</v>
+        <v>0.5770282964720179</v>
       </c>
       <c r="M5" s="45" t="n">
         <v>-1</v>
@@ -6509,7 +6902,7 @@
         <v/>
       </c>
       <c r="F6" s="34" t="n">
-        <v>14.49106599000014</v>
+        <v>14.49106598999975</v>
       </c>
       <c r="G6" s="34" t="n">
         <v>23.14058788999987</v>
@@ -6529,7 +6922,7 @@
         <v/>
       </c>
       <c r="L6" s="19" t="n">
-        <v>0.492145987565989</v>
+        <v>0.4921459875658043</v>
       </c>
       <c r="M6" s="45" t="n">
         <v>1</v>
@@ -6577,7 +6970,7 @@
         <v/>
       </c>
       <c r="L7" s="19" t="n">
-        <v>1.797673394233621</v>
+        <v>1.79767339423362</v>
       </c>
       <c r="M7" s="40" t="inlineStr">
         <is>
@@ -6607,10 +7000,10 @@
         <v/>
       </c>
       <c r="F8" s="34" t="n">
-        <v>11.13631268</v>
+        <v>11.13631267999999</v>
       </c>
       <c r="G8" s="34" t="n">
-        <v>16.74884971999999</v>
+        <v>16.74884972000005</v>
       </c>
       <c r="H8" s="44">
         <f>G8/F8-1</f>
@@ -6627,7 +7020,7 @@
         <v/>
       </c>
       <c r="L8" s="19" t="n">
-        <v>0.6655996445022572</v>
+        <v>0.6655996445022558</v>
       </c>
       <c r="M8" s="45" t="n">
         <v>1</v>
@@ -6655,10 +7048,10 @@
         <v/>
       </c>
       <c r="F9" s="34" t="n">
-        <v>1.475290259999999</v>
+        <v>1.475290260000006</v>
       </c>
       <c r="G9" s="34" t="n">
-        <v>2.616103029999999</v>
+        <v>2.616103030000003</v>
       </c>
       <c r="H9" s="44">
         <f>G9/F9-1</f>
@@ -6675,7 +7068,7 @@
         <v/>
       </c>
       <c r="L9" s="19" t="n">
-        <v>1.258006023303304</v>
+        <v>1.258006023303444</v>
       </c>
       <c r="M9" s="40" t="inlineStr">
         <is>
@@ -6705,10 +7098,10 @@
         <v/>
       </c>
       <c r="F10" s="34" t="n">
-        <v>11.64473919000002</v>
+        <v>11.64473918999999</v>
       </c>
       <c r="G10" s="34" t="n">
-        <v>22.29073934000001</v>
+        <v>22.29073933999993</v>
       </c>
       <c r="H10" s="44">
         <f>G10/F10-1</f>
@@ -6725,7 +7118,7 @@
         <v/>
       </c>
       <c r="L10" s="19" t="n">
-        <v>0.4631940216117396</v>
+        <v>0.4631940216117609</v>
       </c>
       <c r="M10" s="45" t="n">
         <v>6</v>
@@ -6753,10 +7146,10 @@
         <v/>
       </c>
       <c r="F11" s="34" t="n">
-        <v>0.6921173300000001</v>
+        <v>0.6921173299999999</v>
       </c>
       <c r="G11" s="34" t="n">
-        <v>1.18767378</v>
+        <v>1.187673780000001</v>
       </c>
       <c r="H11" s="44">
         <f>G11/F11-1</f>
@@ -6773,7 +7166,7 @@
         <v/>
       </c>
       <c r="L11" s="19" t="n">
-        <v>0.4636366398909313</v>
+        <v>0.4636366398909308</v>
       </c>
       <c r="M11" s="40" t="inlineStr">
         <is>
@@ -6803,10 +7196,10 @@
         <v/>
       </c>
       <c r="F12" s="34" t="n">
-        <v>1.942142250000001</v>
+        <v>1.942142249999997</v>
       </c>
       <c r="G12" s="34" t="n">
-        <v>6.643827520000001</v>
+        <v>6.643827519999999</v>
       </c>
       <c r="H12" s="44">
         <f>G12/F12-1</f>
@@ -6823,7 +7216,7 @@
         <v/>
       </c>
       <c r="L12" s="19" t="n">
-        <v>1.7690934535226</v>
+        <v>1.76909345352259</v>
       </c>
       <c r="M12" s="45" t="n">
         <v>2</v>
@@ -6851,10 +7244,10 @@
         <v/>
       </c>
       <c r="F13" s="34" t="n">
-        <v>0.2846255699999998</v>
+        <v>0.2846255699999999</v>
       </c>
       <c r="G13" s="34" t="n">
-        <v>0.4203621900000001</v>
+        <v>0.4203621899999996</v>
       </c>
       <c r="H13" s="44">
         <f>G13/F13-1</f>
@@ -6871,7 +7264,7 @@
         <v/>
       </c>
       <c r="L13" s="19" t="n">
-        <v>0.522421734851422</v>
+        <v>0.5224217348514271</v>
       </c>
       <c r="M13" s="40" t="inlineStr">
         <is>
@@ -6901,10 +7294,10 @@
         <v/>
       </c>
       <c r="F14" s="34" t="n">
-        <v>1.25765595</v>
+        <v>1.257655950000001</v>
       </c>
       <c r="G14" s="34" t="n">
-        <v>0.9961937400000002</v>
+        <v>0.9961937400000003</v>
       </c>
       <c r="H14" s="44">
         <f>G14/F14-1</f>
@@ -6921,7 +7314,7 @@
         <v/>
       </c>
       <c r="L14" s="19" t="n">
-        <v>0.4008427609025691</v>
+        <v>0.4008427609025713</v>
       </c>
       <c r="M14" s="40" t="inlineStr">
         <is>
@@ -6951,10 +7344,10 @@
         <v/>
       </c>
       <c r="F15" s="34" t="n">
-        <v>0.2656298400000003</v>
+        <v>0.2656298399999997</v>
       </c>
       <c r="G15" s="34" t="n">
-        <v>0.3784858199999999</v>
+        <v>0.3784858199999995</v>
       </c>
       <c r="H15" s="44">
         <f>G15/F15-1</f>
@@ -6971,7 +7364,7 @@
         <v/>
       </c>
       <c r="L15" s="19" t="n">
-        <v>0.4999858989104884</v>
+        <v>0.4999858989104855</v>
       </c>
       <c r="M15" s="40" t="inlineStr">
         <is>
@@ -7149,10 +7542,10 @@
         <v/>
       </c>
       <c r="E4" s="34" t="n">
-        <v>33.37095815999884</v>
+        <v>33.37095816000493</v>
       </c>
       <c r="F4" s="34" t="n">
-        <v>49.92745519999964</v>
+        <v>49.92745519999929</v>
       </c>
       <c r="G4" s="44">
         <f>F4/E4-1</f>
@@ -7176,10 +7569,10 @@
         <v/>
       </c>
       <c r="E5" s="34" t="n">
-        <v>32.14602050999886</v>
+        <v>32.14602051000463</v>
       </c>
       <c r="F5" s="34" t="n">
-        <v>55.81900908999955</v>
+        <v>55.81900908999923</v>
       </c>
       <c r="G5" s="44">
         <f>F5/E5-1</f>
@@ -7203,10 +7596,10 @@
         <v/>
       </c>
       <c r="E6" s="34" t="n">
-        <v>61.26123198000219</v>
+        <v>61.26123197999352</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>78.08621144000018</v>
+        <v>78.0862114399969</v>
       </c>
       <c r="G6" s="44">
         <f>F6/E6-1</f>
@@ -7685,10 +8078,10 @@
         <v/>
       </c>
       <c r="E4" s="17" t="n">
-        <v>315972605.8798329</v>
+        <v>315972605.8803364</v>
       </c>
       <c r="F4" s="17" t="n">
-        <v>489364071.8499241</v>
+        <v>489364071.8501844</v>
       </c>
       <c r="G4" s="19">
         <f>F4/E4-1</f>
@@ -7712,10 +8105,10 @@
         <v/>
       </c>
       <c r="E5" s="17" t="n">
-        <v>136195263.79</v>
+        <v>136195263.7899999</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>105644862.04</v>
+        <v>105644862.0400001</v>
       </c>
       <c r="G5" s="19">
         <f>F5/E5-1</f>

--- a/briefings/sezon-kadro-20260902/verimlilik-2026.xlsx
+++ b/briefings/sezon-kadro-20260902/verimlilik-2026.xlsx
@@ -229,7 +229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -312,7 +312,6 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2020,14 +2019,14 @@
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>Personel maliyeti ve ciro orani — SEZON Tem–Eki (kiyas: Tem) · yil geneli: 01-07 ay (Oca–Tem), her iki yıl · uc POS magazasi (İst. Yolu · Özlüce · Fsm)</t>
+          <t>Personel maliyeti ve ciro orani — SEZON Tem–Eki (kiyas: Tem) · yil geneli: Oca–Tem (yılbaşından bu yana) · uc POS magazasi (İst. Yolu · Özlüce · Fsm)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="59" t="inlineStr">
         <is>
-          <t>⚠ 2026 SEZONU HENÜZ TAMAMLANMADI. Sezon = Tem–Eki ayları; Ağu, Eyl, Eki ayı/ayları için bordro henüz işlenmedi (Ağustos bordrosu koşmadı, Eylül–Ekim daha gelmedi). Karşılaştırma tamamlanan ortak ay(lar) ile sınırlıdır: Tem. Geçen yılın TAM sezonu ayrıca referans olarak verilmiştir.</t>
+          <t>⚠ 2026 sezonu bitmedi: Ağu, Eyl, Eki ayları henüz bordroya girmedi. Karşılaştırma Tem ayı ile yapıldı; geçen yılın tam sezonu ayrıca gösteriliyor.</t>
         </is>
       </c>
     </row>
@@ -2069,28 +2068,28 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
-        <is>
-          <t>FTE — tam zaman esdeger (prim gunu/30)</t>
-        </is>
-      </c>
-      <c r="B4" s="60" t="n">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Calisan (tam gun karsiligi)</t>
+        </is>
+      </c>
+      <c r="B4" s="34" t="n">
         <v>97.13333333333333</v>
       </c>
-      <c r="C4" s="60" t="n">
+      <c r="C4" s="34" t="n">
         <v>112.4333333333333</v>
       </c>
-      <c r="D4" s="61">
+      <c r="D4" s="44">
         <f>C4/B4-1</f>
         <v/>
       </c>
-      <c r="E4" s="60" t="n">
+      <c r="E4" s="34" t="n">
         <v>697.0666666666666</v>
       </c>
-      <c r="F4" s="60" t="n">
+      <c r="F4" s="34" t="n">
         <v>776.1666666666666</v>
       </c>
-      <c r="G4" s="61">
+      <c r="G4" s="44">
         <f>F4/E4-1</f>
         <v/>
       </c>
@@ -2098,7 +2097,7 @@
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>Kayit sayisi (bordro satiri, bilgi)</t>
+          <t>Bordroda gorunen kisi (bilgi)</t>
         </is>
       </c>
       <c r="B5" s="17" t="n">
@@ -2125,7 +2124,7 @@
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>Ortalama prim gunu (kayit basina)</t>
+          <t>Kisi basina ortalama calisilan gun</t>
         </is>
       </c>
       <c r="B6" s="34" t="n">
@@ -2242,7 +2241,7 @@
       <c r="C10" s="52" t="n">
         <v>6782369.460000002</v>
       </c>
-      <c r="D10" s="61">
+      <c r="D10" s="60">
         <f>C10/B10-1</f>
         <v/>
       </c>
@@ -2252,7 +2251,7 @@
       <c r="F10" s="52" t="n">
         <v>47217361.01320001</v>
       </c>
-      <c r="G10" s="61">
+      <c r="G10" s="60">
         <f>F10/E10-1</f>
         <v/>
       </c>
@@ -2304,7 +2303,7 @@
         <v>242487002.9099963</v>
       </c>
       <c r="F12" s="17" t="n">
-        <v>388687036.5200129</v>
+        <v>388687036.520013</v>
       </c>
       <c r="G12" s="44">
         <f>F12/E12-1</f>
@@ -2314,7 +2313,7 @@
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>FTE basina maliyet</t>
+          <t>Kisi basina maliyet</t>
         </is>
       </c>
       <c r="B13" s="17" t="n">
@@ -2341,7 +2340,7 @@
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>FTE basina ciro</t>
+          <t>Kisi basina satis</t>
         </is>
       </c>
       <c r="B14" s="17" t="n">
@@ -2358,7 +2357,7 @@
         <v>347867.7356206909</v>
       </c>
       <c r="F14" s="17" t="n">
-        <v>500777.8009705985</v>
+        <v>500777.8009705986</v>
       </c>
       <c r="G14" s="44">
         <f>F14/E14-1</f>
@@ -2398,31 +2397,31 @@
           <t>MALIYET / CIRO ORANI</t>
         </is>
       </c>
-      <c r="B16" s="62" t="n">
+      <c r="B16" s="61" t="n">
         <v>0.14297033783446</v>
       </c>
-      <c r="C16" s="62" t="n">
+      <c r="C16" s="61" t="n">
         <v>0.1271160646389719</v>
       </c>
-      <c r="D16" s="63">
+      <c r="D16" s="62">
         <f>C16-B16</f>
         <v/>
       </c>
-      <c r="E16" s="62" t="n">
+      <c r="E16" s="61" t="n">
         <v>0.1284870034509203</v>
       </c>
-      <c r="F16" s="62" t="n">
+      <c r="F16" s="61" t="n">
         <v>0.121479124788791</v>
       </c>
-      <c r="G16" s="63">
+      <c r="G16" s="62">
         <f>F16-E16</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="64" t="inlineStr">
-        <is>
-          <t>Δ satirlari yuzde PUAN farkidir (eksi = ciro icindeki personel yuku azaldi). SEZON = Tem (esas) · KUM. = 01-07 ay (Oca–Tem), her iki yıl (yil geneli referansi).</t>
+      <c r="A17" s="63" t="inlineStr">
+        <is>
+          <t>Δ satirlari yuzde PUAN farkidir (eksi = ciro icindeki personel yuku azaldi). SEZON = Tem (esas) · KUM. = Oca–Tem (yılbaşından bu yana) (yil geneli referansi).</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2488,7 @@
           <t>Maliyet / ciro orani</t>
         </is>
       </c>
-      <c r="B25" s="65" t="n">
+      <c r="B25" s="64" t="n">
         <v>0.03538957684954572</v>
       </c>
     </row>
@@ -2504,7 +2503,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="64" t="inlineStr">
+      <c r="A27" s="63" t="inlineStr">
         <is>
           <t>SEZONUN SEKLI: sezonda ciro birkac kat artarken kadro ayni oranda artmaz -&gt; maliyet/ciro orani sezon aylarinda sezon disina gore COK dusuktur. Bu yuzden sezon ile yil-geneli oranlari BIRBIRIYLE kiyaslanmaz.</t>
         </is>
@@ -2672,7 +2671,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="64" t="inlineStr">
+      <c r="A34" s="63" t="inlineStr">
         <is>
           <t>⚠ Segment ayraci `vw_PersonelDepartman.Kadro` = BUGUNKU durum (tarihlenmiyor): gecmiste sezonluk calisip kadroya gecen kisi GECMIS ayda da KADROLU gorunur. Ayrica sezonluk alimin buyuk kismi AGUSTOS'ta; Agustos bordrosu islenince sezonluk agirligi gercek seviyesine cikar.</t>
         </is>
@@ -2813,7 +2812,7 @@
         <v>0.1064043589756548</v>
       </c>
       <c r="K38" s="42" t="n">
-        <v>0.0934279729173756</v>
+        <v>0.09342797291737541</v>
       </c>
       <c r="L38" s="17" t="n">
         <v>117</v>
@@ -3143,30 +3142,30 @@
           <t>Tem*</t>
         </is>
       </c>
-      <c r="B44" s="66" t="n">
+      <c r="B44" s="65" t="n">
         <v>97.13333333333333</v>
       </c>
-      <c r="C44" s="66" t="n">
+      <c r="C44" s="65" t="n">
         <v>112.4333333333333</v>
       </c>
       <c r="D44" s="19">
         <f>C44/B44-1</f>
         <v/>
       </c>
-      <c r="E44" s="67" t="n">
+      <c r="E44" s="66" t="n">
         <v>4386268.467500001</v>
       </c>
-      <c r="F44" s="67" t="n">
+      <c r="F44" s="66" t="n">
         <v>6782369.460000002</v>
       </c>
       <c r="G44" s="19">
         <f>F44/E44-1</f>
         <v/>
       </c>
-      <c r="H44" s="66" t="n">
+      <c r="H44" s="65" t="n">
         <v>643</v>
       </c>
-      <c r="I44" s="66" t="n">
+      <c r="I44" s="65" t="n">
         <v>783</v>
       </c>
       <c r="J44" s="42" t="n">
@@ -3175,25 +3174,25 @@
       <c r="K44" s="42" t="n">
         <v>0.1271160646389719</v>
       </c>
-      <c r="L44" s="67" t="n">
+      <c r="L44" s="66" t="n">
         <v>110</v>
       </c>
-      <c r="M44" s="67" t="n">
+      <c r="M44" s="66" t="n">
         <v>127</v>
       </c>
-      <c r="N44" s="66" t="n">
+      <c r="N44" s="65" t="n">
         <v>26.55905511811024</v>
       </c>
-      <c r="O44" s="66" t="n">
+      <c r="O44" s="65" t="n">
         <v>93.76666666666667</v>
       </c>
-      <c r="P44" s="66" t="n">
+      <c r="P44" s="65" t="n">
         <v>110.9</v>
       </c>
-      <c r="Q44" s="66" t="n">
+      <c r="Q44" s="65" t="n">
         <v>3.366666666666667</v>
       </c>
-      <c r="R44" s="66" t="n">
+      <c r="R44" s="65" t="n">
         <v>1.533333333333333</v>
       </c>
     </row>
@@ -3203,10 +3202,10 @@
           <t>Ağu*</t>
         </is>
       </c>
-      <c r="B45" s="66" t="n">
+      <c r="B45" s="65" t="n">
         <v>120.6333333333333</v>
       </c>
-      <c r="C45" s="66" t="inlineStr">
+      <c r="C45" s="65" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3215,10 +3214,10 @@
         <f>C45/B45-1</f>
         <v/>
       </c>
-      <c r="E45" s="67" t="n">
+      <c r="E45" s="66" t="n">
         <v>5442547.3939</v>
       </c>
-      <c r="F45" s="67" t="inlineStr">
+      <c r="F45" s="66" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3227,10 +3226,10 @@
         <f>F45/E45-1</f>
         <v/>
       </c>
-      <c r="H45" s="66" t="n">
+      <c r="H45" s="65" t="n">
         <v>2139.5</v>
       </c>
-      <c r="I45" s="66" t="inlineStr">
+      <c r="I45" s="65" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3243,31 +3242,31 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L45" s="67" t="n">
+      <c r="L45" s="66" t="n">
         <v>152</v>
       </c>
-      <c r="M45" s="67" t="inlineStr">
+      <c r="M45" s="66" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N45" s="66" t="inlineStr">
+      <c r="N45" s="65" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O45" s="66" t="n">
+      <c r="O45" s="65" t="n">
         <v>94.13333333333334</v>
       </c>
-      <c r="P45" s="66" t="inlineStr">
+      <c r="P45" s="65" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q45" s="66" t="n">
+      <c r="Q45" s="65" t="n">
         <v>26.5</v>
       </c>
-      <c r="R45" s="66" t="inlineStr">
+      <c r="R45" s="65" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3279,10 +3278,10 @@
           <t>Eyl*</t>
         </is>
       </c>
-      <c r="B46" s="66" t="n">
+      <c r="B46" s="65" t="n">
         <v>132.8333333333333</v>
       </c>
-      <c r="C46" s="66" t="inlineStr">
+      <c r="C46" s="65" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3291,10 +3290,10 @@
         <f>C46/B46-1</f>
         <v/>
       </c>
-      <c r="E46" s="67" t="n">
+      <c r="E46" s="66" t="n">
         <v>6568880.7995</v>
       </c>
-      <c r="F46" s="67" t="inlineStr">
+      <c r="F46" s="66" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3303,10 +3302,10 @@
         <f>F46/E46-1</f>
         <v/>
       </c>
-      <c r="H46" s="66" t="n">
+      <c r="H46" s="65" t="n">
         <v>3495</v>
       </c>
-      <c r="I46" s="66" t="inlineStr">
+      <c r="I46" s="65" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3319,31 +3318,31 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L46" s="67" t="n">
+      <c r="L46" s="66" t="n">
         <v>154</v>
       </c>
-      <c r="M46" s="67" t="inlineStr">
+      <c r="M46" s="66" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N46" s="66" t="inlineStr">
+      <c r="N46" s="65" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O46" s="66" t="n">
+      <c r="O46" s="65" t="n">
         <v>95.76666666666667</v>
       </c>
-      <c r="P46" s="66" t="inlineStr">
+      <c r="P46" s="65" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q46" s="66" t="n">
+      <c r="Q46" s="65" t="n">
         <v>37.06666666666666</v>
       </c>
-      <c r="R46" s="66" t="inlineStr">
+      <c r="R46" s="65" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3355,10 +3354,10 @@
           <t>Eki*</t>
         </is>
       </c>
-      <c r="B47" s="66" t="n">
+      <c r="B47" s="65" t="n">
         <v>108.1333333333333</v>
       </c>
-      <c r="C47" s="66" t="inlineStr">
+      <c r="C47" s="65" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3367,10 +3366,10 @@
         <f>C47/B47-1</f>
         <v/>
       </c>
-      <c r="E47" s="67" t="n">
+      <c r="E47" s="66" t="n">
         <v>4906942.701</v>
       </c>
-      <c r="F47" s="67" t="inlineStr">
+      <c r="F47" s="66" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3379,10 +3378,10 @@
         <f>F47/E47-1</f>
         <v/>
       </c>
-      <c r="H47" s="66" t="n">
+      <c r="H47" s="65" t="n">
         <v>1115.5</v>
       </c>
-      <c r="I47" s="66" t="inlineStr">
+      <c r="I47" s="65" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3395,31 +3394,31 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L47" s="67" t="n">
+      <c r="L47" s="66" t="n">
         <v>122</v>
       </c>
-      <c r="M47" s="67" t="inlineStr">
+      <c r="M47" s="66" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N47" s="66" t="inlineStr">
+      <c r="N47" s="65" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O47" s="66" t="n">
+      <c r="O47" s="65" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="P47" s="66" t="inlineStr">
+      <c r="P47" s="65" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q47" s="66" t="n">
+      <c r="Q47" s="65" t="n">
         <v>9.733333333333333</v>
       </c>
-      <c r="R47" s="66" t="inlineStr">
+      <c r="R47" s="65" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3732,7 +3731,7 @@
           <t>VARSAYIM: kisi basi YILLIK FM (saat)</t>
         </is>
       </c>
-      <c r="B66" s="68" t="n">
+      <c r="B66" s="67" t="n">
         <v>465.3191489361705</v>
       </c>
     </row>
@@ -3742,7 +3741,7 @@
           <t>YASAL UST SINIR (saat/yil/kisi)</t>
         </is>
       </c>
-      <c r="B67" s="68" t="n">
+      <c r="B67" s="67" t="n">
         <v>270</v>
       </c>
     </row>
@@ -3864,7 +3863,7 @@
       <c r="L71" s="17" t="n">
         <v>6782369.460000002</v>
       </c>
-      <c r="M71" s="65" t="n">
+      <c r="M71" s="64" t="n">
         <v>0.1271160646389762</v>
       </c>
     </row>
@@ -3879,7 +3878,7 @@
           <t>gercek</t>
         </is>
       </c>
-      <c r="C72" s="69" t="inlineStr">
+      <c r="C72" s="68" t="inlineStr">
         <is>
           <t>TAHMIN</t>
         </is>
@@ -3903,16 +3902,16 @@
       <c r="I72" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="J72" s="70" t="n">
+      <c r="J72" s="69" t="n">
         <v>120.6333333333333</v>
       </c>
-      <c r="K72" s="70" t="n">
+      <c r="K72" s="69" t="n">
         <v>139.6349462365592</v>
       </c>
       <c r="L72" s="56" t="n">
         <v>8423265.297096778</v>
       </c>
-      <c r="M72" s="71" t="n">
+      <c r="M72" s="70" t="n">
         <v>0.04893988567046193</v>
       </c>
     </row>
@@ -3922,12 +3921,12 @@
           <t>Eyl</t>
         </is>
       </c>
-      <c r="B73" s="69" t="inlineStr">
+      <c r="B73" s="68" t="inlineStr">
         <is>
           <t>KISMI</t>
         </is>
       </c>
-      <c r="C73" s="69" t="inlineStr">
+      <c r="C73" s="68" t="inlineStr">
         <is>
           <t>TAHMIN</t>
         </is>
@@ -3951,16 +3950,16 @@
       <c r="I73" s="56" t="n">
         <v>28</v>
       </c>
-      <c r="J73" s="70" t="n">
+      <c r="J73" s="69" t="n">
         <v>132.8333333333333</v>
       </c>
-      <c r="K73" s="70" t="n">
+      <c r="K73" s="69" t="n">
         <v>153.7566346373827</v>
       </c>
       <c r="L73" s="56" t="n">
         <v>9275134.625291698</v>
       </c>
-      <c r="M73" s="71" t="n">
+      <c r="M73" s="70" t="n">
         <v>0.01467807762216236</v>
       </c>
     </row>
@@ -3970,12 +3969,12 @@
           <t>Eki</t>
         </is>
       </c>
-      <c r="B74" s="69" t="inlineStr">
+      <c r="B74" s="68" t="inlineStr">
         <is>
           <t>TAHMIN</t>
         </is>
       </c>
-      <c r="C74" s="69" t="inlineStr">
+      <c r="C74" s="68" t="inlineStr">
         <is>
           <t>TAHMIN</t>
         </is>
@@ -3999,16 +3998,16 @@
       <c r="I74" s="56" t="n">
         <v>31</v>
       </c>
-      <c r="J74" s="70" t="n">
+      <c r="J74" s="69" t="n">
         <v>108.1333333333333</v>
       </c>
-      <c r="K74" s="70" t="n">
+      <c r="K74" s="69" t="n">
         <v>125.1660032029284</v>
       </c>
       <c r="L74" s="56" t="n">
         <v>7550448.362470834</v>
       </c>
-      <c r="M74" s="71" t="n">
+      <c r="M74" s="70" t="n">
         <v>0.05676323642353558</v>
       </c>
     </row>
@@ -4018,28 +4017,28 @@
           <t>Agu+Eyl</t>
         </is>
       </c>
-      <c r="B75" s="64" t="inlineStr">
+      <c r="B75" s="63" t="inlineStr">
         <is>
           <t>kayma notr</t>
         </is>
       </c>
-      <c r="D75" s="72" t="n">
+      <c r="D75" s="71" t="n">
         <v>499925136.6700268</v>
       </c>
-      <c r="E75" s="72" t="n">
+      <c r="E75" s="71" t="n">
         <v>804018436.42835</v>
       </c>
       <c r="F75" s="19">
         <f>E75/D75-1</f>
         <v/>
       </c>
-      <c r="J75" s="73" t="n">
+      <c r="J75" s="72" t="n">
         <v>253.4666666666666</v>
       </c>
-      <c r="K75" s="73" t="n">
+      <c r="K75" s="72" t="n">
         <v>293.3915808739419</v>
       </c>
-      <c r="L75" s="72" t="n">
+      <c r="L75" s="71" t="n">
         <v>17698399.92238848</v>
       </c>
     </row>
@@ -4068,7 +4067,7 @@
       <c r="L76" s="21" t="n">
         <v>32031217.74485931</v>
       </c>
-      <c r="M76" s="74" t="n">
+      <c r="M76" s="73" t="n">
         <v>0.03234200232392012</v>
       </c>
     </row>
@@ -4080,49 +4079,49 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="64" t="inlineStr">
+      <c r="A79" s="63" t="inlineStr">
         <is>
           <t>YONTEM: okul-hizalı gün eşleme (ciro) + sezon şekli×seviye (FTE) + FTE başına maliyet</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="64" t="inlineStr">
+      <c r="A80" s="63" t="inlineStr">
         <is>
           <t>VARSAYIM: Sezon şekli yıl üzerinden aynı: 2025'in gün-bazlı satış dağılımı okul açılışına hizalanarak 2026 takvimine taşındı (açılış 08.09.2025 → 14.09.2026).</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="64" t="inlineStr">
+      <c r="A81" s="63" t="inlineStr">
         <is>
           <t>VARSAYIM: Seviye: hizalı pencerede ÖLÇÜLEN ciro büyümesi (%66.0) uygulandı — ayrı bir büyüme varsayımı yapılmadı.</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="64" t="inlineStr">
+      <c r="A82" s="63" t="inlineStr">
         <is>
           <t>VARSAYIM: FTE: sezon şekli 2025'ten, seviye 2026'nın Tem ayından (katsayı 1.158).</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="64" t="inlineStr">
+      <c r="A83" s="63" t="inlineStr">
         <is>
           <t>VARSAYIM: Maliyet: tahmini FTE × 2026 Tem ayının FTE başına maliyeti (60.323 ₺). Ücret seviyesi sabit varsayıldı → zam/asgari ücret artışı olursa maliyet tahmini ALT SINIRDIR.</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="64" t="inlineStr">
+      <c r="A84" s="63" t="inlineStr">
         <is>
           <t>VARSAYIM: Gerçekleşen günler tahminle değiştirilmedi: 02.09.2026 tarihine kadar gerçek veri, sonrası tahmindir.</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="64" t="inlineStr">
+      <c r="A85" s="63" t="inlineStr">
         <is>
           <t>VARSAYIM: Bayram/tatil kayması ve mağaza açılış-kapanışı modellenmedi.</t>
         </is>
@@ -4138,14 +4137,14 @@
     <row r="88">
       <c r="A88" s="32" t="inlineStr">
         <is>
-          <t>OLCU BIRIMI **FTE** (tam zaman esdeger) = SGK prim gunu / 30. Bordro SATIRI (kayit) yaniltir: ay icinde 1 gun calisan da 1 sayilir; sezonluk giris/cikis yogun oldugu icin sisme en cok sezon ayinda olur. Kayit sayisi ve ortalama prim gunu seffaflik icin ayri satirlarda/kolonlarda durur.</t>
+          <t>CALISAN SAYISI TAM GUN KARSILIGIDIR (SGK prim gunu / 30): yarim ay calisan yarim sayilir. Bordroda gorunen kisi sayisi yaniltir — ay icinde 1 gun calisan da 1 sayilir. Iki rakam da tabloda yan yana durur.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="32" t="inlineStr">
         <is>
-          <t>PENCERE: SEZON = Tem–Eki (Temmuz hazırlık; asıl hacim ve sezonluk kadro Ağustos–Ekim). 2026 sezonu henüz tamamlanmadığı için KIYAS tamamlanan ortak ay(lar) ile yapılır: Tem. KÜMÜLATİF pencere (01-07 ay (Oca–Tem), her iki yıl) yıl geneli referansıdır; aylık kırılım artışın hangi ayda oluştuğunu gösterir; geçen yılın tam sezonu ayrı blokta durur.</t>
+          <t>PENCERE: SEZON = Tem–Eki (Temmuz hazırlık; asıl hacim ve sezonluk kadro Ağustos–Ekim). 2026 sezonu henüz tamamlanmadığı için KIYAS tamamlanan ortak ay(lar) ile yapılır: Tem. KÜMÜLATİF pencere (Oca–Tem (yılbaşından bu yana)) yıl geneli referansıdır; aylık kırılım artışın hangi ayda oluştuğunu gösterir; geçen yılın tam sezonu ayrı blokta durur.</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4158,7 @@
     <row r="91">
       <c r="A91" s="32" t="inlineStr">
         <is>
-          <t>⚠ ⚠ 2026 SEZONU HENÜZ TAMAMLANMADI. Sezon = Tem–Eki ayları; Ağu, Eyl, Eki ayı/ayları için bordro henüz işlenmedi (Ağustos bordrosu koşmadı, Eylül–Ekim daha gelmedi). Karşılaştırma tamamlanan ortak ay(lar) ile sınırlıdır: Tem. Geçen yılın TAM sezonu ayrıca referans olarak verilmiştir.</t>
+          <t>⚠ ⚠ 2026 sezonu bitmedi: Ağu, Eyl, Eki ayları henüz bordroya girmedi. Karşılaştırma Tem ayı ile yapıldı; geçen yılın tam sezonu ayrıca gösteriliyor.</t>
         </is>
       </c>
     </row>
@@ -4217,72 +4216,72 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="75" t="inlineStr">
+      <c r="A3" s="74" t="inlineStr">
         <is>
           <t>Baslik</t>
         </is>
       </c>
-      <c r="B3" s="76" t="inlineStr">
+      <c r="B3" s="75" t="inlineStr">
         <is>
           <t>Kişi başı iş hacmi — sezon 2026 vs 2025</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="75" t="inlineStr">
+      <c r="A4" s="74" t="inlineStr">
         <is>
           <t>Kesim tarihi</t>
         </is>
       </c>
-      <c r="B4" s="76" t="inlineStr">
+      <c r="B4" s="75" t="inlineStr">
         <is>
           <t>otomatik (veri sonu, okul-hizalı pencerede)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="75" t="inlineStr">
+      <c r="A5" s="74" t="inlineStr">
         <is>
           <t>Pencere</t>
         </is>
       </c>
-      <c r="B5" s="76" t="inlineStr">
+      <c r="B5" s="75" t="inlineStr">
         <is>
           <t>Okul açılışına hizalı — 2025: 01.07.2025 – 25.08.2025 · 2026: 07.07.2026 – 31.08.2026 (her iki yıl 56 gün; açılış 20250908 ve 20260914, gün ofseti -69..-14)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="75" t="inlineStr">
+      <c r="A6" s="74" t="inlineStr">
         <is>
           <t>Kadro kaynagi</t>
         </is>
       </c>
-      <c r="B6" s="76" t="inlineStr">
+      <c r="B6" s="75" t="inlineStr">
         <is>
           <t>Zirve BKM_GENEL.dbo.vw_PersonelDepartman — as-of Igt &lt;= T AND (Ict IS NULL OR Ict &gt;= T), sp_PersonelKarsilastirma_Ozet ile birebir</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="75" t="inlineStr">
+      <c r="A7" s="74" t="inlineStr">
         <is>
           <t>Is hacmi kaynagi</t>
         </is>
       </c>
-      <c r="B7" s="76" t="inlineStr">
+      <c r="B7" s="75" t="inlineStr">
         <is>
           <t>DerinSIS irs/irsAyr eTip=100 (POS satışı), Sınav Okulları/Kıyafet hariç, iade netlenmiş</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="75" t="inlineStr">
+      <c r="A8" s="74" t="inlineStr">
         <is>
           <t>Cekirdek SQL</t>
         </is>
       </c>
-      <c r="B8" s="76" t="inlineStr">
+      <c r="B8" s="75" t="inlineStr">
         <is>
           <t>sorgular/2026-09-02-kadro-vs-is-hacmi-savunma.sql (blok 11)</t>
         </is>
@@ -4296,49 +4295,49 @@
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="B11" s="77" t="inlineStr">
+      <c r="B11" s="76" t="inlineStr">
         <is>
           <t>• Ürün adedi enflasyondan bağımsız — kadro kıyasında birincil ölçüt. Ciro ikincil (fiyat endeksi +%19,8, Fisher, eşleşen ürün).</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="B12" s="77" t="inlineStr">
+      <c r="B12" s="76" t="inlineStr">
         <is>
           <t>• Kıyas okul açılışına hizalı yapılır. Takvim tarihine göre kıyas 2026'da yapay düşüş gösterir: açılış 8 Eylül 2025'ten 14 Eylül 2026'ya, 6 gün kaydı.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="B13" s="77" t="inlineStr">
+      <c r="B13" s="76" t="inlineStr">
         <is>
           <t>• İş hacmi EncoreMerkez POS'tan DEĞİL DerinSIS'ten alınır: POS Temmuz 2025'te değişti (ENPOS → EncoreMerkez), EncoreMerkez'in 2025 tabanı eksik.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="B14" s="77" t="inlineStr">
+      <c r="B14" s="76" t="inlineStr">
         <is>
           <t>• Heykel ve Şura POS raporlamasında yok — mağaza sayfası üç POS mağazası (FSM · Özlüce · İst. Yolu). Beş mağaza kadro hareketi Özet'te ayrı.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="B15" s="77" t="inlineStr">
+      <c r="B15" s="76" t="inlineStr">
         <is>
           <t>• Kadro = o tarihte fiilen çalışan kişi (sezonluk + kadrolu). Kişi başı oranlar kasiyer değil TÜM mağaza kadrosu üzerinden.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="B16" s="77" t="inlineStr">
+      <c r="B16" s="76" t="inlineStr">
         <is>
           <t>• Fiş sayısı bu kaynakta yok: eTip 100 günlük özet belgedir (bir gün = bir belge).</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
-      <c r="B17" s="77" t="inlineStr">
+      <c r="B17" s="76" t="inlineStr">
         <is>
           <t>• Kıdem → verimlilik testi NEGATİF çıktı: aynı kasiyerin öğrenme eğrisi düz (220 → 256 → 242 fiş/gün), mağaza kıdem sıralaması verimlilikle uyuşmuyor. 'Tecrübeli 1 kişi = acemi 3 kişi' iddiası bu veriyle savunulamaz.</t>
         </is>
@@ -4502,10 +4501,10 @@
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>66909340.21999986</v>
+        <v>66909340.21999952</v>
       </c>
       <c r="C9" s="17" t="n">
-        <v>114620580.3400004</v>
+        <v>114620580.340005</v>
       </c>
       <c r="D9" s="18">
         <f>C9-B9</f>
@@ -4523,7 +4522,7 @@
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>71817045.76999547</v>
+        <v>71817045.76999521</v>
       </c>
       <c r="C10" s="17" t="n">
         <v>122534175.6099948</v>
@@ -5060,10 +5059,10 @@
         <v/>
       </c>
       <c r="M4" s="17" t="n">
-        <v>20434775.08000033</v>
+        <v>20434775.08000028</v>
       </c>
       <c r="N4" s="17" t="n">
-        <v>40377406.52999959</v>
+        <v>40377406.53000186</v>
       </c>
       <c r="O4" s="19">
         <f>N4/M4-1</f>
@@ -5133,10 +5132,10 @@
         <v/>
       </c>
       <c r="M5" s="17" t="n">
-        <v>28347121.58999967</v>
+        <v>28347121.58999922</v>
       </c>
       <c r="N5" s="17" t="n">
-        <v>44784483.14999995</v>
+        <v>44784483.1500014</v>
       </c>
       <c r="O5" s="19">
         <f>N5/M5-1</f>
@@ -5206,10 +5205,10 @@
         <v/>
       </c>
       <c r="M6" s="17" t="n">
-        <v>18127443.54999987</v>
+        <v>18127443.55000003</v>
       </c>
       <c r="N6" s="17" t="n">
-        <v>29458690.66000083</v>
+        <v>29458690.66000168</v>
       </c>
       <c r="O6" s="19">
         <f>N6/M6-1</f>
@@ -6806,10 +6805,10 @@
         <v/>
       </c>
       <c r="F4" s="34" t="n">
-        <v>18.50432497000117</v>
+        <v>18.50432497000297</v>
       </c>
       <c r="G4" s="34" t="n">
-        <v>32.38086690000175</v>
+        <v>32.38086690000117</v>
       </c>
       <c r="H4" s="44">
         <f>G4/F4-1</f>
@@ -6826,7 +6825,7 @@
         <v/>
       </c>
       <c r="L4" s="19" t="n">
-        <v>0.3747245332279163</v>
+        <v>0.3747245332284828</v>
       </c>
       <c r="M4" s="45" t="n">
         <v>3</v>
@@ -6847,17 +6846,17 @@
         <v>73247</v>
       </c>
       <c r="D5" s="17" t="n">
-        <v>85696</v>
+        <v>85697</v>
       </c>
       <c r="E5" s="44">
         <f>D5/C5-1</f>
         <v/>
       </c>
       <c r="F5" s="34" t="n">
-        <v>10.02370843999998</v>
+        <v>10.02370844</v>
       </c>
       <c r="G5" s="34" t="n">
-        <v>15.50422908999997</v>
+        <v>15.50442399000005</v>
       </c>
       <c r="H5" s="44">
         <f>G5/F5-1</f>
@@ -6867,14 +6866,14 @@
         <v>358316</v>
       </c>
       <c r="J5" s="17" t="n">
-        <v>440372</v>
+        <v>440374</v>
       </c>
       <c r="K5" s="19">
         <f>IF(OR(I5="—",J5="—"),"",J5/I5-1)</f>
         <v/>
       </c>
       <c r="L5" s="19" t="n">
-        <v>0.5770282964720179</v>
+        <v>0.5770368636217145</v>
       </c>
       <c r="M5" s="45" t="n">
         <v>-1</v>
@@ -6905,7 +6904,7 @@
         <v>14.49106598999975</v>
       </c>
       <c r="G6" s="34" t="n">
-        <v>23.14058788999987</v>
+        <v>23.1405878899999</v>
       </c>
       <c r="H6" s="44">
         <f>G6/F6-1</f>
@@ -6922,7 +6921,7 @@
         <v/>
       </c>
       <c r="L6" s="19" t="n">
-        <v>0.4921459875658043</v>
+        <v>0.4921459875658065</v>
       </c>
       <c r="M6" s="45" t="n">
         <v>1</v>
@@ -6970,7 +6969,7 @@
         <v/>
       </c>
       <c r="L7" s="19" t="n">
-        <v>1.79767339423362</v>
+        <v>1.797673394233622</v>
       </c>
       <c r="M7" s="40" t="inlineStr">
         <is>
@@ -7003,7 +7002,7 @@
         <v>11.13631267999999</v>
       </c>
       <c r="G8" s="34" t="n">
-        <v>16.74884972000005</v>
+        <v>16.74884972000006</v>
       </c>
       <c r="H8" s="44">
         <f>G8/F8-1</f>
@@ -7020,7 +7019,7 @@
         <v/>
       </c>
       <c r="L8" s="19" t="n">
-        <v>0.6655996445022558</v>
+        <v>0.6655996445022836</v>
       </c>
       <c r="M8" s="45" t="n">
         <v>1</v>
@@ -7048,10 +7047,10 @@
         <v/>
       </c>
       <c r="F9" s="34" t="n">
-        <v>1.475290260000006</v>
+        <v>1.475290260000007</v>
       </c>
       <c r="G9" s="34" t="n">
-        <v>2.616103030000003</v>
+        <v>2.616103030000004</v>
       </c>
       <c r="H9" s="44">
         <f>G9/F9-1</f>
@@ -7068,7 +7067,7 @@
         <v/>
       </c>
       <c r="L9" s="19" t="n">
-        <v>1.258006023303444</v>
+        <v>1.258006023303468</v>
       </c>
       <c r="M9" s="40" t="inlineStr">
         <is>
@@ -7091,7 +7090,7 @@
         <v>38785</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>53872</v>
+        <v>53873</v>
       </c>
       <c r="E10" s="44">
         <f>D10/C10-1</f>
@@ -7101,7 +7100,7 @@
         <v>11.64473918999999</v>
       </c>
       <c r="G10" s="34" t="n">
-        <v>22.29073933999993</v>
+        <v>22.29116433999994</v>
       </c>
       <c r="H10" s="44">
         <f>G10/F10-1</f>
@@ -7111,14 +7110,14 @@
         <v>218692</v>
       </c>
       <c r="J10" s="17" t="n">
-        <v>266398</v>
+        <v>266399</v>
       </c>
       <c r="K10" s="19">
         <f>IF(OR(I10="—",J10="—"),"",J10/I10-1)</f>
         <v/>
       </c>
       <c r="L10" s="19" t="n">
-        <v>0.4631940216117609</v>
+        <v>0.4632017307261715</v>
       </c>
       <c r="M10" s="45" t="n">
         <v>6</v>
@@ -7146,7 +7145,7 @@
         <v/>
       </c>
       <c r="F11" s="34" t="n">
-        <v>0.6921173299999999</v>
+        <v>0.6921173300000001</v>
       </c>
       <c r="G11" s="34" t="n">
         <v>1.187673780000001</v>
@@ -7166,7 +7165,7 @@
         <v/>
       </c>
       <c r="L11" s="19" t="n">
-        <v>0.4636366398909308</v>
+        <v>0.4636366398909264</v>
       </c>
       <c r="M11" s="40" t="inlineStr">
         <is>
@@ -7196,10 +7195,10 @@
         <v/>
       </c>
       <c r="F12" s="34" t="n">
-        <v>1.942142249999997</v>
+        <v>1.942142249999999</v>
       </c>
       <c r="G12" s="34" t="n">
-        <v>6.643827519999999</v>
+        <v>6.643827519999995</v>
       </c>
       <c r="H12" s="44">
         <f>G12/F12-1</f>
@@ -7216,7 +7215,7 @@
         <v/>
       </c>
       <c r="L12" s="19" t="n">
-        <v>1.76909345352259</v>
+        <v>1.769093453522589</v>
       </c>
       <c r="M12" s="45" t="n">
         <v>2</v>
@@ -7244,10 +7243,10 @@
         <v/>
       </c>
       <c r="F13" s="34" t="n">
-        <v>0.2846255699999999</v>
+        <v>0.2846255699999998</v>
       </c>
       <c r="G13" s="34" t="n">
-        <v>0.4203621899999996</v>
+        <v>0.4203621899999998</v>
       </c>
       <c r="H13" s="44">
         <f>G13/F13-1</f>
@@ -7264,7 +7263,7 @@
         <v/>
       </c>
       <c r="L13" s="19" t="n">
-        <v>0.5224217348514271</v>
+        <v>0.5224217348514226</v>
       </c>
       <c r="M13" s="40" t="inlineStr">
         <is>
@@ -7297,7 +7296,7 @@
         <v>1.257655950000001</v>
       </c>
       <c r="G14" s="34" t="n">
-        <v>0.9961937400000003</v>
+        <v>0.9961937400000005</v>
       </c>
       <c r="H14" s="44">
         <f>G14/F14-1</f>
@@ -7314,7 +7313,7 @@
         <v/>
       </c>
       <c r="L14" s="19" t="n">
-        <v>0.4008427609025713</v>
+        <v>0.4008427609025695</v>
       </c>
       <c r="M14" s="40" t="inlineStr">
         <is>
@@ -7337,7 +7336,7 @@
         <v>2570</v>
       </c>
       <c r="D15" s="17" t="n">
-        <v>2440</v>
+        <v>2439</v>
       </c>
       <c r="E15" s="44">
         <f>D15/C15-1</f>
@@ -7347,7 +7346,7 @@
         <v>0.2656298399999997</v>
       </c>
       <c r="G15" s="34" t="n">
-        <v>0.3784858199999995</v>
+        <v>0.3782909199999996</v>
       </c>
       <c r="H15" s="44">
         <f>G15/F15-1</f>
@@ -7357,14 +7356,14 @@
         <v>12790</v>
       </c>
       <c r="J15" s="17" t="n">
-        <v>13387</v>
+        <v>13385</v>
       </c>
       <c r="K15" s="19">
         <f>IF(OR(I15="—",J15="—"),"",J15/I15-1)</f>
         <v/>
       </c>
       <c r="L15" s="19" t="n">
-        <v>0.4999858989104855</v>
+        <v>0.4996437510927461</v>
       </c>
       <c r="M15" s="40" t="inlineStr">
         <is>
@@ -7542,10 +7541,10 @@
         <v/>
       </c>
       <c r="E4" s="34" t="n">
-        <v>33.37095816000493</v>
+        <v>33.37095816000334</v>
       </c>
       <c r="F4" s="34" t="n">
-        <v>49.92745519999929</v>
+        <v>49.92745520000055</v>
       </c>
       <c r="G4" s="44">
         <f>F4/E4-1</f>
@@ -7569,10 +7568,10 @@
         <v/>
       </c>
       <c r="E5" s="34" t="n">
-        <v>32.14602051000463</v>
+        <v>32.14602051000339</v>
       </c>
       <c r="F5" s="34" t="n">
-        <v>55.81900908999923</v>
+        <v>55.81900909000084</v>
       </c>
       <c r="G5" s="44">
         <f>F5/E5-1</f>
@@ -7596,10 +7595,10 @@
         <v/>
       </c>
       <c r="E6" s="34" t="n">
-        <v>61.26123197999352</v>
+        <v>61.26123198000126</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>78.0862114399969</v>
+        <v>78.08621143999895</v>
       </c>
       <c r="G6" s="44">
         <f>F6/E6-1</f>
@@ -8078,10 +8077,10 @@
         <v/>
       </c>
       <c r="E4" s="17" t="n">
-        <v>315972605.8803364</v>
+        <v>315972605.8803039</v>
       </c>
       <c r="F4" s="17" t="n">
-        <v>489364071.8501844</v>
+        <v>489364071.8501887</v>
       </c>
       <c r="G4" s="19">
         <f>F4/E4-1</f>
